--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G19">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G53">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G63">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G68">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G76">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.36</v>
+        <v>3.31</v>
       </c>
       <c r="O79">
-        <v>3.94</v>
+        <v>3.32</v>
       </c>
       <c r="P79">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.31</v>
+        <v>4.36</v>
       </c>
       <c r="O80">
-        <v>3.32</v>
+        <v>3.94</v>
       </c>
       <c r="P80">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N91">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G109">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="O119">
-        <v>3.93</v>
+        <v>3.48</v>
       </c>
       <c r="P119">
-        <v>5.55</v>
+        <v>3.62</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="O120">
-        <v>3.48</v>
+        <v>3.93</v>
       </c>
       <c r="P120">
-        <v>3.62</v>
+        <v>5.55</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G133">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G142">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G145">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="O148">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P148">
-        <v>4.84</v>
+        <v>3.91</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB148">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="O149">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P149">
-        <v>3.91</v>
+        <v>4.84</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB149">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G162">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O174">
-        <v>4.14</v>
+        <v>4.42</v>
       </c>
       <c r="P174">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,16 +28710,16 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O175">
-        <v>4.42</v>
+        <v>4.14</v>
       </c>
       <c r="P175">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,16 +28873,16 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC175">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD175">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE175">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU182"/>
+  <dimension ref="A1:AU185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G105">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="O120">
-        <v>3.93</v>
+        <v>3.48</v>
       </c>
       <c r="P120">
-        <v>5.55</v>
+        <v>3.62</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-16 14:15:00</t>
+          <t>2026-08-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-16 14:30:00</t>
+          <t>2026-08-16 14:15:00</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G128">
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-16 15:00:00</t>
+          <t>2026-08-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G136">
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-16 15:15:00</t>
+          <t>2026-08-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G140">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-16 15:30:00</t>
+          <t>2026-08-16 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23576,22 +23576,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O146">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P146">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24223,27 +24223,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-16 16:00:00</t>
+          <t>2026-08-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="O149">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P149">
-        <v>4.84</v>
+        <v>3.91</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB149">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G156">
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O157">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P157">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB157">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26016,27 +26016,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G158">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26179,12 +26179,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26505,27 +26505,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G161">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26668,27 +26668,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26831,27 +26831,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G163">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-16 18:00:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G165">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-16 18:15:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27320,12 +27320,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="O166">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P166">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27406,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB166">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC166">
         <v>0</v>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O167">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P167">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB167">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G168">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:15:00</t>
         </is>
       </c>
     </row>
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28716,10 +28716,10 @@
         <v>0</v>
       </c>
       <c r="AC174">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB175">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O176">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB176">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-16 19:30:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29205,10 +29205,10 @@
         <v>0</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-16 20:00:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O180">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P180">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB180">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-16 21:30:00</t>
+          <t>2026-08-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G181">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-16 22:00:00</t>
+          <t>2026-08-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -29928,156 +29928,645 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>SD Aucas</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>0</v>
+      </c>
+      <c r="Q182">
+        <v>0</v>
+      </c>
+      <c r="R182">
+        <v>0</v>
+      </c>
+      <c r="S182">
+        <v>0</v>
+      </c>
+      <c r="T182">
+        <v>0</v>
+      </c>
+      <c r="U182">
+        <v>0</v>
+      </c>
+      <c r="V182">
+        <v>0</v>
+      </c>
+      <c r="W182">
+        <v>0</v>
+      </c>
+      <c r="X182">
+        <v>0</v>
+      </c>
+      <c r="Y182">
+        <v>0</v>
+      </c>
+      <c r="Z182">
+        <v>0</v>
+      </c>
+      <c r="AA182">
+        <v>0</v>
+      </c>
+      <c r="AB182">
+        <v>0</v>
+      </c>
+      <c r="AC182">
+        <v>0</v>
+      </c>
+      <c r="AD182">
+        <v>0</v>
+      </c>
+      <c r="AE182">
+        <v>0</v>
+      </c>
+      <c r="AF182">
+        <v>0</v>
+      </c>
+      <c r="AG182">
+        <v>0</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ182">
+        <v>0</v>
+      </c>
+      <c r="AK182">
+        <v>0</v>
+      </c>
+      <c r="AL182">
+        <v>0</v>
+      </c>
+      <c r="AM182">
+        <v>-1</v>
+      </c>
+      <c r="AN182">
+        <v>-1</v>
+      </c>
+      <c r="AO182">
+        <v>-1</v>
+      </c>
+      <c r="AP182">
+        <v>-1</v>
+      </c>
+      <c r="AQ182">
+        <v>0</v>
+      </c>
+      <c r="AR182">
+        <v>0</v>
+      </c>
+      <c r="AS182">
+        <v>0</v>
+      </c>
+      <c r="AT182">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N183">
+        <v>2.92</v>
+      </c>
+      <c r="O183">
+        <v>3.69</v>
+      </c>
+      <c r="P183">
+        <v>2.39</v>
+      </c>
+      <c r="Q183">
+        <v>0</v>
+      </c>
+      <c r="R183">
+        <v>0</v>
+      </c>
+      <c r="S183">
+        <v>0</v>
+      </c>
+      <c r="T183">
+        <v>0</v>
+      </c>
+      <c r="U183">
+        <v>0</v>
+      </c>
+      <c r="V183">
+        <v>0</v>
+      </c>
+      <c r="W183">
+        <v>0</v>
+      </c>
+      <c r="X183">
+        <v>0</v>
+      </c>
+      <c r="Y183">
+        <v>0</v>
+      </c>
+      <c r="Z183">
+        <v>0</v>
+      </c>
+      <c r="AA183">
+        <v>1.53</v>
+      </c>
+      <c r="AB183">
+        <v>2.3</v>
+      </c>
+      <c r="AC183">
+        <v>0</v>
+      </c>
+      <c r="AD183">
+        <v>0</v>
+      </c>
+      <c r="AE183">
+        <v>0</v>
+      </c>
+      <c r="AF183">
+        <v>0</v>
+      </c>
+      <c r="AG183">
+        <v>0</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ183">
+        <v>0</v>
+      </c>
+      <c r="AK183">
+        <v>0</v>
+      </c>
+      <c r="AL183">
+        <v>0</v>
+      </c>
+      <c r="AM183">
+        <v>-1</v>
+      </c>
+      <c r="AN183">
+        <v>-1</v>
+      </c>
+      <c r="AO183">
+        <v>-1</v>
+      </c>
+      <c r="AP183">
+        <v>-1</v>
+      </c>
+      <c r="AQ183">
+        <v>0</v>
+      </c>
+      <c r="AR183">
+        <v>0</v>
+      </c>
+      <c r="AS183">
+        <v>0</v>
+      </c>
+      <c r="AT183">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+      <c r="Q184">
+        <v>0</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+      <c r="S184">
+        <v>0</v>
+      </c>
+      <c r="T184">
+        <v>0</v>
+      </c>
+      <c r="U184">
+        <v>0</v>
+      </c>
+      <c r="V184">
+        <v>0</v>
+      </c>
+      <c r="W184">
+        <v>0</v>
+      </c>
+      <c r="X184">
+        <v>0</v>
+      </c>
+      <c r="Y184">
+        <v>0</v>
+      </c>
+      <c r="Z184">
+        <v>0</v>
+      </c>
+      <c r="AA184">
+        <v>0</v>
+      </c>
+      <c r="AB184">
+        <v>0</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>0</v>
+      </c>
+      <c r="AF184">
+        <v>0</v>
+      </c>
+      <c r="AG184">
+        <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ184">
+        <v>0</v>
+      </c>
+      <c r="AK184">
+        <v>0</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>-1</v>
+      </c>
+      <c r="AN184">
+        <v>-1</v>
+      </c>
+      <c r="AO184">
+        <v>-1</v>
+      </c>
+      <c r="AP184">
+        <v>-1</v>
+      </c>
+      <c r="AQ184">
+        <v>0</v>
+      </c>
+      <c r="AR184">
+        <v>0</v>
+      </c>
+      <c r="AS184">
+        <v>0</v>
+      </c>
+      <c r="AT184">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>2026-08-16 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="G182">
-        <v>0</v>
-      </c>
-      <c r="H182">
-        <v>0</v>
-      </c>
-      <c r="I182">
-        <v>0</v>
-      </c>
-      <c r="J182">
-        <v>0</v>
-      </c>
-      <c r="K182">
-        <v>0</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="M182" t="inlineStr">
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N182">
+      <c r="N185">
         <v>3.25</v>
       </c>
-      <c r="O182">
+      <c r="O185">
         <v>3.55</v>
       </c>
-      <c r="P182">
+      <c r="P185">
         <v>2</v>
       </c>
-      <c r="Q182">
-        <v>0</v>
-      </c>
-      <c r="R182">
-        <v>0</v>
-      </c>
-      <c r="S182">
-        <v>0</v>
-      </c>
-      <c r="T182">
-        <v>0</v>
-      </c>
-      <c r="U182">
-        <v>0</v>
-      </c>
-      <c r="V182">
-        <v>0</v>
-      </c>
-      <c r="W182">
-        <v>0</v>
-      </c>
-      <c r="X182">
-        <v>0</v>
-      </c>
-      <c r="Y182">
-        <v>0</v>
-      </c>
-      <c r="Z182">
-        <v>0</v>
-      </c>
-      <c r="AA182">
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+      <c r="S185">
+        <v>0</v>
+      </c>
+      <c r="T185">
+        <v>0</v>
+      </c>
+      <c r="U185">
+        <v>0</v>
+      </c>
+      <c r="V185">
+        <v>0</v>
+      </c>
+      <c r="W185">
+        <v>0</v>
+      </c>
+      <c r="X185">
+        <v>0</v>
+      </c>
+      <c r="Y185">
+        <v>0</v>
+      </c>
+      <c r="Z185">
+        <v>0</v>
+      </c>
+      <c r="AA185">
         <v>1.55</v>
       </c>
-      <c r="AB182">
+      <c r="AB185">
         <v>2.3</v>
       </c>
-      <c r="AC182">
-        <v>0</v>
-      </c>
-      <c r="AD182">
-        <v>0</v>
-      </c>
-      <c r="AE182">
-        <v>0</v>
-      </c>
-      <c r="AF182">
-        <v>0</v>
-      </c>
-      <c r="AG182">
-        <v>0</v>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ182">
-        <v>0</v>
-      </c>
-      <c r="AK182">
-        <v>0</v>
-      </c>
-      <c r="AL182">
-        <v>0</v>
-      </c>
-      <c r="AM182">
-        <v>-1</v>
-      </c>
-      <c r="AN182">
-        <v>-1</v>
-      </c>
-      <c r="AO182">
-        <v>-1</v>
-      </c>
-      <c r="AP182">
-        <v>-1</v>
-      </c>
-      <c r="AQ182">
-        <v>0</v>
-      </c>
-      <c r="AR182">
-        <v>0</v>
-      </c>
-      <c r="AS182">
-        <v>0</v>
-      </c>
-      <c r="AT182">
-        <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
+      <c r="AC185">
+        <v>0</v>
+      </c>
+      <c r="AD185">
+        <v>0</v>
+      </c>
+      <c r="AE185">
+        <v>0</v>
+      </c>
+      <c r="AF185">
+        <v>0</v>
+      </c>
+      <c r="AG185">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>0</v>
+      </c>
+      <c r="AK185">
+        <v>0</v>
+      </c>
+      <c r="AL185">
+        <v>0</v>
+      </c>
+      <c r="AM185">
+        <v>-1</v>
+      </c>
+      <c r="AN185">
+        <v>-1</v>
+      </c>
+      <c r="AO185">
+        <v>-1</v>
+      </c>
+      <c r="AP185">
+        <v>-1</v>
+      </c>
+      <c r="AQ185">
+        <v>0</v>
+      </c>
+      <c r="AR185">
+        <v>0</v>
+      </c>
+      <c r="AS185">
+        <v>0</v>
+      </c>
+      <c r="AT185">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
         <is>
           <t>2026-08-16 23:30:00</t>
         </is>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G95">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G146">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O177">
-        <v>4.42</v>
+        <v>4.14</v>
       </c>
       <c r="P177">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,16 +29199,16 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC177">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD177">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O178">
-        <v>4.14</v>
+        <v>4.42</v>
       </c>
       <c r="P178">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,16 +29362,16 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE178">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q141">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14209,10 +14209,10 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE85">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q90">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22033,10 +22033,10 @@
         <v>0</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE133">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q134">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q70">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G137">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28704,10 +28704,10 @@
         <v>0</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA174">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G5">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>6.42</v>
+        <v>2.15</v>
       </c>
       <c r="O133">
-        <v>5.05</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>1.39</v>
+        <v>2.95</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22033,10 +22033,10 @@
         <v>0</v>
       </c>
       <c r="AC133">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.15</v>
+        <v>6.42</v>
       </c>
       <c r="O134">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="P134">
-        <v>2.95</v>
+        <v>1.39</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22196,10 +22196,10 @@
         <v>0</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE134">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G143">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G146">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC184">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22">

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G172">

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU185"/>
+  <dimension ref="A1:AU188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.09</v>
+        <v>2.91</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P84">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.91</v>
+        <v>2.09</v>
       </c>
       <c r="O85">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14209,10 +14209,10 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD85">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16980,10 +16980,10 @@
         <v>0</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O158">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P158">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26342,12 +26342,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB160">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O162">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P162">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26994,27 +26994,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G166">
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-16 18:00:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-16 18:15:00</t>
+          <t>2026-08-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="O169">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P169">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB169">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:15:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="O170">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P170">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB170">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:15:00</t>
         </is>
       </c>
     </row>
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28704,10 +28704,10 @@
         <v>0</v>
       </c>
       <c r="Y174">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z174">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA174">
         <v>0</v>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G175">
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29030,10 +29030,10 @@
         <v>0</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O177">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P177">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="O178">
-        <v>4.42</v>
+        <v>2.67</v>
       </c>
       <c r="P178">
-        <v>4.68</v>
+        <v>4</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29356,10 +29356,10 @@
         <v>0</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA178">
         <v>0</v>
@@ -29368,10 +29368,10 @@
         <v>0</v>
       </c>
       <c r="AC178">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD178">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE178">
         <v>0</v>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="O179">
-        <v>3.27</v>
+        <v>4.14</v>
       </c>
       <c r="P179">
-        <v>3.21</v>
+        <v>4.78</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,11 +29525,11 @@
         <v>0</v>
       </c>
       <c r="AA179">
+        <v>1.6</v>
+      </c>
+      <c r="AB179">
         <v>2.15</v>
       </c>
-      <c r="AB179">
-        <v>1.61</v>
-      </c>
       <c r="AC179">
         <v>0</v>
       </c>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-16 19:30:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="O180">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="P180">
-        <v>5.44</v>
+        <v>4.68</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29694,10 +29694,10 @@
         <v>0</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE180">
         <v>0</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-16 20:00:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.65</v>
+        <v>1.47</v>
       </c>
       <c r="O182">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="P182">
-        <v>2.6</v>
+        <v>5.44</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O183">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P183">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB183">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-16 21:30:00</t>
+          <t>2026-08-16 20:30:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB184">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-16 22:00:00</t>
+          <t>2026-08-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -30417,156 +30417,645 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>SD Aucas</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N185">
+        <v>2.65</v>
+      </c>
+      <c r="O185">
+        <v>2.9</v>
+      </c>
+      <c r="P185">
+        <v>2.6</v>
+      </c>
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+      <c r="S185">
+        <v>0</v>
+      </c>
+      <c r="T185">
+        <v>0</v>
+      </c>
+      <c r="U185">
+        <v>0</v>
+      </c>
+      <c r="V185">
+        <v>0</v>
+      </c>
+      <c r="W185">
+        <v>0</v>
+      </c>
+      <c r="X185">
+        <v>0</v>
+      </c>
+      <c r="Y185">
+        <v>0</v>
+      </c>
+      <c r="Z185">
+        <v>0</v>
+      </c>
+      <c r="AA185">
+        <v>0</v>
+      </c>
+      <c r="AB185">
+        <v>0</v>
+      </c>
+      <c r="AC185">
+        <v>0</v>
+      </c>
+      <c r="AD185">
+        <v>0</v>
+      </c>
+      <c r="AE185">
+        <v>0</v>
+      </c>
+      <c r="AF185">
+        <v>0</v>
+      </c>
+      <c r="AG185">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>0</v>
+      </c>
+      <c r="AK185">
+        <v>0</v>
+      </c>
+      <c r="AL185">
+        <v>0</v>
+      </c>
+      <c r="AM185">
+        <v>-1</v>
+      </c>
+      <c r="AN185">
+        <v>-1</v>
+      </c>
+      <c r="AO185">
+        <v>-1</v>
+      </c>
+      <c r="AP185">
+        <v>-1</v>
+      </c>
+      <c r="AQ185">
+        <v>0</v>
+      </c>
+      <c r="AR185">
+        <v>0</v>
+      </c>
+      <c r="AS185">
+        <v>0</v>
+      </c>
+      <c r="AT185">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N186">
+        <v>2.92</v>
+      </c>
+      <c r="O186">
+        <v>3.69</v>
+      </c>
+      <c r="P186">
+        <v>2.39</v>
+      </c>
+      <c r="Q186">
+        <v>0</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+      <c r="S186">
+        <v>0</v>
+      </c>
+      <c r="T186">
+        <v>0</v>
+      </c>
+      <c r="U186">
+        <v>0</v>
+      </c>
+      <c r="V186">
+        <v>0</v>
+      </c>
+      <c r="W186">
+        <v>0</v>
+      </c>
+      <c r="X186">
+        <v>0</v>
+      </c>
+      <c r="Y186">
+        <v>0</v>
+      </c>
+      <c r="Z186">
+        <v>0</v>
+      </c>
+      <c r="AA186">
+        <v>1.53</v>
+      </c>
+      <c r="AB186">
+        <v>2.3</v>
+      </c>
+      <c r="AC186">
+        <v>0</v>
+      </c>
+      <c r="AD186">
+        <v>0</v>
+      </c>
+      <c r="AE186">
+        <v>0</v>
+      </c>
+      <c r="AF186">
+        <v>0</v>
+      </c>
+      <c r="AG186">
+        <v>0</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ186">
+        <v>0</v>
+      </c>
+      <c r="AK186">
+        <v>0</v>
+      </c>
+      <c r="AL186">
+        <v>0</v>
+      </c>
+      <c r="AM186">
+        <v>-1</v>
+      </c>
+      <c r="AN186">
+        <v>-1</v>
+      </c>
+      <c r="AO186">
+        <v>-1</v>
+      </c>
+      <c r="AP186">
+        <v>-1</v>
+      </c>
+      <c r="AQ186">
+        <v>0</v>
+      </c>
+      <c r="AR186">
+        <v>0</v>
+      </c>
+      <c r="AS186">
+        <v>0</v>
+      </c>
+      <c r="AT186">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N187">
+        <v>2.77</v>
+      </c>
+      <c r="O187">
+        <v>3.28</v>
+      </c>
+      <c r="P187">
+        <v>2.3</v>
+      </c>
+      <c r="Q187">
+        <v>0</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+      <c r="S187">
+        <v>0</v>
+      </c>
+      <c r="T187">
+        <v>0</v>
+      </c>
+      <c r="U187">
+        <v>0</v>
+      </c>
+      <c r="V187">
+        <v>0</v>
+      </c>
+      <c r="W187">
+        <v>0</v>
+      </c>
+      <c r="X187">
+        <v>0</v>
+      </c>
+      <c r="Y187">
+        <v>0</v>
+      </c>
+      <c r="Z187">
+        <v>0</v>
+      </c>
+      <c r="AA187">
+        <v>1.84</v>
+      </c>
+      <c r="AB187">
+        <v>1.82</v>
+      </c>
+      <c r="AC187">
+        <v>0</v>
+      </c>
+      <c r="AD187">
+        <v>0</v>
+      </c>
+      <c r="AE187">
+        <v>0</v>
+      </c>
+      <c r="AF187">
+        <v>0</v>
+      </c>
+      <c r="AG187">
+        <v>0</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ187">
+        <v>0</v>
+      </c>
+      <c r="AK187">
+        <v>0</v>
+      </c>
+      <c r="AL187">
+        <v>0</v>
+      </c>
+      <c r="AM187">
+        <v>-1</v>
+      </c>
+      <c r="AN187">
+        <v>-1</v>
+      </c>
+      <c r="AO187">
+        <v>-1</v>
+      </c>
+      <c r="AP187">
+        <v>-1</v>
+      </c>
+      <c r="AQ187">
+        <v>0</v>
+      </c>
+      <c r="AR187">
+        <v>0</v>
+      </c>
+      <c r="AS187">
+        <v>0</v>
+      </c>
+      <c r="AT187">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>2026-08-16 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="G185">
-        <v>0</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
-      </c>
-      <c r="I185">
-        <v>0</v>
-      </c>
-      <c r="J185">
-        <v>0</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="M185" t="inlineStr">
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N185">
+      <c r="N188">
         <v>3.25</v>
       </c>
-      <c r="O185">
+      <c r="O188">
         <v>3.55</v>
       </c>
-      <c r="P185">
+      <c r="P188">
         <v>2</v>
       </c>
-      <c r="Q185">
-        <v>0</v>
-      </c>
-      <c r="R185">
-        <v>0</v>
-      </c>
-      <c r="S185">
-        <v>0</v>
-      </c>
-      <c r="T185">
-        <v>0</v>
-      </c>
-      <c r="U185">
-        <v>0</v>
-      </c>
-      <c r="V185">
-        <v>0</v>
-      </c>
-      <c r="W185">
-        <v>0</v>
-      </c>
-      <c r="X185">
-        <v>0</v>
-      </c>
-      <c r="Y185">
-        <v>0</v>
-      </c>
-      <c r="Z185">
-        <v>0</v>
-      </c>
-      <c r="AA185">
+      <c r="Q188">
+        <v>0</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+      <c r="S188">
+        <v>0</v>
+      </c>
+      <c r="T188">
+        <v>0</v>
+      </c>
+      <c r="U188">
+        <v>0</v>
+      </c>
+      <c r="V188">
+        <v>0</v>
+      </c>
+      <c r="W188">
+        <v>0</v>
+      </c>
+      <c r="X188">
+        <v>0</v>
+      </c>
+      <c r="Y188">
+        <v>0</v>
+      </c>
+      <c r="Z188">
+        <v>0</v>
+      </c>
+      <c r="AA188">
         <v>1.55</v>
       </c>
-      <c r="AB185">
+      <c r="AB188">
         <v>2.3</v>
       </c>
-      <c r="AC185">
-        <v>0</v>
-      </c>
-      <c r="AD185">
-        <v>0</v>
-      </c>
-      <c r="AE185">
-        <v>0</v>
-      </c>
-      <c r="AF185">
-        <v>0</v>
-      </c>
-      <c r="AG185">
-        <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ185">
-        <v>0</v>
-      </c>
-      <c r="AK185">
-        <v>0</v>
-      </c>
-      <c r="AL185">
-        <v>0</v>
-      </c>
-      <c r="AM185">
-        <v>-1</v>
-      </c>
-      <c r="AN185">
-        <v>-1</v>
-      </c>
-      <c r="AO185">
-        <v>-1</v>
-      </c>
-      <c r="AP185">
-        <v>-1</v>
-      </c>
-      <c r="AQ185">
-        <v>0</v>
-      </c>
-      <c r="AR185">
-        <v>0</v>
-      </c>
-      <c r="AS185">
-        <v>0</v>
-      </c>
-      <c r="AT185">
-        <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
+      <c r="AC188">
+        <v>0</v>
+      </c>
+      <c r="AD188">
+        <v>0</v>
+      </c>
+      <c r="AE188">
+        <v>0</v>
+      </c>
+      <c r="AF188">
+        <v>0</v>
+      </c>
+      <c r="AG188">
+        <v>0</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ188">
+        <v>0</v>
+      </c>
+      <c r="AK188">
+        <v>0</v>
+      </c>
+      <c r="AL188">
+        <v>0</v>
+      </c>
+      <c r="AM188">
+        <v>-1</v>
+      </c>
+      <c r="AN188">
+        <v>-1</v>
+      </c>
+      <c r="AO188">
+        <v>-1</v>
+      </c>
+      <c r="AP188">
+        <v>-1</v>
+      </c>
+      <c r="AQ188">
+        <v>0</v>
+      </c>
+      <c r="AR188">
+        <v>0</v>
+      </c>
+      <c r="AS188">
+        <v>0</v>
+      </c>
+      <c r="AT188">
+        <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
         <is>
           <t>2026-08-16 23:30:00</t>
         </is>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.66</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
-        <v>3.68</v>
+        <v>3.22</v>
       </c>
       <c r="P13">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB13">
         <v>1.77</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="O14">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>2.58</v>
+        <v>3.52</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.08</v>
+        <v>4.66</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P15">
-        <v>3.52</v>
+        <v>1.72</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="O31">
-        <v>4.85</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>6.59</v>
+        <v>4.09</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.84</v>
+        <v>1.41</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>4.85</v>
       </c>
       <c r="P32">
-        <v>2.4</v>
+        <v>6.59</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="O33">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>4.09</v>
+        <v>2.4</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P34">
-        <v>5.46</v>
+        <v>5.11</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="O35">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P35">
-        <v>5.11</v>
+        <v>5.46</v>
       </c>
       <c r="Q35">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC124">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21532,10 +21532,10 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA130">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q168">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU188"/>
+  <dimension ref="A1:AU190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,34 +644,34 @@
         <v>4.1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA2">
         <v>1.98</v>
@@ -680,19 +680,19 @@
         <v>1.79</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="O75">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="P75">
-        <v>3.07</v>
+        <v>4.2</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="O76">
-        <v>4.44</v>
+        <v>3.58</v>
       </c>
       <c r="P76">
-        <v>5.58</v>
+        <v>3.07</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12818,22 +12818,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.31</v>
+        <v>2.84</v>
       </c>
       <c r="O79">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="P79">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.36</v>
+        <v>3.31</v>
       </c>
       <c r="O80">
-        <v>3.94</v>
+        <v>3.32</v>
       </c>
       <c r="P80">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.88</v>
+        <v>4.36</v>
       </c>
       <c r="O81">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="P81">
-        <v>3.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G82">
@@ -13678,10 +13678,10 @@
         <v>1.88</v>
       </c>
       <c r="O82">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="P82">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="O83">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P83">
-        <v>2.82</v>
+        <v>3.44</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="O84">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P84">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.09</v>
+        <v>2.91</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P85">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14209,10 +14209,10 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>3</v>
+        <v>2.09</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P86">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="O87">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-16 12:30:00</t>
+          <t>2026-08-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>2.47</v>
+        <v>2.94</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,17 +15138,17 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G95">
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-16 12:45:00</t>
+          <t>2026-08-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-16 13:00:00</t>
+          <t>2026-08-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16980,10 +16980,10 @@
         <v>0</v>
       </c>
       <c r="AC102">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE102">
         <v>0</v>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17306,10 +17306,10 @@
         <v>0</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.33</v>
+        <v>3.59</v>
       </c>
       <c r="O107">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>9.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-16 13:15:00</t>
+          <t>2026-08-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G109">
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-16 13:30:00</t>
+          <t>2026-08-16 13:15:00</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.47</v>
+        <v>3.78</v>
       </c>
       <c r="O116">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P116">
-        <v>2.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-16 14:00:00</t>
+          <t>2026-08-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.09</v>
+        <v>3.32</v>
       </c>
       <c r="O120">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P120">
-        <v>3.62</v>
+        <v>2.16</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="O121">
-        <v>3.93</v>
+        <v>3.44</v>
       </c>
       <c r="P121">
-        <v>5.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="O123">
-        <v>3.28</v>
+        <v>3.93</v>
       </c>
       <c r="P123">
-        <v>3.29</v>
+        <v>5.55</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="O125">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="P125">
-        <v>3.89</v>
+        <v>3.29</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-16 14:15:00</t>
+          <t>2026-08-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="O126">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P126">
-        <v>2.47</v>
+        <v>3.37</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-16 14:15:00</t>
+          <t>2026-08-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-16 14:30:00</t>
+          <t>2026-08-16 14:15:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-16 14:30:00</t>
+          <t>2026-08-16 14:15:00</t>
         </is>
       </c>
     </row>
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G129">
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21532,10 +21532,10 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z130">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-16 15:00:00</t>
+          <t>2026-08-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,27 +21615,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G131">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-16 15:00:00</t>
+          <t>2026-08-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="O132">
-        <v>5.4</v>
+        <v>2.69</v>
       </c>
       <c r="P132">
-        <v>5.42</v>
+        <v>4.21</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21858,10 +21858,10 @@
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA132">
         <v>0</v>
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>6.42</v>
+        <v>1.42</v>
       </c>
       <c r="O134">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="P134">
-        <v>1.39</v>
+        <v>5.42</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22196,10 +22196,10 @@
         <v>0</v>
       </c>
       <c r="AC134">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD134">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE134">
         <v>0</v>
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G137">
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O138">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P138">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-16 15:15:00</t>
+          <t>2026-08-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O139">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-16 15:15:00</t>
+          <t>2026-08-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="O141">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>5</v>
+        <v>3.46</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-16 15:30:00</t>
+          <t>2026-08-16 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-16 15:30:00</t>
+          <t>2026-08-16 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O144">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P144">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24386,27 +24386,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-16 16:00:00</t>
+          <t>2026-08-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24549,27 +24549,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.99</v>
+        <v>3.48</v>
       </c>
       <c r="O149">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P149">
-        <v>3.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB149">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-16 16:00:00</t>
+          <t>2026-08-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O150">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P150">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB150">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O155">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P155">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O156">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P156">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="O157">
-        <v>3.76</v>
+        <v>4.05</v>
       </c>
       <c r="P157">
-        <v>7.7</v>
+        <v>5.27</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="O159">
-        <v>3.25</v>
+        <v>3.76</v>
       </c>
       <c r="P159">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G160">
@@ -26505,27 +26505,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="O161">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="P161">
-        <v>5.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB161">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-16 16:30:00</t>
+          <t>2026-08-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="O163">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P163">
-        <v>4.74</v>
+        <v>5.09</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G164">
@@ -27157,27 +27157,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.17</v>
+        <v>1.8</v>
       </c>
       <c r="O165">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="P165">
-        <v>2.46</v>
+        <v>4.74</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -27320,27 +27320,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O166">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P166">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-16 17:00:00</t>
+          <t>2026-08-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="O168">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="P168">
-        <v>4.4</v>
+        <v>3.56</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-16 18:00:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G169">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-16 18:15:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,10 +28019,10 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O170">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P170">
         <v>4.4</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-16 18:15:00</t>
+          <t>2026-08-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="O171">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P171">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB171">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:15:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="O172">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P172">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB172">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-16 18:30:00</t>
+          <t>2026-08-16 18:15:00</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O176">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29030,10 +29030,10 @@
         <v>0</v>
       </c>
       <c r="Y176">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z176">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA176">
         <v>0</v>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G177">
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="O178">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="P178">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29356,10 +29356,10 @@
         <v>0</v>
       </c>
       <c r="Y178">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="Z178">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="AA178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-16 19:00:00</t>
+          <t>2026-08-16 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="O180">
-        <v>4.42</v>
+        <v>2.67</v>
       </c>
       <c r="P180">
-        <v>4.68</v>
+        <v>4</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29682,10 +29682,10 @@
         <v>0</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA180">
         <v>0</v>
@@ -29694,10 +29694,10 @@
         <v>0</v>
       </c>
       <c r="AC180">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD180">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE180">
         <v>0</v>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="O181">
-        <v>3.27</v>
+        <v>4.14</v>
       </c>
       <c r="P181">
-        <v>3.21</v>
+        <v>4.78</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,11 +29851,11 @@
         <v>0</v>
       </c>
       <c r="AA181">
+        <v>1.6</v>
+      </c>
+      <c r="AB181">
         <v>2.15</v>
       </c>
-      <c r="AB181">
-        <v>1.61</v>
-      </c>
       <c r="AC181">
         <v>0</v>
       </c>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-16 19:30:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="O182">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="P182">
-        <v>5.44</v>
+        <v>4.68</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE182">
         <v>0</v>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-16 20:00:00</t>
+          <t>2026-08-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-16 20:30:00</t>
+          <t>2026-08-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-16 21:00:00</t>
+          <t>2026-08-16 20:30:00</t>
         </is>
       </c>
     </row>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-08-16 21:30:00</t>
+          <t>2026-08-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O187">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="P187">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB187">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-16 22:00:00</t>
+          <t>2026-08-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="O188">
-        <v>3.55</v>
+        <v>3.69</v>
       </c>
       <c r="P188">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,7 +30992,7 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB188">
         <v>2.3</v>
@@ -31056,6 +31056,332 @@
         <v>0</v>
       </c>
       <c r="AU188" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N189">
+        <v>2.77</v>
+      </c>
+      <c r="O189">
+        <v>3.28</v>
+      </c>
+      <c r="P189">
+        <v>2.3</v>
+      </c>
+      <c r="Q189">
+        <v>0</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
+      </c>
+      <c r="S189">
+        <v>0</v>
+      </c>
+      <c r="T189">
+        <v>0</v>
+      </c>
+      <c r="U189">
+        <v>0</v>
+      </c>
+      <c r="V189">
+        <v>0</v>
+      </c>
+      <c r="W189">
+        <v>0</v>
+      </c>
+      <c r="X189">
+        <v>0</v>
+      </c>
+      <c r="Y189">
+        <v>0</v>
+      </c>
+      <c r="Z189">
+        <v>0</v>
+      </c>
+      <c r="AA189">
+        <v>1.84</v>
+      </c>
+      <c r="AB189">
+        <v>1.82</v>
+      </c>
+      <c r="AC189">
+        <v>0</v>
+      </c>
+      <c r="AD189">
+        <v>0</v>
+      </c>
+      <c r="AE189">
+        <v>0</v>
+      </c>
+      <c r="AF189">
+        <v>0</v>
+      </c>
+      <c r="AG189">
+        <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
+        <v>0</v>
+      </c>
+      <c r="AK189">
+        <v>0</v>
+      </c>
+      <c r="AL189">
+        <v>0</v>
+      </c>
+      <c r="AM189">
+        <v>-1</v>
+      </c>
+      <c r="AN189">
+        <v>-1</v>
+      </c>
+      <c r="AO189">
+        <v>-1</v>
+      </c>
+      <c r="AP189">
+        <v>-1</v>
+      </c>
+      <c r="AQ189">
+        <v>0</v>
+      </c>
+      <c r="AR189">
+        <v>0</v>
+      </c>
+      <c r="AS189">
+        <v>0</v>
+      </c>
+      <c r="AT189">
+        <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>2026-08-16 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N190">
+        <v>3.25</v>
+      </c>
+      <c r="O190">
+        <v>3.55</v>
+      </c>
+      <c r="P190">
+        <v>2</v>
+      </c>
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+      <c r="S190">
+        <v>0</v>
+      </c>
+      <c r="T190">
+        <v>0</v>
+      </c>
+      <c r="U190">
+        <v>0</v>
+      </c>
+      <c r="V190">
+        <v>0</v>
+      </c>
+      <c r="W190">
+        <v>0</v>
+      </c>
+      <c r="X190">
+        <v>0</v>
+      </c>
+      <c r="Y190">
+        <v>0</v>
+      </c>
+      <c r="Z190">
+        <v>0</v>
+      </c>
+      <c r="AA190">
+        <v>1.55</v>
+      </c>
+      <c r="AB190">
+        <v>2.3</v>
+      </c>
+      <c r="AC190">
+        <v>0</v>
+      </c>
+      <c r="AD190">
+        <v>0</v>
+      </c>
+      <c r="AE190">
+        <v>0</v>
+      </c>
+      <c r="AF190">
+        <v>0</v>
+      </c>
+      <c r="AG190">
+        <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
+        <v>0</v>
+      </c>
+      <c r="AK190">
+        <v>0</v>
+      </c>
+      <c r="AL190">
+        <v>0</v>
+      </c>
+      <c r="AM190">
+        <v>-1</v>
+      </c>
+      <c r="AN190">
+        <v>-1</v>
+      </c>
+      <c r="AO190">
+        <v>-1</v>
+      </c>
+      <c r="AP190">
+        <v>-1</v>
+      </c>
+      <c r="AQ190">
+        <v>0</v>
+      </c>
+      <c r="AR190">
+        <v>0</v>
+      </c>
+      <c r="AS190">
+        <v>0</v>
+      </c>
+      <c r="AT190">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
         <is>
           <t>2026-08-16 23:30:00</t>
         </is>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="O75">
-        <v>3.99</v>
+        <v>3.58</v>
       </c>
       <c r="P75">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="O76">
-        <v>3.58</v>
+        <v>4.44</v>
       </c>
       <c r="P76">
-        <v>3.07</v>
+        <v>5.58</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="O77">
-        <v>4.44</v>
+        <v>3.99</v>
       </c>
       <c r="P77">
-        <v>5.58</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,17 +15138,17 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N91">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,17 +15301,17 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q92">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G68">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.32</v>
+        <v>7.65</v>
       </c>
       <c r="O103">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="P103">
-        <v>7.37</v>
+        <v>1.3</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17143,10 +17143,10 @@
         <v>0</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>7.65</v>
+        <v>1.32</v>
       </c>
       <c r="O104">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="P104">
-        <v>1.3</v>
+        <v>7.37</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17306,10 +17306,10 @@
         <v>0</v>
       </c>
       <c r="AC104">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE104">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -1459,55 +1459,55 @@
         <v>2.94</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>2.65</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
         <v>1.96</v>
@@ -1984,19 +1984,19 @@
         <v>1.74</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.38</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
         <v>1.55</v>
@@ -2310,19 +2310,19 @@
         <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>4.32</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16">
         <v>1.79</v>
@@ -2962,19 +2962,19 @@
         <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>3.3</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>8.6</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>3.06</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
         <v>1.53</v>
@@ -4266,19 +4266,19 @@
         <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,40 +4393,40 @@
         <v>3.78</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
         <v>2.25</v>
@@ -4435,13 +4435,13 @@
         <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,34 +4556,34 @@
         <v>2.37</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA26">
         <v>1.53</v>
@@ -4592,19 +4592,19 @@
         <v>2.3</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>6.61</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>5.11</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>5.46</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.39</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>2.08</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA39">
         <v>1.73</v>
@@ -6711,19 +6711,19 @@
         <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>9.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>6.95</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>2.47</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>1.67</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>6.64</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>3.12</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>1.65</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>1.93</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10750,34 +10750,34 @@
         <v>2.82</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA64">
         <v>1.8</v>
@@ -10786,19 +10786,19 @@
         <v>1.92</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>5.11</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11891,55 +11891,55 @@
         <v>3.05</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>4.74</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,34 +13195,34 @@
         <v>2.37</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA79">
         <v>1.72</v>
@@ -13231,19 +13231,19 @@
         <v>1.98</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>2.16</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>1.71</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>3.64</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="O83">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="P83">
-        <v>3.44</v>
+        <v>2.82</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC83">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AD83">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="O84">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="P84">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.91</v>
+        <v>2.09</v>
       </c>
       <c r="O85">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AC85">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD85">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="O86">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P86">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>2.39</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>2.66</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>2.94</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>2.47</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>2.3</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,34 +15803,34 @@
         <v>3.23</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA95">
         <v>1.98</v>
@@ -15839,19 +15839,19 @@
         <v>1.83</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>2.45</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16153,31 +16153,31 @@
         <v>0</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE97">
         <v>0</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -17107,40 +17107,40 @@
         <v>1.3</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC103">
         <v>1.93</v>
@@ -17149,13 +17149,13 @@
         <v>1.88</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>7.37</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>1.94</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17922,55 +17922,55 @@
         <v>9.6</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>2.13</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>3.65</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.68</v>
+        <v>4.66</v>
       </c>
       <c r="O13">
-        <v>3.22</v>
+        <v>3.68</v>
       </c>
       <c r="P13">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
         <v>1.77</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>3.52</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.66</v>
+        <v>2.68</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>3.22</v>
       </c>
       <c r="P15">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB15">
         <v>1.77</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="O16">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="R16">
+        <v>2.48</v>
+      </c>
+      <c r="S16">
+        <v>1.26</v>
+      </c>
+      <c r="T16">
+        <v>3.32</v>
+      </c>
+      <c r="U16">
         <v>2.25</v>
       </c>
-      <c r="S16">
-        <v>1.36</v>
-      </c>
-      <c r="T16">
-        <v>2.88</v>
-      </c>
-      <c r="U16">
-        <v>2.88</v>
-      </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.2</v>
+        <v>4.74</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AC16">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD16">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>3.09</v>
+      </c>
+      <c r="O17">
+        <v>3.04</v>
+      </c>
+      <c r="P17">
+        <v>2.24</v>
+      </c>
+      <c r="Q17">
+        <v>4.32</v>
+      </c>
+      <c r="R17">
         <v>1.93</v>
       </c>
-      <c r="O17">
-        <v>3.6</v>
-      </c>
-      <c r="P17">
-        <v>3.3</v>
-      </c>
-      <c r="Q17">
-        <v>2.33</v>
-      </c>
-      <c r="R17">
-        <v>2.48</v>
-      </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="T17">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="U17">
+        <v>3.18</v>
+      </c>
+      <c r="V17">
+        <v>1.28</v>
+      </c>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1.03</v>
+      </c>
+      <c r="Y17">
+        <v>1.36</v>
+      </c>
+      <c r="Z17">
+        <v>2.7</v>
+      </c>
+      <c r="AA17">
         <v>2.25</v>
       </c>
-      <c r="V17">
-        <v>1.53</v>
-      </c>
-      <c r="W17">
-        <v>1.11</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
+      <c r="AB17">
+        <v>1.61</v>
+      </c>
+      <c r="AC17">
+        <v>3.98</v>
+      </c>
+      <c r="AD17">
         <v>1.17</v>
       </c>
-      <c r="Z17">
-        <v>4.74</v>
-      </c>
-      <c r="AA17">
-        <v>1.56</v>
-      </c>
-      <c r="AB17">
-        <v>2.27</v>
-      </c>
-      <c r="AC17">
-        <v>2.35</v>
-      </c>
-      <c r="AD17">
-        <v>1.47</v>
-      </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="O18">
-        <v>4.8</v>
+        <v>3.68</v>
       </c>
       <c r="P18">
-        <v>8.6</v>
+        <v>4.32</v>
       </c>
       <c r="Q18">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>4.87</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AB18">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.09</v>
+        <v>1.29</v>
       </c>
       <c r="O19">
-        <v>3.04</v>
+        <v>4.8</v>
       </c>
       <c r="P19">
-        <v>2.24</v>
+        <v>8.6</v>
       </c>
       <c r="Q19">
-        <v>4.32</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="S19">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
-        <v>3.18</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
+        <v>1.12</v>
+      </c>
+      <c r="X19">
         <v>1.01</v>
       </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>4.87</v>
       </c>
       <c r="AA19">
+        <v>1.49</v>
+      </c>
+      <c r="AB19">
+        <v>2.43</v>
+      </c>
+      <c r="AC19">
         <v>2.25</v>
       </c>
-      <c r="AB19">
-        <v>1.61</v>
-      </c>
-      <c r="AC19">
-        <v>3.98</v>
-      </c>
       <c r="AD19">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="P31">
-        <v>4.09</v>
+        <v>6.59</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.41</v>
+        <v>2.84</v>
       </c>
       <c r="O32">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>6.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="P33">
-        <v>2.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AB33">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6512,40 +6512,40 @@
         <v>2.51</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC38">
         <v>1.97</v>
@@ -6554,13 +6554,13 @@
         <v>1.78</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>2.29</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -7840,31 +7840,31 @@
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>1.78</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.13</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>3.07</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>5.58</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,65 +13349,65 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.31</v>
+        <v>4.36</v>
       </c>
       <c r="O80">
-        <v>3.32</v>
+        <v>3.94</v>
       </c>
       <c r="P80">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="Q80">
-        <v>4.12</v>
+        <v>4.55</v>
       </c>
       <c r="R80">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T80">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="U80">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="V80">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="W80">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z80">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="AA80">
+        <v>1.58</v>
+      </c>
+      <c r="AB80">
+        <v>2.3</v>
+      </c>
+      <c r="AC80">
+        <v>2.32</v>
+      </c>
+      <c r="AD80">
+        <v>1.49</v>
+      </c>
+      <c r="AE80">
+        <v>1.2</v>
+      </c>
+      <c r="AF80">
+        <v>1.7</v>
+      </c>
+      <c r="AG80">
         <v>2</v>
       </c>
-      <c r="AB80">
-        <v>1.76</v>
-      </c>
-      <c r="AC80">
-        <v>3.55</v>
-      </c>
-      <c r="AD80">
-        <v>1.28</v>
-      </c>
-      <c r="AE80">
-        <v>1.09</v>
-      </c>
-      <c r="AF80">
-        <v>1.75</v>
-      </c>
-      <c r="AG80">
-        <v>1.95</v>
-      </c>
       <c r="AH80" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK80">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>4.36</v>
+        <v>3.31</v>
       </c>
       <c r="O81">
-        <v>3.94</v>
+        <v>3.32</v>
       </c>
       <c r="P81">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="Q81">
-        <v>4.55</v>
+        <v>4.12</v>
       </c>
       <c r="R81">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="U81">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="V81">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA81">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AB81">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC81">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="AD81">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF81">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AK81">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,68 +15138,68 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N91">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>3.19</v>
+        <v>2.47</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="U91">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z91">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA91">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="AD91">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK91">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,84 +15301,84 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
-        <v>2.47</v>
+        <v>3.19</v>
       </c>
       <c r="Q92">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T92">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="U92">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="V92">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="W92">
+        <v>1.15</v>
+      </c>
+      <c r="X92">
         <v>1.03</v>
       </c>
-      <c r="X92">
-        <v>1.06</v>
-      </c>
       <c r="Y92">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA92">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AB92">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="AC92">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="AD92">
+        <v>1.44</v>
+      </c>
+      <c r="AE92">
+        <v>1.14</v>
+      </c>
+      <c r="AF92">
+        <v>1.53</v>
+      </c>
+      <c r="AG92">
+        <v>2.4</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.25</v>
       </c>
-      <c r="AE92">
-        <v>1.04</v>
-      </c>
-      <c r="AF92">
-        <v>1.75</v>
-      </c>
-      <c r="AG92">
-        <v>1.94</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.35</v>
-      </c>
       <c r="AK92">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -21019,55 +21019,55 @@
         <v>3.89</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21834,28 +21834,28 @@
         <v>4.21</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y132">
         <v>1.71</v>
@@ -21864,25 +21864,25 @@
         <v>1.98</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22160,55 +22160,55 @@
         <v>5.42</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X134">
         <v>0</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>2.95</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22486,40 +22486,40 @@
         <v>1.39</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC136">
         <v>1.93</v>
@@ -22528,13 +22528,13 @@
         <v>1.83</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -24116,55 +24116,55 @@
         <v>5.35</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G148">

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.66</v>
+        <v>2.08</v>
       </c>
       <c r="O13">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>1.72</v>
+        <v>3.52</v>
       </c>
       <c r="Q13">
-        <v>5.21</v>
+        <v>2.54</v>
       </c>
       <c r="R13">
         <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U13">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA13">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD13">
         <v>1.24</v>
       </c>
       <c r="AE13">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
+        <v>1.83</v>
+      </c>
+      <c r="AG13">
         <v>1.85</v>
       </c>
-      <c r="AG13">
-        <v>1.8</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK13">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.08</v>
+        <v>4.66</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P14">
-        <v>3.52</v>
+        <v>1.72</v>
       </c>
       <c r="Q14">
-        <v>2.54</v>
+        <v>5.21</v>
       </c>
       <c r="R14">
         <v>2.08</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U14">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA14">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB14">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC14">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD14">
         <v>1.24</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>3.09</v>
+      </c>
+      <c r="O16">
+        <v>3.04</v>
+      </c>
+      <c r="P16">
+        <v>2.24</v>
+      </c>
+      <c r="Q16">
+        <v>4.32</v>
+      </c>
+      <c r="R16">
         <v>1.93</v>
       </c>
-      <c r="O16">
-        <v>3.6</v>
-      </c>
-      <c r="P16">
-        <v>3.3</v>
-      </c>
-      <c r="Q16">
-        <v>2.33</v>
-      </c>
-      <c r="R16">
-        <v>2.48</v>
-      </c>
       <c r="S16">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="T16">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="U16">
+        <v>3.18</v>
+      </c>
+      <c r="V16">
+        <v>1.28</v>
+      </c>
+      <c r="W16">
+        <v>1.01</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.36</v>
+      </c>
+      <c r="Z16">
+        <v>2.7</v>
+      </c>
+      <c r="AA16">
         <v>2.25</v>
       </c>
-      <c r="V16">
-        <v>1.53</v>
-      </c>
-      <c r="W16">
-        <v>1.11</v>
-      </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
+      <c r="AB16">
+        <v>1.61</v>
+      </c>
+      <c r="AC16">
+        <v>3.98</v>
+      </c>
+      <c r="AD16">
         <v>1.17</v>
       </c>
-      <c r="Z16">
-        <v>4.74</v>
-      </c>
-      <c r="AA16">
-        <v>1.56</v>
-      </c>
-      <c r="AB16">
-        <v>2.27</v>
-      </c>
-      <c r="AC16">
-        <v>2.35</v>
-      </c>
-      <c r="AD16">
-        <v>1.47</v>
-      </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG16">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.09</v>
+        <v>1.68</v>
       </c>
       <c r="O17">
-        <v>3.04</v>
+        <v>3.68</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>4.32</v>
       </c>
       <c r="Q17">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="R17">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
         <v>1.01</v>
       </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AB17">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>3.98</v>
+        <v>3.14</v>
       </c>
       <c r="AD17">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
+        <v>1.8</v>
+      </c>
+      <c r="AG17">
         <v>1.91</v>
       </c>
-      <c r="AG17">
-        <v>1.78</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="O18">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="P18">
-        <v>4.32</v>
+        <v>8.6</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>4.87</v>
       </c>
       <c r="AA18">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AC18">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="O19">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="R19">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T19">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,28 +3442,28 @@
         <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>4.87</v>
+        <v>4.74</v>
       </c>
       <c r="AA19">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AB19">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE19">
         <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>3.78</v>
+        <v>2.37</v>
       </c>
       <c r="Q25">
+        <v>3.06</v>
+      </c>
+      <c r="R25">
         <v>2.3</v>
       </c>
-      <c r="R25">
-        <v>2.4</v>
-      </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
+        <v>2.41</v>
+      </c>
+      <c r="V25">
+        <v>1.5</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.17</v>
+      </c>
+      <c r="Z25">
+        <v>4.05</v>
+      </c>
+      <c r="AA25">
+        <v>1.53</v>
+      </c>
+      <c r="AB25">
         <v>2.3</v>
       </c>
-      <c r="V25">
-        <v>1.57</v>
-      </c>
-      <c r="W25">
-        <v>1.15</v>
-      </c>
-      <c r="X25">
-        <v>1.02</v>
-      </c>
-      <c r="Y25">
-        <v>1.13</v>
-      </c>
-      <c r="Z25">
-        <v>4.55</v>
-      </c>
-      <c r="AA25">
-        <v>1.57</v>
-      </c>
-      <c r="AB25">
-        <v>2.35</v>
-      </c>
       <c r="AC25">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AD25">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>2.37</v>
+        <v>3.78</v>
       </c>
       <c r="Q26">
-        <v>3.06</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
+        <v>2.4</v>
+      </c>
+      <c r="S26">
+        <v>1.25</v>
+      </c>
+      <c r="T26">
+        <v>3.34</v>
+      </c>
+      <c r="U26">
         <v>2.3</v>
       </c>
-      <c r="S26">
-        <v>1.28</v>
-      </c>
-      <c r="T26">
-        <v>3.3</v>
-      </c>
-      <c r="U26">
-        <v>2.41</v>
-      </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
+        <v>1.13</v>
+      </c>
+      <c r="Z26">
+        <v>4.55</v>
+      </c>
+      <c r="AA26">
+        <v>1.57</v>
+      </c>
+      <c r="AB26">
+        <v>2.35</v>
+      </c>
+      <c r="AC26">
+        <v>2.25</v>
+      </c>
+      <c r="AD26">
+        <v>1.57</v>
+      </c>
+      <c r="AE26">
         <v>1.17</v>
       </c>
-      <c r="Z26">
-        <v>4.05</v>
-      </c>
-      <c r="AA26">
-        <v>1.53</v>
-      </c>
-      <c r="AB26">
-        <v>2.3</v>
-      </c>
-      <c r="AC26">
-        <v>2.54</v>
-      </c>
-      <c r="AD26">
-        <v>1.41</v>
-      </c>
-      <c r="AE26">
-        <v>1.14</v>
-      </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.11</v>
+      </c>
+      <c r="O4">
+        <v>3.55</v>
+      </c>
+      <c r="P4">
+        <v>2.8</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
         <v>1.57</v>
       </c>
-      <c r="O4">
-        <v>3.9</v>
-      </c>
-      <c r="P4">
-        <v>4.45</v>
-      </c>
-      <c r="Q4">
-        <v>2.11</v>
-      </c>
-      <c r="R4">
-        <v>2.27</v>
-      </c>
-      <c r="S4">
-        <v>1.29</v>
-      </c>
-      <c r="T4">
-        <v>3.08</v>
-      </c>
-      <c r="U4">
-        <v>2.51</v>
-      </c>
-      <c r="V4">
-        <v>1.47</v>
-      </c>
-      <c r="W4">
-        <v>1.11</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.18</v>
-      </c>
-      <c r="Z4">
-        <v>3.84</v>
-      </c>
-      <c r="AA4">
-        <v>1.65</v>
-      </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.57</v>
+      </c>
+      <c r="O5">
+        <v>3.9</v>
+      </c>
+      <c r="P5">
+        <v>4.45</v>
+      </c>
+      <c r="Q5">
         <v>2.11</v>
       </c>
-      <c r="O5">
-        <v>3.55</v>
-      </c>
-      <c r="P5">
-        <v>2.8</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,43 +2428,43 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="O13">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
-        <v>3.2</v>
+        <v>5.21</v>
       </c>
       <c r="R13">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
         <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1</v>
       </c>
       <c r="Y13">
         <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="AA13">
         <v>1.99</v>
@@ -2473,19 +2473,19 @@
         <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD13">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,65 +2591,65 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.05</v>
+        <v>2.01</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
       <c r="P14">
-        <v>1.78</v>
+        <v>3.12</v>
       </c>
       <c r="Q14">
-        <v>5.21</v>
+        <v>2.71</v>
       </c>
       <c r="R14">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AD14">
         <v>1.24</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
+        <v>1.83</v>
+      </c>
+      <c r="AG14">
         <v>1.85</v>
       </c>
-      <c r="AG14">
-        <v>1.83</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
         <v>3.27</v>
       </c>
       <c r="P15">
-        <v>3.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="R15">
         <v>2.01</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U15">
         <v>2.88</v>
@@ -2781,37 +2781,37 @@
         <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z15">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
         <v>3.35</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4061,61 +4061,61 @@
         <v>1.6</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="S23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
         <v>4</v>
       </c>
       <c r="U23">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="V23">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W23">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z23">
-        <v>5.98</v>
+        <v>5.89</v>
       </c>
       <c r="AA23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB23">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC23">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD23">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF23">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S24">
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB24">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC24">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
         <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG24">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.72</v>
+      </c>
+      <c r="O25">
+        <v>3.9</v>
+      </c>
+      <c r="P25">
+        <v>4.15</v>
+      </c>
+      <c r="Q25">
+        <v>2.2</v>
+      </c>
+      <c r="R25">
         <v>2.4</v>
-      </c>
-      <c r="O25">
-        <v>3.6</v>
-      </c>
-      <c r="P25">
-        <v>2.58</v>
-      </c>
-      <c r="Q25">
-        <v>2.8</v>
-      </c>
-      <c r="R25">
-        <v>2.21</v>
       </c>
       <c r="S25">
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>4.92</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD25">
         <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>3.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q31">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="U31">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="Z31">
-        <v>4.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA31">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="AB31">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AK31">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.37</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V33">
+        <v>1.57</v>
+      </c>
+      <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.12</v>
+      </c>
+      <c r="Z33">
+        <v>4.7</v>
+      </c>
+      <c r="AA33">
+        <v>1.51</v>
+      </c>
+      <c r="AB33">
+        <v>2.27</v>
+      </c>
+      <c r="AC33">
+        <v>2.42</v>
+      </c>
+      <c r="AD33">
         <v>1.44</v>
       </c>
-      <c r="W33">
-        <v>1.06</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.26</v>
-      </c>
-      <c r="Z33">
-        <v>3.44</v>
-      </c>
-      <c r="AA33">
-        <v>1.86</v>
-      </c>
-      <c r="AB33">
-        <v>1.94</v>
-      </c>
-      <c r="AC33">
-        <v>2.94</v>
-      </c>
-      <c r="AD33">
-        <v>1.31</v>
-      </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="P34">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="V34">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>2.95</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>1.94</v>
       </c>
       <c r="AD34">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AF34">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="Q35">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="V35">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>2.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC35">
-        <v>1.94</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>2.39</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.35</v>
@@ -6198,7 +6198,7 @@
         <v>3</v>
       </c>
       <c r="U36">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
         <v>1.45</v>
@@ -6210,28 +6210,28 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
         <v>1.93</v>
       </c>
       <c r="AB36">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD36">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AK36">
         <v>1.41</v>
@@ -7979,13 +7979,13 @@
         <v>2.37</v>
       </c>
       <c r="Q47">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R47">
         <v>2.16</v>
       </c>
       <c r="S47">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T47">
         <v>2.75</v>
@@ -8018,7 +8018,7 @@
         <v>3.5</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
         <v>1.05</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="O57">
-        <v>3.35</v>
+        <v>3.51</v>
       </c>
       <c r="P57">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q57">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R57">
         <v>2.04</v>
@@ -9621,7 +9621,7 @@
         <v>2.75</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V57">
         <v>1.38</v>
@@ -9639,7 +9639,7 @@
         <v>3.4</v>
       </c>
       <c r="AA57">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AB57">
         <v>1.83</v>
@@ -9654,7 +9654,7 @@
         <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AG57">
         <v>1.9</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AK57">
         <v>1.24</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB59">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10581,7 +10581,7 @@
         <v>2.56</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
         <v>2.3</v>
@@ -10590,25 +10590,25 @@
         <v>2.9</v>
       </c>
       <c r="R63">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
         <v>1.11</v>
@@ -10626,7 +10626,7 @@
         <v>1.99</v>
       </c>
       <c r="AD63">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AE63">
         <v>1.22</v>
@@ -10635,7 +10635,7 @@
         <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
         <v>1.39</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G68">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="O76">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>4.32</v>
+        <v>3.9</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12739,7 +12739,7 @@
         <v>2.17</v>
       </c>
       <c r="AB76">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC76">
         <v>4.2</v>
@@ -12770,7 +12770,7 @@
         <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="O83">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="P83">
-        <v>2.19</v>
+        <v>1.47</v>
       </c>
       <c r="Q83">
-        <v>4.12</v>
+        <v>5.75</v>
       </c>
       <c r="R83">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T83">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA83">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="AC83">
-        <v>3.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD83">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG83">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O84">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="P84">
-        <v>1.47</v>
+        <v>2.19</v>
       </c>
       <c r="Q84">
-        <v>5.75</v>
+        <v>4.12</v>
       </c>
       <c r="R84">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="S84">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="U84">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="V84">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W84">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.31</v>
+      </c>
+      <c r="Z84">
+        <v>3.25</v>
+      </c>
+      <c r="AA84">
+        <v>1.94</v>
+      </c>
+      <c r="AB84">
+        <v>1.74</v>
+      </c>
+      <c r="AC84">
+        <v>3.38</v>
+      </c>
+      <c r="AD84">
+        <v>1.24</v>
+      </c>
+      <c r="AE84">
         <v>1.04</v>
       </c>
-      <c r="Y84">
-        <v>1.18</v>
-      </c>
-      <c r="Z84">
-        <v>4.5</v>
-      </c>
-      <c r="AA84">
-        <v>1.57</v>
-      </c>
-      <c r="AB84">
-        <v>2.46</v>
-      </c>
-      <c r="AC84">
-        <v>2.27</v>
-      </c>
-      <c r="AD84">
-        <v>1.55</v>
-      </c>
-      <c r="AE84">
-        <v>1.18</v>
-      </c>
       <c r="AF84">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG84">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AK84">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14991,22 +14991,22 @@
         <v>2.95</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S90">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T90">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U90">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V90">
         <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
         <v>1.04</v>
@@ -15021,13 +15021,13 @@
         <v>2.15</v>
       </c>
       <c r="AB90">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AC90">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE90">
         <v>1.04</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AK90">
         <v>1.41</v>
@@ -15960,16 +15960,16 @@
         <v>3.7</v>
       </c>
       <c r="O96">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Q96">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R96">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S96">
         <v>1.37</v>
@@ -15978,7 +15978,7 @@
         <v>2.81</v>
       </c>
       <c r="U96">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V96">
         <v>1.36</v>
@@ -15990,10 +15990,10 @@
         <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA96">
         <v>1.9</v>
@@ -16005,13 +16005,13 @@
         <v>3.28</v>
       </c>
       <c r="AD96">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE96">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG96">
         <v>1.91</v>
@@ -17759,13 +17759,13 @@
         <v>2.8</v>
       </c>
       <c r="Q107">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R107">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T107">
         <v>3.1</v>
@@ -17774,10 +17774,10 @@
         <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -17792,7 +17792,7 @@
         <v>1.87</v>
       </c>
       <c r="AB107">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
         <v>2.97</v>
@@ -17807,7 +17807,7 @@
         <v>1.65</v>
       </c>
       <c r="AG107">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.26</v>
       </c>
       <c r="AK107">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18749,7 +18749,7 @@
         <v>2.63</v>
       </c>
       <c r="U113">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V113">
         <v>1.36</v>
@@ -18782,10 +18782,10 @@
         <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG113">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O125">
         <v>3.1</v>
@@ -20693,7 +20693,7 @@
         <v>2.9</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R125">
         <v>2</v>
@@ -20702,31 +20702,31 @@
         <v>1.44</v>
       </c>
       <c r="T125">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U125">
-        <v>3.33</v>
+        <v>2.94</v>
       </c>
       <c r="V125">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W125">
         <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
         <v>1.4</v>
       </c>
       <c r="Z125">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA125">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AB125">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC125">
         <v>4.2</v>
@@ -20741,7 +20741,7 @@
         <v>1.85</v>
       </c>
       <c r="AG125">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20856,34 +20856,34 @@
         <v>5</v>
       </c>
       <c r="Q126">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R126">
         <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T126">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U126">
         <v>2.89</v>
       </c>
       <c r="V126">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA126">
         <v>2.03</v>
@@ -20895,7 +20895,7 @@
         <v>3.6</v>
       </c>
       <c r="AD126">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE126">
         <v>1.05</v>
@@ -20920,7 +20920,7 @@
         <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21662,10 +21662,10 @@
         </is>
       </c>
       <c r="N131">
+        <v>3.25</v>
+      </c>
+      <c r="O131">
         <v>3.4</v>
-      </c>
-      <c r="O131">
-        <v>3.52</v>
       </c>
       <c r="P131">
         <v>2.15</v>
@@ -21988,37 +21988,37 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O133">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P133">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q133">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="R133">
         <v>2.34</v>
       </c>
       <c r="S133">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T133">
         <v>3.8</v>
       </c>
       <c r="U133">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V133">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="W133">
         <v>1.13</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
         <v>1.08</v>
@@ -22036,13 +22036,13 @@
         <v>1.86</v>
       </c>
       <c r="AD133">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE133">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF133">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG133">
         <v>2.62</v>
@@ -22061,7 +22061,7 @@
         <v>1.2</v>
       </c>
       <c r="AK133">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G144">
@@ -23777,68 +23777,68 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N144">
-        <v>4.55</v>
+        <v>2.07</v>
       </c>
       <c r="O144">
         <v>3.42</v>
       </c>
       <c r="P144">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
       <c r="Q144">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="R144">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S144">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T144">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="U144">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="V144">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W144">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y144">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z144">
-        <v>4.35</v>
+        <v>4.08</v>
       </c>
       <c r="AA144">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AB144">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="AC144">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AD144">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AE144">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF144">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AK144">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G145">
@@ -23940,68 +23940,68 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N145">
-        <v>2.07</v>
+        <v>4.55</v>
       </c>
       <c r="O145">
         <v>3.42</v>
       </c>
       <c r="P145">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="Q145">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S145">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T145">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="U145">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="W145">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X145">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z145">
-        <v>4.08</v>
+        <v>4.35</v>
       </c>
       <c r="AA145">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AB145">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="AC145">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD145">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AE145">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK145">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24922,46 +24922,46 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O151">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P151">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q151">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R151">
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T151">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U151">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V151">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W151">
         <v>1.08</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z151">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA151">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB151">
         <v>1.8</v>
@@ -24973,13 +24973,13 @@
         <v>1.25</v>
       </c>
       <c r="AE151">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF151">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG151">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="O154">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P154">
-        <v>3.91</v>
+        <v>4.46</v>
       </c>
       <c r="Q154">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R154">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S154">
+        <v>1.38</v>
+      </c>
+      <c r="T154">
+        <v>2.66</v>
+      </c>
+      <c r="U154">
+        <v>2.93</v>
+      </c>
+      <c r="V154">
         <v>1.4</v>
-      </c>
-      <c r="T154">
-        <v>2.91</v>
-      </c>
-      <c r="U154">
-        <v>2.85</v>
-      </c>
-      <c r="V154">
-        <v>1.38</v>
       </c>
       <c r="W154">
         <v>1.05</v>
       </c>
       <c r="X154">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z154">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA154">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB154">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC154">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD154">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE154">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF154">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG154">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>1.25</v>
       </c>
       <c r="AK154">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="O155">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P155">
-        <v>4.46</v>
+        <v>3.91</v>
       </c>
       <c r="Q155">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R155">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S155">
+        <v>1.4</v>
+      </c>
+      <c r="T155">
+        <v>2.91</v>
+      </c>
+      <c r="U155">
+        <v>2.85</v>
+      </c>
+      <c r="V155">
         <v>1.38</v>
-      </c>
-      <c r="T155">
-        <v>2.66</v>
-      </c>
-      <c r="U155">
-        <v>2.93</v>
-      </c>
-      <c r="V155">
-        <v>1.4</v>
       </c>
       <c r="W155">
         <v>1.05</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y155">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA155">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB155">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC155">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD155">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE155">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF155">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AG155">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -27367,19 +27367,19 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O166">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P166">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="Q166">
         <v>2.15</v>
       </c>
       <c r="R166">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S166">
         <v>1.36</v>
@@ -27397,25 +27397,25 @@
         <v>1.08</v>
       </c>
       <c r="X166">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y166">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z166">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="AA166">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB166">
         <v>1.81</v>
       </c>
       <c r="AC166">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="AD166">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE166">
         <v>1.11</v>
@@ -27424,7 +27424,7 @@
         <v>1.83</v>
       </c>
       <c r="AG166">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O182">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="P182">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="Q182">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="R182">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="S182">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T182">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U182">
-        <v>3.52</v>
+        <v>2.82</v>
       </c>
       <c r="V182">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W182">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X182">
+        <v>1.03</v>
+      </c>
+      <c r="Y182">
+        <v>1.33</v>
+      </c>
+      <c r="Z182">
+        <v>3.1</v>
+      </c>
+      <c r="AA182">
+        <v>2.02</v>
+      </c>
+      <c r="AB182">
+        <v>1.7</v>
+      </c>
+      <c r="AC182">
+        <v>3.83</v>
+      </c>
+      <c r="AD182">
+        <v>1.25</v>
+      </c>
+      <c r="AE182">
         <v>1.05</v>
       </c>
-      <c r="Y182">
-        <v>1.5</v>
-      </c>
-      <c r="Z182">
-        <v>2.59</v>
-      </c>
-      <c r="AA182">
-        <v>2.6</v>
-      </c>
-      <c r="AB182">
-        <v>1.47</v>
-      </c>
-      <c r="AC182">
-        <v>4.8</v>
-      </c>
-      <c r="AD182">
-        <v>1.12</v>
-      </c>
-      <c r="AE182">
-        <v>1</v>
-      </c>
       <c r="AF182">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AG182">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK182">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,80 +30138,80 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O183">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="P183">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="Q183">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="R183">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="S183">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="T183">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U183">
-        <v>2.82</v>
+        <v>3.52</v>
       </c>
       <c r="V183">
+        <v>1.27</v>
+      </c>
+      <c r="W183">
+        <v>1.01</v>
+      </c>
+      <c r="X183">
+        <v>1.05</v>
+      </c>
+      <c r="Y183">
+        <v>1.5</v>
+      </c>
+      <c r="Z183">
+        <v>2.59</v>
+      </c>
+      <c r="AA183">
+        <v>2.6</v>
+      </c>
+      <c r="AB183">
+        <v>1.47</v>
+      </c>
+      <c r="AC183">
+        <v>4.8</v>
+      </c>
+      <c r="AD183">
+        <v>1.12</v>
+      </c>
+      <c r="AE183">
+        <v>1</v>
+      </c>
+      <c r="AF183">
+        <v>2.05</v>
+      </c>
+      <c r="AG183">
+        <v>1.66</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ183">
         <v>1.36</v>
       </c>
-      <c r="W183">
-        <v>1.04</v>
-      </c>
-      <c r="X183">
-        <v>1.03</v>
-      </c>
-      <c r="Y183">
-        <v>1.33</v>
-      </c>
-      <c r="Z183">
-        <v>3.1</v>
-      </c>
-      <c r="AA183">
-        <v>2.02</v>
-      </c>
-      <c r="AB183">
-        <v>1.7</v>
-      </c>
-      <c r="AC183">
-        <v>3.83</v>
-      </c>
-      <c r="AD183">
-        <v>1.25</v>
-      </c>
-      <c r="AE183">
-        <v>1.05</v>
-      </c>
-      <c r="AF183">
-        <v>1.79</v>
-      </c>
-      <c r="AG183">
-        <v>1.9</v>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ183">
-        <v>1.3</v>
-      </c>
       <c r="AK183">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL183">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V4">
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>4.33</v>
+      </c>
+      <c r="AA4">
+        <v>1.58</v>
+      </c>
+      <c r="AB4">
+        <v>2.21</v>
+      </c>
+      <c r="AC4">
+        <v>2.41</v>
+      </c>
+      <c r="AD4">
+        <v>1.45</v>
+      </c>
+      <c r="AE4">
         <v>1.18</v>
       </c>
-      <c r="Z4">
-        <v>3.85</v>
-      </c>
-      <c r="AA4">
-        <v>1.64</v>
-      </c>
-      <c r="AB4">
-        <v>2.02</v>
-      </c>
-      <c r="AC4">
-        <v>2.77</v>
-      </c>
-      <c r="AD4">
-        <v>1.4</v>
-      </c>
-      <c r="AE4">
-        <v>1.12</v>
-      </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.5</v>
       </c>
       <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.18</v>
+      </c>
+      <c r="Z5">
+        <v>3.85</v>
+      </c>
+      <c r="AA5">
+        <v>1.64</v>
+      </c>
+      <c r="AB5">
+        <v>2.02</v>
+      </c>
+      <c r="AC5">
+        <v>2.77</v>
+      </c>
+      <c r="AD5">
+        <v>1.4</v>
+      </c>
+      <c r="AE5">
         <v>1.12</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.14</v>
-      </c>
-      <c r="Z5">
-        <v>4.33</v>
-      </c>
-      <c r="AA5">
-        <v>1.58</v>
-      </c>
-      <c r="AB5">
-        <v>2.21</v>
-      </c>
-      <c r="AC5">
-        <v>2.41</v>
-      </c>
-      <c r="AD5">
-        <v>1.45</v>
-      </c>
-      <c r="AE5">
-        <v>1.18</v>
-      </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O14">
         <v>3.3</v>
       </c>
       <c r="P14">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q14">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U14">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
         <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC14">
         <v>3.35</v>
       </c>
       <c r="AD14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK14">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
         <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="Q15">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="U15">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
         <v>3.35</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AK15">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.72</v>
+      </c>
+      <c r="O25">
+        <v>3.9</v>
+      </c>
+      <c r="P25">
+        <v>4.15</v>
+      </c>
+      <c r="Q25">
+        <v>2.2</v>
+      </c>
+      <c r="R25">
         <v>2.4</v>
-      </c>
-      <c r="O25">
-        <v>3.5</v>
-      </c>
-      <c r="P25">
-        <v>2.53</v>
-      </c>
-      <c r="Q25">
-        <v>2.88</v>
-      </c>
-      <c r="R25">
-        <v>2.21</v>
       </c>
       <c r="S25">
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
         <v>1.57</v>
@@ -4414,34 +4414,34 @@
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD25">
         <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>4.15</v>
+        <v>2.53</v>
       </c>
       <c r="Q26">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
         <v>1.57</v>
@@ -4577,34 +4577,34 @@
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB26">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD26">
         <v>1.5</v>
       </c>
       <c r="AE26">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G145">
@@ -23940,68 +23940,68 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N145">
-        <v>2.11</v>
+        <v>4.55</v>
       </c>
       <c r="O145">
         <v>3.42</v>
       </c>
       <c r="P145">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="Q145">
+        <v>4.2</v>
+      </c>
+      <c r="R145">
+        <v>2.4</v>
+      </c>
+      <c r="S145">
+        <v>1.25</v>
+      </c>
+      <c r="T145">
+        <v>3.45</v>
+      </c>
+      <c r="U145">
+        <v>2.25</v>
+      </c>
+      <c r="V145">
+        <v>1.55</v>
+      </c>
+      <c r="W145">
+        <v>1.15</v>
+      </c>
+      <c r="X145">
+        <v>1.01</v>
+      </c>
+      <c r="Y145">
+        <v>1.14</v>
+      </c>
+      <c r="Z145">
+        <v>4.35</v>
+      </c>
+      <c r="AA145">
+        <v>1.57</v>
+      </c>
+      <c r="AB145">
+        <v>2.3</v>
+      </c>
+      <c r="AC145">
         <v>2.55</v>
       </c>
-      <c r="R145">
-        <v>2.35</v>
-      </c>
-      <c r="S145">
-        <v>1.3</v>
-      </c>
-      <c r="T145">
-        <v>3.1</v>
-      </c>
-      <c r="U145">
-        <v>2.45</v>
-      </c>
-      <c r="V145">
-        <v>1.47</v>
-      </c>
-      <c r="W145">
-        <v>1.12</v>
-      </c>
-      <c r="X145">
-        <v>1.04</v>
-      </c>
-      <c r="Y145">
-        <v>1.23</v>
-      </c>
-      <c r="Z145">
-        <v>3.9</v>
-      </c>
-      <c r="AA145">
-        <v>1.74</v>
-      </c>
-      <c r="AB145">
-        <v>2.1</v>
-      </c>
-      <c r="AC145">
-        <v>2.8</v>
-      </c>
       <c r="AD145">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE145">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG145">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
+        <v>1.95</v>
+      </c>
+      <c r="AK145">
         <v>1.25</v>
-      </c>
-      <c r="AK145">
-        <v>1.7</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G146">
@@ -24103,84 +24103,84 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N146">
-        <v>4.55</v>
+        <v>2.11</v>
       </c>
       <c r="O146">
         <v>3.42</v>
       </c>
       <c r="P146">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="Q146">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="R146">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
+        <v>3.1</v>
+      </c>
+      <c r="U146">
+        <v>2.45</v>
+      </c>
+      <c r="V146">
+        <v>1.47</v>
+      </c>
+      <c r="W146">
+        <v>1.12</v>
+      </c>
+      <c r="X146">
+        <v>1.04</v>
+      </c>
+      <c r="Y146">
+        <v>1.23</v>
+      </c>
+      <c r="Z146">
+        <v>3.9</v>
+      </c>
+      <c r="AA146">
+        <v>1.74</v>
+      </c>
+      <c r="AB146">
+        <v>2.1</v>
+      </c>
+      <c r="AC146">
+        <v>2.8</v>
+      </c>
+      <c r="AD146">
+        <v>1.42</v>
+      </c>
+      <c r="AE146">
+        <v>1.11</v>
+      </c>
+      <c r="AF146">
+        <v>1.6</v>
+      </c>
+      <c r="AG146">
+        <v>2.18</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
         <v>1.25</v>
       </c>
-      <c r="T146">
-        <v>3.45</v>
-      </c>
-      <c r="U146">
-        <v>2.25</v>
-      </c>
-      <c r="V146">
-        <v>1.55</v>
-      </c>
-      <c r="W146">
-        <v>1.15</v>
-      </c>
-      <c r="X146">
-        <v>1.01</v>
-      </c>
-      <c r="Y146">
-        <v>1.14</v>
-      </c>
-      <c r="Z146">
-        <v>4.35</v>
-      </c>
-      <c r="AA146">
-        <v>1.57</v>
-      </c>
-      <c r="AB146">
-        <v>2.3</v>
-      </c>
-      <c r="AC146">
-        <v>2.55</v>
-      </c>
-      <c r="AD146">
-        <v>1.48</v>
-      </c>
-      <c r="AE146">
-        <v>1.2</v>
-      </c>
-      <c r="AF146">
-        <v>1.53</v>
-      </c>
-      <c r="AG146">
-        <v>2.38</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.95</v>
-      </c>
       <c r="AK146">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AL146">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U4">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
         <v>1.5</v>
       </c>
       <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.18</v>
+      </c>
+      <c r="Z4">
+        <v>3.85</v>
+      </c>
+      <c r="AA4">
+        <v>1.64</v>
+      </c>
+      <c r="AB4">
+        <v>2.02</v>
+      </c>
+      <c r="AC4">
+        <v>2.77</v>
+      </c>
+      <c r="AD4">
+        <v>1.4</v>
+      </c>
+      <c r="AE4">
         <v>1.12</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.14</v>
-      </c>
-      <c r="Z4">
-        <v>4.33</v>
-      </c>
-      <c r="AA4">
-        <v>1.58</v>
-      </c>
-      <c r="AB4">
-        <v>2.21</v>
-      </c>
-      <c r="AC4">
-        <v>2.41</v>
-      </c>
-      <c r="AD4">
-        <v>1.45</v>
-      </c>
-      <c r="AE4">
-        <v>1.18</v>
-      </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
         <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>4.33</v>
+      </c>
+      <c r="AA5">
+        <v>1.58</v>
+      </c>
+      <c r="AB5">
+        <v>2.21</v>
+      </c>
+      <c r="AC5">
+        <v>2.41</v>
+      </c>
+      <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
         <v>1.18</v>
       </c>
-      <c r="Z5">
-        <v>3.85</v>
-      </c>
-      <c r="AA5">
-        <v>1.64</v>
-      </c>
-      <c r="AB5">
-        <v>2.02</v>
-      </c>
-      <c r="AC5">
-        <v>2.77</v>
-      </c>
-      <c r="AD5">
-        <v>1.4</v>
-      </c>
-      <c r="AE5">
-        <v>1.12</v>
-      </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
         <v>2.8</v>
@@ -1311,40 +1311,40 @@
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
         <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
         <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
         <v>2.4</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2307,7 +2307,7 @@
         <v>1.65</v>
       </c>
       <c r="AB12">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
         <v>2.63</v>
@@ -2319,7 +2319,7 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
         <v>2.38</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q21">
-        <v>4.4</v>
+        <v>4.88</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S21">
         <v>1.44</v>
@@ -3759,28 +3759,28 @@
         <v>1.3</v>
       </c>
       <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
         <v>1.06</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.35</v>
       </c>
       <c r="Z21">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA21">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB21">
         <v>1.63</v>
       </c>
       <c r="AC21">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="AD21">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
         <v>1.03</v>
@@ -3805,7 +3805,7 @@
         <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>2.19</v>
       </c>
       <c r="R27">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
         <v>3.14</v>
@@ -4740,7 +4740,7 @@
         <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.2</v>
@@ -4758,7 +4758,7 @@
         <v>2.81</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
         <v>1.09</v>
@@ -4783,7 +4783,7 @@
         <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4888,10 +4888,10 @@
         <v>1.99</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U28">
         <v>2.97</v>
@@ -4912,10 +4912,10 @@
         <v>2.83</v>
       </c>
       <c r="AA28">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
         <v>3.75</v>
@@ -4927,7 +4927,7 @@
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG28">
         <v>1.82</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.46</v>
+        <v>3.13</v>
       </c>
       <c r="O30">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O34">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P34">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="Q34">
         <v>1.75</v>
       </c>
       <c r="R34">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="S34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="V34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,28 +5887,28 @@
         <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
         <v>1.38</v>
       </c>
       <c r="AB34">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AC34">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD34">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
+        <v>1.06</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>3.1</v>
+      </c>
+      <c r="AA35">
+        <v>2.05</v>
+      </c>
+      <c r="AB35">
+        <v>1.7</v>
+      </c>
+      <c r="AC35">
+        <v>3.5</v>
+      </c>
+      <c r="AD35">
+        <v>1.29</v>
+      </c>
+      <c r="AE35">
         <v>1.05</v>
-      </c>
-      <c r="Y35">
-        <v>1.28</v>
-      </c>
-      <c r="Z35">
-        <v>3.5</v>
-      </c>
-      <c r="AA35">
-        <v>1.85</v>
-      </c>
-      <c r="AB35">
-        <v>1.82</v>
-      </c>
-      <c r="AC35">
-        <v>3.08</v>
-      </c>
-      <c r="AD35">
-        <v>1.35</v>
-      </c>
-      <c r="AE35">
-        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>1.79</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O37">
         <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R37">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S37">
         <v>1.36</v>
@@ -6361,43 +6361,43 @@
         <v>2.96</v>
       </c>
       <c r="U37">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA37">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB37">
         <v>1.78</v>
       </c>
       <c r="AC37">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD37">
         <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
         <v>1.8</v>
@@ -6844,16 +6844,16 @@
         <v>2.78</v>
       </c>
       <c r="S40">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U40">
         <v>1.95</v>
       </c>
       <c r="V40">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="W40">
         <v>1.22</v>
@@ -6868,25 +6868,25 @@
         <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB40">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AC40">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE40">
         <v>1.35</v>
       </c>
       <c r="AF40">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7013,7 +7013,7 @@
         <v>4.8</v>
       </c>
       <c r="U41">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V41">
         <v>1.83</v>
@@ -7025,16 +7025,16 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
         <v>7</v>
       </c>
       <c r="AA41">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB41">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AC41">
         <v>1.85</v>
@@ -7043,13 +7043,13 @@
         <v>1.9</v>
       </c>
       <c r="AE41">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG41">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK41">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,28 +7318,28 @@
         </is>
       </c>
       <c r="N43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O43">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q43">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
         <v>2.86</v>
       </c>
       <c r="U43">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="V43">
         <v>1.37</v>
@@ -7348,7 +7348,7 @@
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
@@ -7357,10 +7357,10 @@
         <v>3.28</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC43">
         <v>3.14</v>
@@ -7372,10 +7372,10 @@
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG43">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>3.3</v>
       </c>
       <c r="AK43">
         <v>1.05</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O52">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q52">
         <v>3.2</v>
@@ -8821,19 +8821,19 @@
         <v>1.41</v>
       </c>
       <c r="Z52">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="AA52">
         <v>2.33</v>
       </c>
       <c r="AB52">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC52">
         <v>4.36</v>
       </c>
       <c r="AD52">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
         <v>1.02</v>
@@ -8842,7 +8842,7 @@
         <v>1.88</v>
       </c>
       <c r="AG52">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9440,28 +9440,28 @@
         <v>3.8</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P56">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q56">
+        <v>4.33</v>
+      </c>
+      <c r="R56">
+        <v>2.46</v>
+      </c>
+      <c r="S56">
+        <v>1.2</v>
+      </c>
+      <c r="T56">
         <v>4</v>
       </c>
-      <c r="R56">
-        <v>2.31</v>
-      </c>
-      <c r="S56">
-        <v>1.26</v>
-      </c>
-      <c r="T56">
-        <v>3.5</v>
-      </c>
       <c r="U56">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V56">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9470,10 +9470,10 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>5.25</v>
+        <v>5.21</v>
       </c>
       <c r="AA56">
         <v>1.51</v>
@@ -9482,13 +9482,13 @@
         <v>2.55</v>
       </c>
       <c r="AC56">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AD56">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE56">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AF56">
         <v>1.45</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="AK56">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -11885,61 +11885,61 @@
         <v>1.43</v>
       </c>
       <c r="O71">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="P71">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q71">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R71">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T71">
         <v>3.88</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V71">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
         <v>5.75</v>
       </c>
       <c r="AA71">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC71">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD71">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE71">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF71">
         <v>1.54</v>
       </c>
       <c r="AG71">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK71">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q73">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="R73">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S73">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="T73">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U73">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V73">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="W73">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="AA73">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AC73">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AD73">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AE73">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF73">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG73">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12700,10 +12700,10 @@
         <v>1.94</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P76">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12718,10 +12718,10 @@
         <v>2.5</v>
       </c>
       <c r="U76">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V76">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W76">
         <v>1.02</v>
@@ -12730,31 +12730,31 @@
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z76">
         <v>2.8</v>
       </c>
       <c r="AA76">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AB76">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC76">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AD76">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG76">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -15142,46 +15142,46 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O91">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P91">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q91">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S91">
         <v>1.55</v>
       </c>
       <c r="T91">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U91">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="V91">
         <v>1.24</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y91">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z91">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AA91">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AB91">
         <v>1.46</v>
@@ -15193,10 +15193,10 @@
         <v>1.13</v>
       </c>
       <c r="AE91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG91">
         <v>1.68</v>
@@ -15215,7 +15215,7 @@
         <v>1.4</v>
       </c>
       <c r="AK91">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16147,7 +16147,7 @@
         <v>1.36</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X97">
         <v>1.01</v>
@@ -16159,7 +16159,7 @@
         <v>3.28</v>
       </c>
       <c r="AA97">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB97">
         <v>1.8</v>
@@ -16177,7 +16177,7 @@
         <v>1.71</v>
       </c>
       <c r="AG97">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16295,7 +16295,7 @@
         <v>3.3</v>
       </c>
       <c r="R98">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -16307,7 +16307,7 @@
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
         <v>1.06</v>
@@ -16325,7 +16325,7 @@
         <v>2.07</v>
       </c>
       <c r="AB98">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC98">
         <v>3.5</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AK98">
         <v>1.39</v>
@@ -16612,13 +16612,13 @@
         <v>1.42</v>
       </c>
       <c r="O100">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P100">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q100">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R100">
         <v>2.11</v>
@@ -16648,16 +16648,16 @@
         <v>3.65</v>
       </c>
       <c r="AA100">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB100">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC100">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE100">
         <v>1.07</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK100">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S107">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T107">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V107">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W107">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z107">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA107">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC107">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,52 +18076,52 @@
         </is>
       </c>
       <c r="N109">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O109">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P109">
         <v>1.73</v>
       </c>
       <c r="Q109">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="R109">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S109">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
         <v>3.3</v>
       </c>
       <c r="U109">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V109">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA109">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB109">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC109">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AD109">
         <v>1.5</v>
@@ -18130,7 +18130,7 @@
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
         <v>2.25</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK109">
         <v>1.18</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="O110">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P110">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q110">
         <v>1.61</v>
@@ -18257,10 +18257,10 @@
         <v>1.33</v>
       </c>
       <c r="T110">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U110">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V110">
         <v>1.43</v>
@@ -18269,7 +18269,7 @@
         <v>1.1</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
         <v>1.21</v>
@@ -18278,22 +18278,22 @@
         <v>3.65</v>
       </c>
       <c r="AA110">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB110">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC110">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD110">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE110">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AG110">
         <v>1.57</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK110">
         <v>3.3</v>
@@ -19543,31 +19543,31 @@
         </is>
       </c>
       <c r="N118">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O118">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q118">
-        <v>4.75</v>
+        <v>4.48</v>
       </c>
       <c r="R118">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S118">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T118">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U118">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W118">
         <v>1.04</v>
@@ -19576,31 +19576,31 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z118">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB118">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC118">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="AD118">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF118">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG118">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AK118">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20847,16 +20847,16 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O126">
         <v>3.1</v>
       </c>
       <c r="P126">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q126">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R126">
         <v>2</v>
@@ -20868,7 +20868,7 @@
         <v>2.62</v>
       </c>
       <c r="U126">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="V126">
         <v>1.33</v>
@@ -20877,25 +20877,25 @@
         <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y126">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z126">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AA126">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AB126">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC126">
         <v>4.2</v>
       </c>
       <c r="AD126">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
@@ -20904,7 +20904,7 @@
         <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21013,55 +21013,55 @@
         <v>1.6</v>
       </c>
       <c r="O127">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="P127">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q127">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S127">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T127">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
         <v>2.89</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W127">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z127">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AA127">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB127">
         <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD127">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE127">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
         <v>2.05</v>
@@ -21083,7 +21083,7 @@
         <v>1.27</v>
       </c>
       <c r="AK127">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P132">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="AA132">
+        <v>1.95</v>
+      </c>
+      <c r="AB132">
         <v>1.85</v>
-      </c>
-      <c r="AB132">
-        <v>1.95</v>
       </c>
       <c r="AC132">
         <v>0</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O133">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q133">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="R133">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T133">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U133">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V133">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="AA133">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB133">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC133">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD133">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE133">
         <v>1.17</v>
       </c>
       <c r="AF133">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG133">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AK133">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O141">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P141">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23455,10 +23455,10 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O142">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P142">
         <v>2.1</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O143">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P143">
-        <v>4</v>
+        <v>4.61</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -24279,7 +24279,7 @@
         <v>4.4</v>
       </c>
       <c r="Q147">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R147">
         <v>2.1</v>
@@ -24297,10 +24297,10 @@
         <v>1.33</v>
       </c>
       <c r="W147">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X147">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y147">
         <v>1.33</v>
@@ -24312,10 +24312,10 @@
         <v>1.98</v>
       </c>
       <c r="AB147">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC147">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AD147">
         <v>1.21</v>
@@ -24436,10 +24436,10 @@
         <v>2.12</v>
       </c>
       <c r="O148">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P148">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q148">
         <v>2.9</v>
@@ -24448,13 +24448,13 @@
         <v>2.2</v>
       </c>
       <c r="S148">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T148">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U148">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V148">
         <v>1.45</v>
@@ -24469,28 +24469,28 @@
         <v>1.24</v>
       </c>
       <c r="Z148">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA148">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB148">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC148">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AD148">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE148">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF148">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG148">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24596,34 +24596,34 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O149">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="P149">
-        <v>8.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q149">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R149">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S149">
         <v>1.22</v>
       </c>
       <c r="T149">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="U149">
         <v>2.2</v>
       </c>
       <c r="V149">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W149">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X149">
         <v>1.02</v>
@@ -24632,28 +24632,28 @@
         <v>1.1</v>
       </c>
       <c r="Z149">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA149">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB149">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC149">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD149">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE149">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF149">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG149">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK149">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -27533,13 +27533,13 @@
         <v>1.65</v>
       </c>
       <c r="O167">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q167">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="R167">
         <v>2.15</v>
@@ -27557,7 +27557,7 @@
         <v>1.4</v>
       </c>
       <c r="W167">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
         <v>1.05</v>
@@ -27566,19 +27566,19 @@
         <v>1.26</v>
       </c>
       <c r="Z167">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA167">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB167">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC167">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AD167">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE167">
         <v>1.11</v>
@@ -27587,7 +27587,7 @@
         <v>1.83</v>
       </c>
       <c r="AG167">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK167">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AL167">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V4">
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>4.33</v>
+      </c>
+      <c r="AA4">
+        <v>1.58</v>
+      </c>
+      <c r="AB4">
+        <v>2.21</v>
+      </c>
+      <c r="AC4">
+        <v>2.41</v>
+      </c>
+      <c r="AD4">
+        <v>1.45</v>
+      </c>
+      <c r="AE4">
         <v>1.18</v>
       </c>
-      <c r="Z4">
-        <v>3.85</v>
-      </c>
-      <c r="AA4">
-        <v>1.64</v>
-      </c>
-      <c r="AB4">
-        <v>2.02</v>
-      </c>
-      <c r="AC4">
-        <v>2.77</v>
-      </c>
-      <c r="AD4">
-        <v>1.4</v>
-      </c>
-      <c r="AE4">
-        <v>1.12</v>
-      </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.5</v>
       </c>
       <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.18</v>
+      </c>
+      <c r="Z5">
+        <v>3.85</v>
+      </c>
+      <c r="AA5">
+        <v>1.64</v>
+      </c>
+      <c r="AB5">
+        <v>2.02</v>
+      </c>
+      <c r="AC5">
+        <v>2.77</v>
+      </c>
+      <c r="AD5">
+        <v>1.4</v>
+      </c>
+      <c r="AE5">
         <v>1.12</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.14</v>
-      </c>
-      <c r="Z5">
-        <v>4.33</v>
-      </c>
-      <c r="AA5">
-        <v>1.58</v>
-      </c>
-      <c r="AB5">
-        <v>2.21</v>
-      </c>
-      <c r="AC5">
-        <v>2.41</v>
-      </c>
-      <c r="AD5">
-        <v>1.45</v>
-      </c>
-      <c r="AE5">
-        <v>1.18</v>
-      </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1471,10 +1471,10 @@
         <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
         <v>1.12</v>
@@ -1486,10 +1486,10 @@
         <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB7">
         <v>2.1</v>
@@ -1498,13 +1498,13 @@
         <v>2.6</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
         <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
         <v>2.31</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
         <v>1.62</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
+        <v>2.88</v>
+      </c>
+      <c r="P9">
+        <v>2.98</v>
+      </c>
+      <c r="Q9">
         <v>2.9</v>
       </c>
-      <c r="P9">
-        <v>2.95</v>
-      </c>
-      <c r="Q9">
-        <v>3.2</v>
-      </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S9">
         <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
         <v>3.4</v>
@@ -1806,13 +1806,13 @@
         <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="AA9">
         <v>2.41</v>
@@ -1821,19 +1821,19 @@
         <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="AD9">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
         <v>1.53</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
         <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T10">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
         <v>2.88</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
         <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK10">
         <v>1.29</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
         <v>3.3</v>
       </c>
       <c r="P14">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="R14">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
         <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC14">
         <v>3.35</v>
       </c>
       <c r="AD14">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
         <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q15">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="R15">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z15">
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
         <v>3.35</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.81</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>2.43</v>
       </c>
       <c r="AC18">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.94</v>
+        <v>2.99</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="V19">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA19">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>2.99</v>
+        <v>1.94</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3759,28 +3759,28 @@
         <v>1.3</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
         <v>1.03</v>
       </c>
-      <c r="X21">
-        <v>1.06</v>
-      </c>
       <c r="Y21">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z21">
         <v>2.85</v>
       </c>
       <c r="AA21">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
         <v>1.03</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AK21">
         <v>1.2</v>
@@ -4061,7 +4061,7 @@
         <v>1.6</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P23">
         <v>4.2</v>
@@ -4076,22 +4076,22 @@
         <v>1.2</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="U23">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="V23">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
         <v>5.89</v>
@@ -4100,22 +4100,22 @@
         <v>1.41</v>
       </c>
       <c r="AB23">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AC23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD23">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE23">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF23">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG23">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4230,55 +4230,55 @@
         <v>3</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
         <v>4.6</v>
       </c>
       <c r="AA24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC24">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AD24">
         <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
         <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4399,28 +4399,28 @@
         <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
         <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
         <v>1.57</v>
@@ -4432,10 +4432,10 @@
         <v>2.42</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
         <v>1.53</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O26">
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC26">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
         <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q28">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="R28">
         <v>1.99</v>
@@ -4903,7 +4903,7 @@
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
         <v>1.33</v>
@@ -4918,16 +4918,16 @@
         <v>1.65</v>
       </c>
       <c r="AC28">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE28">
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG28">
         <v>1.82</v>
@@ -4946,7 +4946,7 @@
         <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="O36">
-        <v>3.51</v>
+        <v>3.15</v>
       </c>
       <c r="P36">
         <v>2.39</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.35</v>
@@ -6210,25 +6210,25 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
         <v>1.29</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
         <v>1.74</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
         <v>1.41</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q39">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="U39">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V39">
         <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB39">
         <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
         <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -7170,49 +7170,49 @@
         <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
         <v>2.2</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AC42">
         <v>2.45</v>
       </c>
       <c r="AD42">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
         <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
         <v>1.44</v>
@@ -7481,55 +7481,55 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q44">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R44">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S44">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="U44">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="V44">
         <v>1.36</v>
       </c>
       <c r="W44">
+        <v>1.07</v>
+      </c>
+      <c r="X44">
         <v>1.04</v>
       </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
       <c r="Y44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA44">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC44">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD44">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
         <v>1.04</v>
@@ -7538,7 +7538,7 @@
         <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK44">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="O47">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
         <v>3.5</v>
       </c>
       <c r="R47">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S47">
         <v>1.34</v>
@@ -8006,7 +8006,7 @@
         <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AA47">
         <v>2.06</v>
@@ -8018,7 +8018,7 @@
         <v>3.5</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
         <v>1.05</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9618,13 +9618,13 @@
         <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
         <v>2.8</v>
       </c>
       <c r="V57">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
         <v>1.06</v>
@@ -9633,10 +9633,10 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z57">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA57">
         <v>2.11</v>
@@ -9673,7 +9673,7 @@
         <v>1.27</v>
       </c>
       <c r="AK57">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,16 +9772,16 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R58">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U58">
         <v>3</v>
@@ -9790,16 +9790,16 @@
         <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
         <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA58">
         <v>2.09</v>
@@ -9808,10 +9808,10 @@
         <v>1.7</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="AD58">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE58">
         <v>1.08</v>
@@ -9820,7 +9820,7 @@
         <v>1.92</v>
       </c>
       <c r="AG58">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,19 +10095,19 @@
         <v>2.8</v>
       </c>
       <c r="P60">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
         <v>3</v>
       </c>
       <c r="R60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
         <v>1.38</v>
       </c>
       <c r="T60">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="U60">
         <v>2.85</v>
@@ -10116,37 +10116,37 @@
         <v>1.36</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
         <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="AA60">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB60">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC60">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD60">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE60">
         <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG60">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10424,22 +10424,22 @@
         <v>2.05</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R62">
         <v>2.32</v>
       </c>
       <c r="S62">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
         <v>3.32</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W62">
         <v>1.1</v>
@@ -10451,28 +10451,28 @@
         <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA62">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB62">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC62">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE62">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF62">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG62">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O63">
         <v>3.55</v>
@@ -10587,55 +10587,55 @@
         <v>2.3</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V63">
         <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z63">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA63">
         <v>1.48</v>
       </c>
       <c r="AB63">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC63">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="AD63">
+        <v>1.44</v>
+      </c>
+      <c r="AE63">
+        <v>1.18</v>
+      </c>
+      <c r="AF63">
         <v>1.43</v>
       </c>
-      <c r="AE63">
-        <v>1.22</v>
-      </c>
-      <c r="AF63">
-        <v>1.44</v>
-      </c>
       <c r="AG63">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q66">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="R66">
         <v>2.26</v>
@@ -11085,25 +11085,25 @@
         <v>1.39</v>
       </c>
       <c r="T66">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V66">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AA66">
         <v>1.92</v>
@@ -11115,7 +11115,7 @@
         <v>3.05</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE66">
         <v>1.07</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AK66">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O81">
         <v>3.5</v>
       </c>
       <c r="P81">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q81">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="R81">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T81">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U81">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W81">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1.02</v>
@@ -13548,25 +13548,25 @@
         <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA81">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB81">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC81">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="AD81">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE81">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG81">
         <v>2.15</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AK81">
         <v>1.36</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="O82">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q82">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R82">
         <v>2.3</v>
@@ -13693,13 +13693,13 @@
         <v>1.3</v>
       </c>
       <c r="T82">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U82">
         <v>2.53</v>
       </c>
       <c r="V82">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13711,28 +13711,28 @@
         <v>1.2</v>
       </c>
       <c r="Z82">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA82">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB82">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC82">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD82">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE82">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF82">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,10 +13844,10 @@
         <v>4.4</v>
       </c>
       <c r="P83">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Q83">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="R83">
         <v>2.45</v>
@@ -13856,13 +13856,13 @@
         <v>1.25</v>
       </c>
       <c r="T83">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W83">
         <v>1.13</v>
@@ -13877,16 +13877,16 @@
         <v>4.55</v>
       </c>
       <c r="AA83">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC83">
         <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE83">
         <v>1.19</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AK83">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q84">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="R84">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S84">
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="U84">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V84">
         <v>1.36</v>
@@ -14031,19 +14031,19 @@
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
         <v>1.31</v>
       </c>
       <c r="Z84">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA84">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC84">
         <v>3.3</v>
@@ -14055,10 +14055,10 @@
         <v>1.05</v>
       </c>
       <c r="AF84">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG84">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AK84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14994,10 +14994,10 @@
         <v>1.97</v>
       </c>
       <c r="S90">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T90">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U90">
         <v>2.5</v>
@@ -15018,7 +15018,7 @@
         <v>2.9</v>
       </c>
       <c r="AA90">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AB90">
         <v>1.88</v>
@@ -15027,13 +15027,13 @@
         <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE90">
         <v>1.04</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG90">
         <v>1.85</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
         <v>1.41</v>
@@ -15305,34 +15305,34 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P92">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T92">
         <v>2.91</v>
       </c>
       <c r="U92">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X92">
         <v>1</v>
@@ -15341,16 +15341,16 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA92">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB92">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC92">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD92">
         <v>1.4</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15474,7 +15474,7 @@
         <v>3.35</v>
       </c>
       <c r="P93">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="Q93">
         <v>2.65</v>
@@ -15507,19 +15507,19 @@
         <v>4.5</v>
       </c>
       <c r="AA93">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB93">
         <v>2.3</v>
       </c>
       <c r="AC93">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD93">
         <v>1.5</v>
       </c>
       <c r="AE93">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF93">
         <v>1.5</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
         <v>1.62</v>
@@ -15631,34 +15631,34 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O94">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
         <v>2.56</v>
       </c>
       <c r="Q94">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R94">
         <v>1.96</v>
       </c>
       <c r="S94">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U94">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V94">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X94">
         <v>1.06</v>
@@ -15667,22 +15667,22 @@
         <v>1.35</v>
       </c>
       <c r="Z94">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA94">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB94">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AC94">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD94">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF94">
         <v>1.81</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK94">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U95">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V95">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AC95">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG95">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK95">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,28 +15957,28 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O96">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
         <v>1.8</v>
       </c>
       <c r="Q96">
-        <v>4.2</v>
+        <v>4.58</v>
       </c>
       <c r="R96">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T96">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U96">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V96">
         <v>1.36</v>
@@ -15987,13 +15987,13 @@
         <v>1.03</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AA96">
         <v>1.9</v>
@@ -16002,10 +16002,10 @@
         <v>1.78</v>
       </c>
       <c r="AC96">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AD96">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
         <v>1.08</v>
@@ -16014,7 +16014,7 @@
         <v>1.79</v>
       </c>
       <c r="AG96">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16781,16 +16781,16 @@
         <v>2.9</v>
       </c>
       <c r="Q101">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="R101">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U101">
         <v>2.82</v>
@@ -16802,13 +16802,13 @@
         <v>1.06</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
         <v>1.35</v>
       </c>
       <c r="Z101">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="AA101">
         <v>1.95</v>
@@ -16820,16 +16820,16 @@
         <v>3.2</v>
       </c>
       <c r="AD101">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
         <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.32</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -19389,19 +19389,19 @@
         <v>2.1</v>
       </c>
       <c r="Q117">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R117">
         <v>2.05</v>
       </c>
       <c r="S117">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T117">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U117">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V117">
         <v>1.37</v>
@@ -19413,10 +19413,10 @@
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z117">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA117">
         <v>1.98</v>
@@ -19425,19 +19425,19 @@
         <v>1.78</v>
       </c>
       <c r="AC117">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AD117">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE117">
         <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG117">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AK117">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20361,13 +20361,13 @@
         <v>3</v>
       </c>
       <c r="O123">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P123">
         <v>2.15</v>
       </c>
       <c r="Q123">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="R123">
         <v>2</v>
@@ -20382,10 +20382,10 @@
         <v>3.1</v>
       </c>
       <c r="V123">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X123">
         <v>1.03</v>
@@ -20400,22 +20400,22 @@
         <v>2.15</v>
       </c>
       <c r="AB123">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC123">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="AD123">
         <v>1.19</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF123">
         <v>1.85</v>
       </c>
       <c r="AG123">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
         <v>1.3</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="O124">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="P124">
         <v>3.25</v>
@@ -20533,13 +20533,13 @@
         <v>2.9</v>
       </c>
       <c r="R124">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S124">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="U124">
         <v>3.08</v>
@@ -20548,10 +20548,10 @@
         <v>1.3</v>
       </c>
       <c r="W124">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y124">
         <v>1.35</v>
@@ -20563,22 +20563,22 @@
         <v>2.3</v>
       </c>
       <c r="AB124">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AC124">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD124">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF124">
         <v>1.91</v>
       </c>
       <c r="AG124">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O128">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="P128">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q128">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R128">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S128">
         <v>1.4</v>
       </c>
       <c r="T128">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="U128">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V128">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W128">
+        <v>1.06</v>
+      </c>
+      <c r="X128">
         <v>1.05</v>
       </c>
-      <c r="X128">
-        <v>1.06</v>
-      </c>
       <c r="Y128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z128">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="AA128">
         <v>2.2</v>
       </c>
       <c r="AB128">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC128">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="AD128">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE128">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF128">
         <v>1.91</v>
       </c>
       <c r="AG128">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK128">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,25 +21336,25 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O129">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P129">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
       </c>
       <c r="R129">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S129">
         <v>1.36</v>
       </c>
       <c r="T129">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="U129">
         <v>2.5</v>
@@ -21363,10 +21363,10 @@
         <v>1.44</v>
       </c>
       <c r="W129">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X129">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
         <v>1.26</v>
@@ -21375,22 +21375,22 @@
         <v>3.54</v>
       </c>
       <c r="AA129">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB129">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC129">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="AD129">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE129">
         <v>1.08</v>
       </c>
       <c r="AF129">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG129">
         <v>1.94</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK129">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,28 +21499,28 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P130">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q130">
         <v>2.72</v>
       </c>
       <c r="R130">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="S130">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T130">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="U130">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V130">
         <v>1.34</v>
@@ -21529,22 +21529,22 @@
         <v>1.07</v>
       </c>
       <c r="X130">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y130">
         <v>1.36</v>
       </c>
       <c r="Z130">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AA130">
         <v>2.1</v>
       </c>
       <c r="AB130">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC130">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AD130">
         <v>1.21</v>
@@ -21553,7 +21553,7 @@
         <v>1.07</v>
       </c>
       <c r="AF130">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG130">
         <v>1.91</v>
@@ -22154,7 +22154,7 @@
         <v>2</v>
       </c>
       <c r="O134">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P134">
         <v>3.1</v>
@@ -22166,7 +22166,7 @@
         <v>2.34</v>
       </c>
       <c r="S134">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T134">
         <v>3.8</v>
@@ -22187,22 +22187,22 @@
         <v>1.08</v>
       </c>
       <c r="Z134">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA134">
         <v>1.33</v>
       </c>
       <c r="AB134">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC134">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AD134">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE134">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AF134">
         <v>1.4</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
+        <v>3.6</v>
+      </c>
+      <c r="O137">
         <v>3.75</v>
       </c>
-      <c r="O137">
-        <v>3.7</v>
-      </c>
       <c r="P137">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q137">
         <v>4.5</v>
@@ -22655,13 +22655,13 @@
         <v>2.23</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T137">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U137">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V137">
         <v>1.45</v>
@@ -22670,34 +22670,34 @@
         <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y137">
         <v>1.19</v>
       </c>
       <c r="Z137">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA137">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB137">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AC137">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="AD137">
         <v>1.37</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF137">
         <v>1.73</v>
       </c>
       <c r="AG137">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -23784,10 +23784,10 @@
         <v>1.67</v>
       </c>
       <c r="O144">
+        <v>3.75</v>
+      </c>
+      <c r="P144">
         <v>3.9</v>
-      </c>
-      <c r="P144">
-        <v>4</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -23796,16 +23796,16 @@
         <v>2.4</v>
       </c>
       <c r="S144">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T144">
         <v>3.75</v>
       </c>
       <c r="U144">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V144">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W144">
         <v>1.14</v>
@@ -23814,7 +23814,7 @@
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z144">
         <v>4.92</v>
@@ -23823,19 +23823,19 @@
         <v>1.54</v>
       </c>
       <c r="AB144">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AC144">
         <v>2.29</v>
       </c>
       <c r="AD144">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE144">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF144">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG144">
         <v>2.4</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK144">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,10 +23944,10 @@
         </is>
       </c>
       <c r="N145">
-        <v>4.55</v>
+        <v>4.03</v>
       </c>
       <c r="O145">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P145">
         <v>1.79</v>
@@ -23962,25 +23962,25 @@
         <v>1.25</v>
       </c>
       <c r="T145">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U145">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V145">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W145">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
         <v>1.14</v>
       </c>
       <c r="Z145">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA145">
         <v>1.57</v>
@@ -23992,16 +23992,16 @@
         <v>2.55</v>
       </c>
       <c r="AD145">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE145">
         <v>1.2</v>
       </c>
       <c r="AF145">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24113,49 +24113,49 @@
         <v>3.42</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="Q146">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="R146">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S146">
         <v>1.3</v>
       </c>
       <c r="T146">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U146">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V146">
         <v>1.47</v>
       </c>
       <c r="W146">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z146">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA146">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB146">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC146">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AD146">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE146">
         <v>1.11</v>
@@ -24164,7 +24164,7 @@
         <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.5</v>
+        <v>3.06</v>
       </c>
       <c r="O152">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P152">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q152">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R152">
         <v>2.1</v>
@@ -25103,46 +25103,46 @@
         <v>1.38</v>
       </c>
       <c r="T152">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U152">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V152">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W152">
         <v>1.08</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
         <v>1.3</v>
       </c>
       <c r="Z152">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA152">
         <v>1.95</v>
       </c>
       <c r="AB152">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC152">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AD152">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE152">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF152">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG152">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>1.3</v>
       </c>
       <c r="AK152">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25903,25 +25903,25 @@
         <v>2.04</v>
       </c>
       <c r="O157">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P157">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q157">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="R157">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S157">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T157">
         <v>2.24</v>
       </c>
       <c r="U157">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V157">
         <v>1.25</v>
@@ -25936,10 +25936,10 @@
         <v>1.41</v>
       </c>
       <c r="Z157">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AA157">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AB157">
         <v>1.46</v>
@@ -25954,7 +25954,7 @@
         <v>1</v>
       </c>
       <c r="AF157">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG157">
         <v>1.7</v>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK157">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26069,16 +26069,16 @@
         <v>2.9</v>
       </c>
       <c r="P158">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q158">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R158">
         <v>1.95</v>
       </c>
       <c r="S158">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T158">
         <v>2.29</v>
@@ -26099,13 +26099,13 @@
         <v>1.4</v>
       </c>
       <c r="Z158">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AA158">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB158">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC158">
         <v>4.1</v>
@@ -26117,10 +26117,10 @@
         <v>1.01</v>
       </c>
       <c r="AF158">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AG158">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26398,10 +26398,10 @@
         <v>15</v>
       </c>
       <c r="Q160">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R160">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="S160">
         <v>1.18</v>
@@ -26410,43 +26410,43 @@
         <v>4.5</v>
       </c>
       <c r="U160">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="V160">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="W160">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X160">
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z160">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA160">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB160">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AC160">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD160">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE160">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF160">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG160">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK160">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26561,52 +26561,52 @@
         <v>2.53</v>
       </c>
       <c r="Q161">
-        <v>3.55</v>
+        <v>4.21</v>
       </c>
       <c r="R161">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S161">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T161">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="U161">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V161">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W161">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X161">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z161">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA161">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AB161">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC161">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AD161">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE161">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF161">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG161">
         <v>1.8</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK161">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,40 +26715,40 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O162">
         <v>3.75</v>
       </c>
       <c r="P162">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="Q162">
+        <v>2.16</v>
+      </c>
+      <c r="R162">
         <v>2.15</v>
       </c>
-      <c r="R162">
-        <v>2.3</v>
-      </c>
       <c r="S162">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T162">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U162">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V162">
         <v>1.5</v>
       </c>
       <c r="W162">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X162">
         <v>1.04</v>
       </c>
       <c r="Y162">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z162">
         <v>4</v>
@@ -26760,19 +26760,19 @@
         <v>2.1</v>
       </c>
       <c r="AC162">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AD162">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE162">
         <v>1.15</v>
       </c>
       <c r="AF162">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG162">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK162">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27367,25 +27367,25 @@
         </is>
       </c>
       <c r="N166">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O166">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P166">
         <v>1.8</v>
       </c>
       <c r="Q166">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="R166">
         <v>2.2</v>
       </c>
       <c r="S166">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T166">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="U166">
         <v>2.6</v>
@@ -27400,25 +27400,25 @@
         <v>1</v>
       </c>
       <c r="Y166">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z166">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA166">
         <v>1.81</v>
       </c>
       <c r="AB166">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC166">
         <v>3.1</v>
       </c>
       <c r="AD166">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE166">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF166">
         <v>1.75</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AK166">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27856,31 +27856,31 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O169">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P169">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="Q169">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R169">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S169">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T169">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U169">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="V169">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W169">
         <v>1.04</v>
@@ -27889,28 +27889,28 @@
         <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z169">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AA169">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB169">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC169">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AD169">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE169">
         <v>1.05</v>
       </c>
       <c r="AF169">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG169">
         <v>1.83</v>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK169">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28019,22 +28019,22 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="O170">
         <v>3.75</v>
       </c>
       <c r="P170">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
       </c>
       <c r="R170">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S170">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T170">
         <v>2.94</v>
@@ -28049,7 +28049,7 @@
         <v>1.08</v>
       </c>
       <c r="X170">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y170">
         <v>1.32</v>
@@ -28064,19 +28064,19 @@
         <v>1.83</v>
       </c>
       <c r="AC170">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD170">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE170">
         <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG170">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>1.17</v>
       </c>
       <c r="AK170">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="O180">
         <v>2.75</v>
       </c>
       <c r="P180">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="Q180">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="R180">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S180">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T180">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U180">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V180">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W180">
         <v>1.04</v>
       </c>
       <c r="X180">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y180">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Z180">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA180">
         <v>2.67</v>
       </c>
       <c r="AB180">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AC180">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AD180">
         <v>1.12</v>
       </c>
       <c r="AE180">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF180">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG180">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK180">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="O181">
         <v>3.25</v>
       </c>
       <c r="P181">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="Q181">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R181">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S181">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T181">
         <v>2.75</v>
       </c>
       <c r="U181">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="V181">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W181">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X181">
         <v>1.04</v>
       </c>
       <c r="Y181">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z181">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA181">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB181">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC181">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD181">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE181">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF181">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG181">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK181">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30147,10 +30147,10 @@
         <v>2.8</v>
       </c>
       <c r="Q183">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="R183">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S183">
         <v>1.44</v>
@@ -30162,7 +30162,7 @@
         <v>2.8</v>
       </c>
       <c r="V183">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W183">
         <v>1.05</v>
@@ -30171,31 +30171,31 @@
         <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z183">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA183">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB183">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC183">
-        <v>3.83</v>
+        <v>3.34</v>
       </c>
       <c r="AD183">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE183">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF183">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG183">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>1.3</v>
       </c>
       <c r="AK183">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30301,55 +30301,55 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="O184">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P184">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q184">
         <v>2.9</v>
       </c>
       <c r="R184">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S184">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T184">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U184">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="V184">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W184">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X184">
         <v>1.05</v>
       </c>
       <c r="Y184">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z184">
         <v>2.53</v>
       </c>
       <c r="AA184">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB184">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC184">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD184">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE184">
         <v>1</v>
@@ -30358,7 +30358,7 @@
         <v>2.05</v>
       </c>
       <c r="AG184">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK184">
         <v>1.62</v>
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL189">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -650,19 +650,19 @@
         <v>2.09</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -674,16 +674,16 @@
         <v>3.08</v>
       </c>
       <c r="AA2">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC2">
         <v>3.42</v>
       </c>
       <c r="AD2">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
         <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>4.85</v>
+        <v>4.35</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="AA4">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>4.33</v>
+      </c>
+      <c r="AA5">
+        <v>1.6</v>
+      </c>
+      <c r="AB5">
+        <v>2.24</v>
+      </c>
+      <c r="AC5">
+        <v>2.41</v>
+      </c>
+      <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
         <v>1.18</v>
       </c>
-      <c r="Z5">
-        <v>3.85</v>
-      </c>
-      <c r="AA5">
-        <v>1.64</v>
-      </c>
-      <c r="AB5">
-        <v>2.02</v>
-      </c>
-      <c r="AC5">
-        <v>2.77</v>
-      </c>
-      <c r="AD5">
-        <v>1.4</v>
-      </c>
-      <c r="AE5">
+      <c r="AF5">
+        <v>1.65</v>
+      </c>
+      <c r="AG5">
+        <v>2.17</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.12</v>
       </c>
-      <c r="AF5">
-        <v>1.73</v>
-      </c>
-      <c r="AG5">
-        <v>1.96</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.17</v>
-      </c>
       <c r="AK5">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -2428,43 +2428,43 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
         <v>1.73</v>
       </c>
       <c r="Q13">
-        <v>4.5</v>
+        <v>5.21</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="V13">
         <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
         <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AA13">
         <v>1.99</v>
@@ -2473,10 +2473,10 @@
         <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD13">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
         <v>1.09</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.5</v>
+      </c>
+      <c r="O14">
+        <v>3.2</v>
+      </c>
+      <c r="P14">
+        <v>2.45</v>
+      </c>
+      <c r="Q14">
+        <v>3.28</v>
+      </c>
+      <c r="R14">
         <v>2.05</v>
       </c>
-      <c r="O14">
-        <v>3.3</v>
-      </c>
-      <c r="P14">
-        <v>3.12</v>
-      </c>
-      <c r="Q14">
-        <v>2.54</v>
-      </c>
-      <c r="R14">
-        <v>2.18</v>
-      </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.53</v>
+        <v>3.05</v>
       </c>
       <c r="U14">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
         <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
         <v>3.35</v>
       </c>
       <c r="AD14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK14">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q15">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U15">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
+        <v>1.83</v>
+      </c>
+      <c r="AG15">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.31</v>
+      </c>
+      <c r="AK15">
         <v>1.7</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.44</v>
-      </c>
-      <c r="AK15">
-        <v>1.48</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O16">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q16">
-        <v>4.32</v>
+        <v>3.75</v>
       </c>
       <c r="R16">
         <v>2.14</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2953,28 +2953,28 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
         <v>2.23</v>
       </c>
       <c r="AB16">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC16">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD16">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
         <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
         <v>1.3</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O17">
         <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q17">
         <v>2.33</v>
@@ -3095,40 +3095,40 @@
         <v>2.48</v>
       </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="U17">
         <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE17">
         <v>1.2</v>
@@ -3153,7 +3153,7 @@
         <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,25 +3246,25 @@
         <v>1.28</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P18">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q18">
         <v>1.73</v>
       </c>
       <c r="R18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.66</v>
@@ -3273,7 +3273,7 @@
         <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.13</v>
@@ -3282,25 +3282,25 @@
         <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB18">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD18">
         <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
         <v>4.3</v>
@@ -3421,46 +3421,46 @@
         <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U19">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AA19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC19">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
         <v>1.88</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="O20">
         <v>3.35</v>
       </c>
       <c r="P20">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <v>2.2</v>
@@ -3596,37 +3596,37 @@
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC25">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
+        <v>1.44</v>
+      </c>
+      <c r="AE25">
+        <v>1.2</v>
+      </c>
+      <c r="AF25">
+        <v>1.5</v>
+      </c>
+      <c r="AG25">
+        <v>2.55</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.22</v>
+      </c>
+      <c r="AK25">
         <v>1.53</v>
-      </c>
-      <c r="AE25">
-        <v>1.18</v>
-      </c>
-      <c r="AF25">
-        <v>1.53</v>
-      </c>
-      <c r="AG25">
-        <v>2.3</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.2</v>
-      </c>
-      <c r="AK25">
-        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q26">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
         <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA26">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
+        <v>2.35</v>
+      </c>
+      <c r="AC26">
+        <v>2.42</v>
+      </c>
+      <c r="AD26">
+        <v>1.53</v>
+      </c>
+      <c r="AE26">
+        <v>1.18</v>
+      </c>
+      <c r="AF26">
+        <v>1.53</v>
+      </c>
+      <c r="AG26">
         <v>2.3</v>
       </c>
-      <c r="AC26">
-        <v>2.55</v>
-      </c>
-      <c r="AD26">
-        <v>1.44</v>
-      </c>
-      <c r="AE26">
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.2</v>
       </c>
-      <c r="AF26">
-        <v>1.5</v>
-      </c>
-      <c r="AG26">
-        <v>2.55</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.22</v>
-      </c>
       <c r="AK26">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P31">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
         <v>3.5</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
         <v>1.38</v>
@@ -5395,7 +5395,7 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
         <v>3.44</v>
@@ -5404,19 +5404,19 @@
         <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC31">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
         <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
         <v>2.15</v>
@@ -5435,7 +5435,7 @@
         <v>1.58</v>
       </c>
       <c r="AK31">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P32">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R32">
         <v>2.44</v>
@@ -5546,43 +5546,43 @@
         <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W32">
         <v>1.15</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA32">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB32">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AC32">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD32">
         <v>1.6</v>
       </c>
       <c r="AE32">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF32">
         <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK32">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O33">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5709,7 +5709,7 @@
         <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
         <v>1.57</v>
@@ -5739,13 +5739,13 @@
         <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>1.9</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q37">
         <v>2.67</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="O38">
         <v>3.84</v>
       </c>
       <c r="P38">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="Q38">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R38">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S38">
         <v>1.21</v>
@@ -6527,7 +6527,7 @@
         <v>2.01</v>
       </c>
       <c r="V38">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="W38">
         <v>1.2</v>
@@ -6551,16 +6551,16 @@
         <v>1.98</v>
       </c>
       <c r="AD38">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE38">
         <v>1.36</v>
       </c>
       <c r="AF38">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG38">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O39">
         <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q39">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="R39">
         <v>2.14</v>
@@ -6699,10 +6699,10 @@
         <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA39">
         <v>1.75</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O40">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
       <c r="Q40">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="R40">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="S40">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U40">
         <v>1.95</v>
       </c>
       <c r="V40">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AC40">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD40">
         <v>1.9</v>
       </c>
       <c r="AE40">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AG40">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O41">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="P41">
-        <v>9.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q41">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="R41">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T41">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
         <v>1.95</v>
       </c>
       <c r="V41">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="AC41">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD41">
         <v>1.9</v>
       </c>
       <c r="AE41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF41">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P42">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -7191,7 +7191,7 @@
         <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA42">
         <v>1.6</v>
@@ -7321,34 +7321,34 @@
         <v>9</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P43">
         <v>1.28</v>
       </c>
       <c r="Q43">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="U43">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
@@ -7357,25 +7357,25 @@
         <v>3.28</v>
       </c>
       <c r="AA43">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
         <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE43">
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AG43">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>3.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="O49">
         <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
+        <v>1.95</v>
+      </c>
+      <c r="AB49">
         <v>1.85</v>
-      </c>
-      <c r="AB49">
-        <v>1.95</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q50">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R50">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S50">
         <v>1.27</v>
@@ -8480,43 +8480,43 @@
         <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
         <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
         <v>2.63</v>
       </c>
       <c r="AD50">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O51">
         <v>4.6</v>
@@ -8643,10 +8643,10 @@
         <v>3.42</v>
       </c>
       <c r="U51">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
         <v>1.13</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE51">
         <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
         <v>2.7</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q64">
         <v>2.6</v>
       </c>
       <c r="R64">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S64">
         <v>1.29</v>
@@ -10762,40 +10762,40 @@
         <v>3.3</v>
       </c>
       <c r="U64">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
         <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC64">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AD64">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
         <v>2.3</v>
@@ -10814,7 +10814,7 @@
         <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q65">
         <v>4</v>
       </c>
       <c r="R65">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
         <v>1.28</v>
@@ -10931,10 +10931,10 @@
         <v>1.55</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
         <v>1.19</v>
@@ -10946,10 +10946,10 @@
         <v>1.66</v>
       </c>
       <c r="AB65">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC65">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AD65">
         <v>1.44</v>
@@ -10958,10 +10958,10 @@
         <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11085,10 +11085,10 @@
         <v>1.39</v>
       </c>
       <c r="T66">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V66">
         <v>1.4</v>
@@ -11103,7 +11103,7 @@
         <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
         <v>1.92</v>
@@ -11115,7 +11115,7 @@
         <v>3.05</v>
       </c>
       <c r="AD66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE66">
         <v>1.07</v>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P73">
         <v>3.05</v>
@@ -12241,7 +12241,7 @@
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
         <v>5.4</v>
@@ -12733,7 +12733,7 @@
         <v>1.4</v>
       </c>
       <c r="Z76">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA76">
         <v>2.33</v>
@@ -12742,7 +12742,7 @@
         <v>1.61</v>
       </c>
       <c r="AC76">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD76">
         <v>1.19</v>
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P78">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Q78">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="R78">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
         <v>2.41</v>
       </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W78">
         <v>1.08</v>
@@ -13056,16 +13056,16 @@
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
         <v>4.2</v>
       </c>
       <c r="AA78">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB78">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
         <v>2.75</v>
@@ -13074,13 +13074,13 @@
         <v>1.49</v>
       </c>
       <c r="AE78">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF78">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O79">
         <v>4.45</v>
       </c>
       <c r="P79">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="Q79">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="R79">
         <v>2.55</v>
@@ -13213,16 +13213,16 @@
         <v>1.65</v>
       </c>
       <c r="W79">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z79">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA79">
         <v>1.41</v>
@@ -13237,13 +13237,13 @@
         <v>1.72</v>
       </c>
       <c r="AE79">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG79">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK79">
         <v>2.4</v>
@@ -13358,16 +13358,16 @@
         <v>4.2</v>
       </c>
       <c r="Q80">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R80">
         <v>2.59</v>
       </c>
       <c r="S80">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U80">
         <v>2.23</v>
@@ -13388,7 +13388,7 @@
         <v>5.2</v>
       </c>
       <c r="AA80">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB80">
         <v>2.55</v>
@@ -13397,7 +13397,7 @@
         <v>2.25</v>
       </c>
       <c r="AD80">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE80">
         <v>1.21</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O82">
         <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q82">
         <v>3.3</v>
@@ -13729,10 +13729,10 @@
         <v>1.17</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>1.92</v>
       </c>
       <c r="O85">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P85">
         <v>3.15</v>
@@ -14188,7 +14188,7 @@
         <v>2.18</v>
       </c>
       <c r="V85">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="AA85">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB85">
         <v>2.32</v>
       </c>
       <c r="AC85">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AD85">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE85">
         <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14330,10 +14330,10 @@
         <v>2.2</v>
       </c>
       <c r="O86">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="Q86">
         <v>2.81</v>
@@ -14342,7 +14342,7 @@
         <v>2.3</v>
       </c>
       <c r="S86">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
         <v>3.4</v>
@@ -14357,7 +14357,7 @@
         <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.15</v>
@@ -14366,7 +14366,7 @@
         <v>4.8</v>
       </c>
       <c r="AA86">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB86">
         <v>2.29</v>
@@ -14493,7 +14493,7 @@
         <v>2.8</v>
       </c>
       <c r="O87">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P87">
         <v>2.11</v>
@@ -14511,7 +14511,7 @@
         <v>4.1</v>
       </c>
       <c r="U87">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V87">
         <v>1.78</v>
@@ -14523,13 +14523,13 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z87">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB87">
         <v>2.96</v>
@@ -14541,7 +14541,7 @@
         <v>1.85</v>
       </c>
       <c r="AE87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF87">
         <v>1.32</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.55</v>
       </c>
       <c r="P88">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="Q88">
         <v>2.4</v>
@@ -14674,13 +14674,13 @@
         <v>4.4</v>
       </c>
       <c r="U88">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V88">
         <v>1.75</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14695,10 +14695,10 @@
         <v>1.33</v>
       </c>
       <c r="AB88">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC88">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD88">
         <v>1.83</v>
@@ -14710,7 +14710,7 @@
         <v>1.33</v>
       </c>
       <c r="AG88">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>1.92</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P89">
         <v>2.87</v>
@@ -14831,19 +14831,19 @@
         <v>2.9</v>
       </c>
       <c r="S89">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T89">
         <v>4.95</v>
       </c>
       <c r="U89">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V89">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="W89">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -14855,25 +14855,25 @@
         <v>8.6</v>
       </c>
       <c r="AA89">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AB89">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="AC89">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AD89">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AE89">
         <v>1.63</v>
       </c>
       <c r="AF89">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AG89">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O91">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P91">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -15157,19 +15157,19 @@
         <v>1.95</v>
       </c>
       <c r="S91">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T91">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="U91">
         <v>3.34</v>
       </c>
       <c r="V91">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W91">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X91">
         <v>1.07</v>
@@ -15193,13 +15193,13 @@
         <v>1.13</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF91">
         <v>2.02</v>
       </c>
       <c r="AG91">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.4</v>
       </c>
       <c r="AK91">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
         <v>1.8</v>
@@ -16642,10 +16642,10 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z100">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AA100">
         <v>1.81</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="P102">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O105">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="P105">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q105">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R105">
         <v>2.7</v>
@@ -17442,46 +17442,46 @@
         <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V105">
         <v>1.67</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z105">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA105">
         <v>1.44</v>
       </c>
       <c r="AB105">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC105">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE105">
         <v>1.24</v>
       </c>
       <c r="AF105">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,31 +17596,31 @@
         <v>1.29</v>
       </c>
       <c r="Q106">
-        <v>7.5</v>
+        <v>6.79</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="S106">
         <v>1.18</v>
       </c>
       <c r="T106">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U106">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V106">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W106">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
         <v>5.75</v>
@@ -17629,10 +17629,10 @@
         <v>1.36</v>
       </c>
       <c r="AB106">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AC106">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AD106">
         <v>1.79</v>
@@ -17641,7 +17641,7 @@
         <v>1.33</v>
       </c>
       <c r="AF106">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
         <v>2.12</v>
@@ -17660,7 +17660,7 @@
         <v>1.09</v>
       </c>
       <c r="AK106">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA108">
         <v>1.85</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.14</v>
+        <v>2.32</v>
       </c>
       <c r="AK111">
         <v>1.07</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P113">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q113">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R113">
         <v>2.1</v>
       </c>
       <c r="S113">
+        <v>1.42</v>
+      </c>
+      <c r="T113">
+        <v>2.56</v>
+      </c>
+      <c r="U113">
+        <v>2.9</v>
+      </c>
+      <c r="V113">
+        <v>1.3</v>
+      </c>
+      <c r="W113">
+        <v>1.07</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
         <v>1.36</v>
       </c>
-      <c r="T113">
-        <v>2.63</v>
-      </c>
-      <c r="U113">
-        <v>2.91</v>
-      </c>
-      <c r="V113">
-        <v>1.36</v>
-      </c>
-      <c r="W113">
-        <v>1.05</v>
-      </c>
-      <c r="X113">
-        <v>1</v>
-      </c>
-      <c r="Y113">
-        <v>1.28</v>
-      </c>
       <c r="Z113">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AA113">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB113">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC113">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AD113">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG113">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK113">
         <v>1.67</v>
@@ -18894,22 +18894,22 @@
         <v>1.75</v>
       </c>
       <c r="O114">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q114">
         <v>2.3</v>
       </c>
       <c r="R114">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S114">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U114">
         <v>2.8</v>
@@ -18918,16 +18918,16 @@
         <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z114">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AA114">
         <v>2</v>
@@ -18945,10 +18945,10 @@
         <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG114">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -20868,7 +20868,7 @@
         <v>2.62</v>
       </c>
       <c r="U126">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="V126">
         <v>1.33</v>
@@ -20892,7 +20892,7 @@
         <v>1.71</v>
       </c>
       <c r="AC126">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD126">
         <v>1.19</v>
@@ -21502,13 +21502,13 @@
         <v>2.05</v>
       </c>
       <c r="O130">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="P130">
         <v>3.5</v>
       </c>
       <c r="Q130">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R130">
         <v>2.16</v>
@@ -21535,19 +21535,19 @@
         <v>1.36</v>
       </c>
       <c r="Z130">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AA130">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB130">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC130">
         <v>3.9</v>
       </c>
       <c r="AD130">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE130">
         <v>1.07</v>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK130">
         <v>1.67</v>
@@ -21662,25 +21662,25 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O131">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P131">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="Q131">
         <v>2.45</v>
       </c>
       <c r="R131">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="S131">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T131">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="U131">
         <v>2.45</v>
@@ -21689,25 +21689,25 @@
         <v>1.44</v>
       </c>
       <c r="W131">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z131">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA131">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB131">
         <v>2.04</v>
       </c>
       <c r="AC131">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD131">
         <v>1.36</v>
@@ -21719,7 +21719,7 @@
         <v>1.66</v>
       </c>
       <c r="AG131">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21828,7 +21828,7 @@
         <v>3</v>
       </c>
       <c r="O132">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="P132">
         <v>2.2</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="AA132">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB132">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC132">
         <v>0</v>
@@ -21997,7 +21997,7 @@
         <v>2.23</v>
       </c>
       <c r="Q133">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R133">
         <v>2.25</v>
@@ -22006,13 +22006,13 @@
         <v>1.3</v>
       </c>
       <c r="T133">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U133">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V133">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W133">
         <v>1.12</v>
@@ -22024,10 +22024,10 @@
         <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA133">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB133">
         <v>2.1</v>
@@ -22039,10 +22039,10 @@
         <v>1.4</v>
       </c>
       <c r="AE133">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF133">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG133">
         <v>2.3</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK133">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22477,16 +22477,16 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O136">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P136">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q136">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="R136">
         <v>1.75</v>
@@ -22507,25 +22507,25 @@
         <v>1.02</v>
       </c>
       <c r="X136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Y136">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z136">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AA136">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AB136">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC136">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="AD136">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE136">
         <v>1.01</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AK136">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O138">
         <v>3.55</v>
       </c>
       <c r="P138">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q138">
         <v>2.62</v>
@@ -22821,13 +22821,13 @@
         <v>1.2</v>
       </c>
       <c r="T138">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U138">
         <v>2.11</v>
       </c>
       <c r="V138">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W138">
         <v>1.2</v>
@@ -22839,19 +22839,19 @@
         <v>1.08</v>
       </c>
       <c r="Z138">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA138">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB138">
         <v>2.63</v>
       </c>
       <c r="AC138">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD138">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE138">
         <v>1.25</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AK138">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,34 +22966,34 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O139">
-        <v>5.05</v>
+        <v>4.65</v>
       </c>
       <c r="P139">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q139">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="R139">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="S139">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T139">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="U139">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V139">
         <v>2.5</v>
       </c>
       <c r="W139">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X139">
         <v>1</v>
@@ -23005,19 +23005,19 @@
         <v>13</v>
       </c>
       <c r="AA139">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB139">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AC139">
         <v>1.36</v>
       </c>
       <c r="AD139">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AE139">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF139">
         <v>1.25</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK139">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,31 +23129,31 @@
         </is>
       </c>
       <c r="N140">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="O140">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P140">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="Q140">
         <v>4.8</v>
       </c>
       <c r="R140">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S140">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T140">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="U140">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V140">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W140">
         <v>1.2</v>
@@ -23162,31 +23162,31 @@
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z140">
-        <v>5.89</v>
+        <v>5.55</v>
       </c>
       <c r="AA140">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB140">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC140">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AD140">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE140">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AF140">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG140">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK140">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24451,7 +24451,7 @@
         <v>1.36</v>
       </c>
       <c r="T148">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U148">
         <v>2.62</v>
@@ -24478,10 +24478,10 @@
         <v>2.04</v>
       </c>
       <c r="AC148">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AD148">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE148">
         <v>1.1</v>
@@ -24608,7 +24608,7 @@
         <v>1.67</v>
       </c>
       <c r="R149">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S149">
         <v>1.22</v>
@@ -25091,7 +25091,7 @@
         <v>3.3</v>
       </c>
       <c r="P152">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q152">
         <v>3.12</v>
@@ -25121,7 +25121,7 @@
         <v>1.3</v>
       </c>
       <c r="Z152">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA152">
         <v>1.95</v>
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25592,43 +25592,43 @@
         <v>1.39</v>
       </c>
       <c r="T155">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U155">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="V155">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W155">
         <v>1.05</v>
       </c>
       <c r="X155">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
         <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="AA155">
         <v>2.03</v>
       </c>
       <c r="AB155">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC155">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD155">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE155">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF155">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
         <v>1.85</v>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O156">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -25752,7 +25752,7 @@
         <v>2.15</v>
       </c>
       <c r="S156">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
         <v>2.73</v>
@@ -25761,25 +25761,25 @@
         <v>2.93</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
         <v>1.29</v>
       </c>
       <c r="Z156">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA156">
         <v>1.9</v>
       </c>
       <c r="AB156">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC156">
         <v>3.45</v>
@@ -25788,13 +25788,13 @@
         <v>1.3</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF156">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O159">
         <v>3.2</v>
       </c>
       <c r="P159">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q159">
         <v>3.1</v>
@@ -26241,7 +26241,7 @@
         <v>2.07</v>
       </c>
       <c r="S159">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
         <v>3.1</v>
@@ -26256,31 +26256,31 @@
         <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y159">
         <v>1.25</v>
       </c>
       <c r="Z159">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA159">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB159">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC159">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD159">
         <v>1.36</v>
       </c>
       <c r="AE159">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF159">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG159">
         <v>2.12</v>
@@ -26296,7 +26296,7 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK159">
         <v>1.42</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="O160">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="P160">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q160">
         <v>1.5</v>
@@ -26878,25 +26878,25 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O163">
         <v>3.6</v>
       </c>
       <c r="P163">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="Q163">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R163">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S163">
         <v>1.44</v>
       </c>
       <c r="T163">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U163">
         <v>3</v>
@@ -26905,7 +26905,7 @@
         <v>1.26</v>
       </c>
       <c r="W163">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X163">
         <v>1.08</v>
@@ -26920,16 +26920,16 @@
         <v>2.38</v>
       </c>
       <c r="AB163">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC163">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD163">
         <v>1.17</v>
       </c>
       <c r="AE163">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF163">
         <v>2.3</v>
@@ -26951,7 +26951,7 @@
         <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27204,19 +27204,19 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="O165">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P165">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q165">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R165">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S165">
         <v>1.46</v>
@@ -27228,7 +27228,7 @@
         <v>3.24</v>
       </c>
       <c r="V165">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W165">
         <v>1.03</v>
@@ -27243,25 +27243,25 @@
         <v>2.7</v>
       </c>
       <c r="AA165">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AB165">
         <v>1.57</v>
       </c>
       <c r="AC165">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="AD165">
         <v>1.22</v>
       </c>
       <c r="AE165">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG165">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK165">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27889,7 +27889,7 @@
         <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z169">
         <v>2.87</v>
@@ -27898,10 +27898,10 @@
         <v>2.1</v>
       </c>
       <c r="AB169">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC169">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AD169">
         <v>1.27</v>
@@ -27929,7 +27929,7 @@
         <v>1.22</v>
       </c>
       <c r="AK169">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28022,22 +28022,22 @@
         <v>1.58</v>
       </c>
       <c r="O170">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P170">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="Q170">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R170">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S170">
         <v>1.39</v>
       </c>
       <c r="T170">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="U170">
         <v>2.88</v>
@@ -28052,16 +28052,16 @@
         <v>1.05</v>
       </c>
       <c r="Y170">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z170">
         <v>3.35</v>
       </c>
       <c r="AA170">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB170">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC170">
         <v>3.4</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK170">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
+        <v>2.62</v>
+      </c>
+      <c r="O171">
         <v>2.7</v>
       </c>
-      <c r="O171">
-        <v>2.65</v>
-      </c>
       <c r="P171">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28351,7 +28351,7 @@
         <v>2.75</v>
       </c>
       <c r="P172">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q172">
         <v>2.78</v>
@@ -28360,10 +28360,10 @@
         <v>1.74</v>
       </c>
       <c r="S172">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T172">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="U172">
         <v>4</v>
@@ -28375,25 +28375,25 @@
         <v>1.03</v>
       </c>
       <c r="X172">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y172">
         <v>1.65</v>
       </c>
       <c r="Z172">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AA172">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB172">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC172">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AD172">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE172">
         <v>1.02</v>
@@ -28402,7 +28402,7 @@
         <v>2.45</v>
       </c>
       <c r="AG172">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK172">
         <v>1.62</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB173">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28677,49 +28677,49 @@
         <v>3</v>
       </c>
       <c r="P174">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q174">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="R174">
         <v>1.91</v>
       </c>
       <c r="S174">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="T174">
         <v>2.25</v>
       </c>
       <c r="U174">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="V174">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W174">
         <v>1.03</v>
       </c>
       <c r="X174">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y174">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z174">
         <v>2.15</v>
       </c>
       <c r="AA174">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AB174">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC174">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="AD174">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE174">
         <v>1.03</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK174">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28843,7 +28843,7 @@
         <v>3.8</v>
       </c>
       <c r="Q175">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="R175">
         <v>1.68</v>
@@ -28852,31 +28852,31 @@
         <v>1.75</v>
       </c>
       <c r="T175">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="U175">
         <v>4.4</v>
       </c>
       <c r="V175">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W175">
         <v>1.03</v>
       </c>
       <c r="X175">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Y175">
         <v>1.77</v>
       </c>
       <c r="Z175">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AA175">
         <v>3.5</v>
       </c>
       <c r="AB175">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC175">
         <v>6.75</v>
@@ -28888,10 +28888,10 @@
         <v>1.02</v>
       </c>
       <c r="AF175">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AG175">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O177">
         <v>3.25</v>
@@ -29184,31 +29184,31 @@
         <v>3.25</v>
       </c>
       <c r="V177">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W177">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X177">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y177">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z177">
         <v>2.65</v>
       </c>
       <c r="AA177">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB177">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC177">
-        <v>4.49</v>
+        <v>4.3</v>
       </c>
       <c r="AD177">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE177">
         <v>1.05</v>
@@ -29217,7 +29217,7 @@
         <v>2.17</v>
       </c>
       <c r="AG177">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK177">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="O178">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P178">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q178">
         <v>4.5</v>
@@ -29338,10 +29338,10 @@
         <v>2.15</v>
       </c>
       <c r="S178">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T178">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U178">
         <v>2.75</v>
@@ -29362,10 +29362,10 @@
         <v>3.3</v>
       </c>
       <c r="AA178">
+        <v>2.01</v>
+      </c>
+      <c r="AB178">
         <v>1.92</v>
-      </c>
-      <c r="AB178">
-        <v>1.73</v>
       </c>
       <c r="AC178">
         <v>3.4</v>
@@ -29374,13 +29374,13 @@
         <v>1.3</v>
       </c>
       <c r="AE178">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF178">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG178">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
+        <v>1.28</v>
+      </c>
+      <c r="AK178">
         <v>1.21</v>
-      </c>
-      <c r="AK178">
-        <v>1.15</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O179">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P179">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q179">
         <v>2.9</v>
@@ -29501,43 +29501,43 @@
         <v>2.2</v>
       </c>
       <c r="S179">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T179">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U179">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V179">
         <v>1.42</v>
       </c>
       <c r="W179">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X179">
         <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z179">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AA179">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB179">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC179">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AD179">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE179">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF179">
         <v>1.73</v>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK179">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29975,31 +29975,31 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O182">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P182">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q182">
         <v>1.87</v>
       </c>
       <c r="R182">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="S182">
         <v>1.29</v>
       </c>
       <c r="T182">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U182">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V182">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W182">
         <v>1.13</v>
@@ -30014,22 +30014,22 @@
         <v>4.4</v>
       </c>
       <c r="AA182">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB182">
         <v>2.2</v>
       </c>
       <c r="AC182">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD182">
         <v>1.49</v>
       </c>
       <c r="AE182">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF182">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG182">
         <v>1.95</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK182">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30464,31 +30464,31 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O185">
-        <v>4.8</v>
+        <v>5.23</v>
       </c>
       <c r="P185">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="Q185">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R185">
         <v>2.75</v>
       </c>
       <c r="S185">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T185">
         <v>4.8</v>
       </c>
       <c r="U185">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V185">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W185">
         <v>1.22</v>
@@ -30500,28 +30500,28 @@
         <v>1.11</v>
       </c>
       <c r="Z185">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA185">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB185">
         <v>3.05</v>
       </c>
       <c r="AC185">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD185">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AE185">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF185">
         <v>1.4</v>
       </c>
       <c r="AG185">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK185">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30627,49 +30627,49 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="O186">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P186">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q186">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R186">
         <v>2.3</v>
       </c>
       <c r="S186">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T186">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U186">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V186">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W186">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X186">
         <v>1.04</v>
       </c>
       <c r="Y186">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z186">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA186">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB186">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC186">
         <v>2.63</v>
@@ -30678,7 +30678,7 @@
         <v>1.48</v>
       </c>
       <c r="AE186">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF186">
         <v>1.55</v>
@@ -30793,22 +30793,22 @@
         <v>2.2</v>
       </c>
       <c r="O187">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P187">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q187">
         <v>2.75</v>
       </c>
       <c r="R187">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S187">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T187">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U187">
         <v>3.2</v>
@@ -30820,31 +30820,31 @@
         <v>1.03</v>
       </c>
       <c r="X187">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z187">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="AA187">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AB187">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC187">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="AD187">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE187">
         <v>1.05</v>
       </c>
       <c r="AF187">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG187">
         <v>1.8</v>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK187">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30986,7 +30986,7 @@
         <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z188">
         <v>4.33</v>
@@ -31001,16 +31001,16 @@
         <v>2.65</v>
       </c>
       <c r="AD188">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE188">
         <v>1.16</v>
       </c>
       <c r="AF188">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG188">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>1.5</v>
       </c>
       <c r="AG189">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31457,19 +31457,19 @@
         <v>1.94</v>
       </c>
       <c r="S191">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T191">
         <v>2.73</v>
       </c>
       <c r="U191">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="V191">
         <v>1.35</v>
       </c>
       <c r="W191">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X191">
         <v>1.03</v>
@@ -31481,16 +31481,16 @@
         <v>3.1</v>
       </c>
       <c r="AA191">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB191">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC191">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD191">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE191">
         <v>1.06</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O192">
         <v>3.94</v>
@@ -31614,16 +31614,16 @@
         <v>2.25</v>
       </c>
       <c r="Q192">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R192">
         <v>2.3</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T192">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U192">
         <v>2.3</v>
@@ -31632,25 +31632,25 @@
         <v>1.53</v>
       </c>
       <c r="W192">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X192">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y192">
         <v>1.16</v>
       </c>
       <c r="Z192">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA192">
         <v>1.66</v>
       </c>
       <c r="AB192">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC192">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AD192">
         <v>1.5</v>
@@ -31659,7 +31659,7 @@
         <v>1.15</v>
       </c>
       <c r="AF192">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG192">
         <v>2.4</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AK192">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31777,16 +31777,16 @@
         <v>2.3</v>
       </c>
       <c r="Q193">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R193">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S193">
         <v>1.37</v>
       </c>
       <c r="T193">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U193">
         <v>2.75</v>
@@ -31798,7 +31798,7 @@
         <v>1.06</v>
       </c>
       <c r="X193">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y193">
         <v>1.24</v>
@@ -31807,10 +31807,10 @@
         <v>3.34</v>
       </c>
       <c r="AA193">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB193">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC193">
         <v>3.14</v>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AK193">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O194">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="P194">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q194">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="R194">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S194">
         <v>1.29</v>
       </c>
       <c r="T194">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U194">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V194">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W194">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X194">
         <v>1.03</v>
       </c>
       <c r="Y194">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z194">
-        <v>4.74</v>
+        <v>5.3</v>
       </c>
       <c r="AA194">
         <v>1.57</v>
       </c>
       <c r="AB194">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AC194">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD194">
+        <v>1.55</v>
+      </c>
+      <c r="AE194">
+        <v>1.23</v>
+      </c>
+      <c r="AF194">
         <v>1.53</v>
       </c>
-      <c r="AE194">
-        <v>1.18</v>
-      </c>
-      <c r="AF194">
-        <v>1.5</v>
-      </c>
       <c r="AG194">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>1.2</v>
       </c>
       <c r="AK194">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL194">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P4">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB5">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AC5">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
         <v>1.45</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="O18">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="P18">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q18">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>4.6</v>
+        <v>3.49</v>
       </c>
       <c r="AA18">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC18">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>2.99</v>
+        <v>1.94</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="P19">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R19">
+        <v>2.62</v>
+      </c>
+      <c r="S19">
+        <v>1.22</v>
+      </c>
+      <c r="T19">
+        <v>3.55</v>
+      </c>
+      <c r="U19">
         <v>2.2</v>
       </c>
-      <c r="S19">
-        <v>1.35</v>
-      </c>
-      <c r="T19">
-        <v>2.82</v>
-      </c>
-      <c r="U19">
-        <v>2.7</v>
-      </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>3.49</v>
+        <v>4.6</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK19">
-        <v>1.94</v>
+        <v>2.99</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
         <v>2.5</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O31">
         <v>3.32</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="Q32">
         <v>1.85</v>
       </c>
       <c r="R32">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="S32">
         <v>1.22</v>
@@ -5582,7 +5582,7 @@
         <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.9</v>
+        <v>3.37</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -5733,7 +5733,7 @@
         <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
         <v>1.53</v>
@@ -6509,7 +6509,7 @@
         <v>3.84</v>
       </c>
       <c r="P38">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
         <v>3.04</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O50">
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
         <v>1.27</v>
@@ -8483,7 +8483,7 @@
         <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.06</v>
@@ -8498,10 +8498,10 @@
         <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC50">
         <v>2.63</v>
@@ -8532,7 +8532,7 @@
         <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O51">
         <v>4.6</v>
@@ -8634,7 +8634,7 @@
         <v>1.79</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
         <v>1.23</v>
@@ -9802,10 +9802,10 @@
         <v>2.97</v>
       </c>
       <c r="AA58">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AB58">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC58">
         <v>3.99</v>
@@ -10488,7 +10488,7 @@
         <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O64">
         <v>3.5</v>
@@ -10907,7 +10907,7 @@
         <v>3.55</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
         <v>1.73</v>
@@ -10940,7 +10940,7 @@
         <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA65">
         <v>1.66</v>
@@ -10952,13 +10952,13 @@
         <v>2.51</v>
       </c>
       <c r="AD65">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
         <v>2.18</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O79">
-        <v>4.45</v>
+        <v>4.26</v>
       </c>
       <c r="P79">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="Q79">
         <v>1.84</v>
@@ -13358,10 +13358,10 @@
         <v>4.2</v>
       </c>
       <c r="Q80">
+        <v>2.3</v>
+      </c>
+      <c r="R80">
         <v>2.31</v>
-      </c>
-      <c r="R80">
-        <v>2.59</v>
       </c>
       <c r="S80">
         <v>1.24</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="O83">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P83">
         <v>1.38</v>
@@ -13880,7 +13880,7 @@
         <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC83">
         <v>2.25</v>
@@ -14010,16 +14010,16 @@
         <v>2.18</v>
       </c>
       <c r="Q84">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="R84">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="S84">
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U84">
         <v>2.8</v>
@@ -14031,7 +14031,7 @@
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y84">
         <v>1.31</v>
@@ -14040,10 +14040,10 @@
         <v>3.1</v>
       </c>
       <c r="AA84">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB84">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC84">
         <v>3.3</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O105">
         <v>5</v>
       </c>
       <c r="P105">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q105">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R105">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S105">
         <v>1.22</v>
@@ -17445,7 +17445,7 @@
         <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="V105">
         <v>1.67</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AK105">
         <v>2.94</v>
@@ -17593,7 +17593,7 @@
         <v>5.25</v>
       </c>
       <c r="P106">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Q106">
         <v>6.79</v>
@@ -17614,7 +17614,7 @@
         <v>1.78</v>
       </c>
       <c r="W106">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17629,10 +17629,10 @@
         <v>1.36</v>
       </c>
       <c r="AB106">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AC106">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AD106">
         <v>1.79</v>
@@ -18251,7 +18251,7 @@
         <v>1.61</v>
       </c>
       <c r="R110">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S110">
         <v>1.33</v>
@@ -18263,7 +18263,7 @@
         <v>2.63</v>
       </c>
       <c r="V110">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
         <v>1.1</v>
@@ -18272,7 +18272,7 @@
         <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
         <v>3.65</v>
@@ -18284,7 +18284,7 @@
         <v>1.95</v>
       </c>
       <c r="AC110">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD110">
         <v>1.33</v>
@@ -18293,7 +18293,7 @@
         <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AG110">
         <v>1.57</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK110">
         <v>3.3</v>
@@ -18734,10 +18734,10 @@
         <v>3.2</v>
       </c>
       <c r="P113">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q113">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
         <v>2.1</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O131">
         <v>3.62</v>
       </c>
       <c r="P131">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="Q131">
         <v>2.45</v>
@@ -22151,31 +22151,31 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O134">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P134">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q134">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="R134">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S134">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T134">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U134">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="V134">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W134">
         <v>1.13</v>
@@ -22187,19 +22187,19 @@
         <v>1.08</v>
       </c>
       <c r="Z134">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AA134">
         <v>1.33</v>
       </c>
       <c r="AB134">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC134">
         <v>2.11</v>
       </c>
       <c r="AD134">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE134">
         <v>1.23</v>
@@ -22224,7 +22224,7 @@
         <v>1.2</v>
       </c>
       <c r="AK134">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -24273,13 +24273,13 @@
         <v>1.72</v>
       </c>
       <c r="O147">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
         <v>4.4</v>
       </c>
       <c r="Q147">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R147">
         <v>2.1</v>
@@ -24288,7 +24288,7 @@
         <v>1.4</v>
       </c>
       <c r="T147">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U147">
         <v>2.87</v>
@@ -24297,7 +24297,7 @@
         <v>1.33</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X147">
         <v>1.06</v>
@@ -24309,10 +24309,10 @@
         <v>3</v>
       </c>
       <c r="AA147">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB147">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC147">
         <v>3.58</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="O150">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P150">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25251,10 +25251,10 @@
         <v>2.99</v>
       </c>
       <c r="O153">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P153">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q153">
         <v>3.5</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O155">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="Q155">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R155">
         <v>2.15</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T155">
+        <v>2.73</v>
+      </c>
+      <c r="U155">
         <v>2.93</v>
-      </c>
-      <c r="U155">
-        <v>2.98</v>
       </c>
       <c r="V155">
         <v>1.38</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y155">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z155">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA155">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB155">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC155">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD155">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG155">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O156">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P156">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q156">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R156">
         <v>2.15</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T156">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U156">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="V156">
         <v>1.38</v>
       </c>
       <c r="W156">
+        <v>1.05</v>
+      </c>
+      <c r="X156">
+        <v>1.03</v>
+      </c>
+      <c r="Y156">
+        <v>1.28</v>
+      </c>
+      <c r="Z156">
+        <v>3.55</v>
+      </c>
+      <c r="AA156">
+        <v>2.03</v>
+      </c>
+      <c r="AB156">
+        <v>1.8</v>
+      </c>
+      <c r="AC156">
+        <v>3.35</v>
+      </c>
+      <c r="AD156">
+        <v>1.32</v>
+      </c>
+      <c r="AE156">
         <v>1.08</v>
       </c>
-      <c r="X156">
-        <v>1.04</v>
-      </c>
-      <c r="Y156">
-        <v>1.29</v>
-      </c>
-      <c r="Z156">
-        <v>3.5</v>
-      </c>
-      <c r="AA156">
-        <v>1.9</v>
-      </c>
-      <c r="AB156">
-        <v>1.81</v>
-      </c>
-      <c r="AC156">
-        <v>3.45</v>
-      </c>
-      <c r="AD156">
-        <v>1.3</v>
-      </c>
-      <c r="AE156">
-        <v>1.09</v>
-      </c>
       <c r="AF156">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="O157">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P157">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q157">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R157">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S157">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T157">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="U157">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="V157">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W157">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z157">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA157">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="AB157">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC157">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AD157">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE157">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF157">
         <v>2.05</v>
       </c>
       <c r="AG157">
+        <v>1.67</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
+        <v>1.22</v>
+      </c>
+      <c r="AK157">
         <v>1.7</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.21</v>
-      </c>
-      <c r="AK157">
-        <v>1.65</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="O158">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P158">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q158">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="R158">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S158">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T158">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U158">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="V158">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W158">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X158">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y158">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z158">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AA158">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AB158">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC158">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="AD158">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE158">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF158">
         <v>2.05</v>
       </c>
       <c r="AG158">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK158">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28997,19 +28997,19 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O176">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P176">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="Q176">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R176">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S176">
         <v>1.18</v>
@@ -29018,10 +29018,10 @@
         <v>4.4</v>
       </c>
       <c r="U176">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="V176">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="W176">
         <v>1.22</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK176">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30159,7 +30159,7 @@
         <v>2.53</v>
       </c>
       <c r="U183">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V183">
         <v>1.36</v>
@@ -30192,10 +30192,10 @@
         <v>1.08</v>
       </c>
       <c r="AF183">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG183">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30310,10 +30310,10 @@
         <v>3.25</v>
       </c>
       <c r="Q184">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R184">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S184">
         <v>1.5</v>
@@ -30346,7 +30346,7 @@
         <v>1.47</v>
       </c>
       <c r="AC184">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD184">
         <v>1.11</v>
@@ -31279,7 +31279,7 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O190">
         <v>3.3</v>
@@ -31300,10 +31300,10 @@
         <v>3.2</v>
       </c>
       <c r="U190">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V190">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
         <v>1.11</v>
@@ -31318,22 +31318,22 @@
         <v>3.7</v>
       </c>
       <c r="AA190">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB190">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC190">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD190">
         <v>1.38</v>
       </c>
       <c r="AE190">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF190">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG190">
         <v>2.2</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O4">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="AA4">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AC5">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD5">
         <v>1.45</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>2.7</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S6">
         <v>1.3</v>
@@ -1311,10 +1311,10 @@
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA6">
         <v>1.7</v>
@@ -1332,13 +1332,13 @@
         <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
         <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
         <v>1.62</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
         <v>1.42</v>
@@ -1658,7 +1658,7 @@
         <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
         <v>1.25</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
         <v>2.98</v>
@@ -1818,7 +1818,7 @@
         <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC9">
         <v>4.76</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
+        <v>3.25</v>
+      </c>
+      <c r="O10">
         <v>3.2</v>
       </c>
-      <c r="O10">
-        <v>3.15</v>
-      </c>
       <c r="P10">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1957,7 +1957,7 @@
         <v>1.42</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U10">
         <v>2.88</v>
@@ -1975,10 +1975,10 @@
         <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P12">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S12">
         <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V12">
         <v>1.55</v>
@@ -2298,7 +2298,7 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
         <v>4.65</v>
@@ -2307,19 +2307,19 @@
         <v>1.65</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC12">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
         <v>2.38</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q23">
         <v>2.1</v>
@@ -4115,7 +4115,7 @@
         <v>1.4</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O24">
         <v>3.6</v>
@@ -4236,13 +4236,13 @@
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V24">
         <v>1.55</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
         <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AD24">
         <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
         <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.68</v>
+      </c>
+      <c r="O25">
+        <v>3.6</v>
+      </c>
+      <c r="P25">
+        <v>4.4</v>
+      </c>
+      <c r="Q25">
+        <v>2.2</v>
+      </c>
+      <c r="R25">
+        <v>2.4</v>
+      </c>
+      <c r="S25">
+        <v>1.22</v>
+      </c>
+      <c r="T25">
+        <v>3.2</v>
+      </c>
+      <c r="U25">
         <v>2.3</v>
       </c>
-      <c r="O25">
-        <v>3.5</v>
-      </c>
-      <c r="P25">
-        <v>2.6</v>
-      </c>
-      <c r="Q25">
-        <v>2.9</v>
-      </c>
-      <c r="R25">
-        <v>2.3</v>
-      </c>
-      <c r="S25">
-        <v>1.25</v>
-      </c>
-      <c r="T25">
-        <v>3.28</v>
-      </c>
-      <c r="U25">
-        <v>2.33</v>
-      </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
+        <v>2.35</v>
+      </c>
+      <c r="AC25">
+        <v>2.42</v>
+      </c>
+      <c r="AD25">
+        <v>1.53</v>
+      </c>
+      <c r="AE25">
+        <v>1.18</v>
+      </c>
+      <c r="AF25">
+        <v>1.53</v>
+      </c>
+      <c r="AG25">
         <v>2.3</v>
       </c>
-      <c r="AC25">
-        <v>2.55</v>
-      </c>
-      <c r="AD25">
-        <v>1.44</v>
-      </c>
-      <c r="AE25">
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.2</v>
       </c>
-      <c r="AF25">
-        <v>1.5</v>
-      </c>
-      <c r="AG25">
-        <v>2.55</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.22</v>
-      </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>4.15</v>
+        <v>2.53</v>
       </c>
       <c r="Q26">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
         <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V26">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AD26">
+        <v>1.44</v>
+      </c>
+      <c r="AE26">
+        <v>1.22</v>
+      </c>
+      <c r="AF26">
+        <v>1.5</v>
+      </c>
+      <c r="AG26">
+        <v>2.55</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.22</v>
+      </c>
+      <c r="AK26">
         <v>1.53</v>
-      </c>
-      <c r="AE26">
-        <v>1.18</v>
-      </c>
-      <c r="AF26">
-        <v>1.53</v>
-      </c>
-      <c r="AG26">
-        <v>2.3</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.2</v>
-      </c>
-      <c r="AK26">
-        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="P27">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="Q27">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
         <v>2.19</v>
@@ -4749,10 +4749,10 @@
         <v>3.9</v>
       </c>
       <c r="AA27">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB27">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
         <v>2.81</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O34">
         <v>5.3</v>
@@ -5863,7 +5863,7 @@
         <v>1.75</v>
       </c>
       <c r="R34">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S34">
         <v>1.2</v>
@@ -5875,10 +5875,10 @@
         <v>1.96</v>
       </c>
       <c r="V34">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5896,16 +5896,16 @@
         <v>3</v>
       </c>
       <c r="AC34">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AD34">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
         <v>2.45</v>
@@ -5924,7 +5924,7 @@
         <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>4.75</v>
+        <v>4.93</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -6035,40 +6035,40 @@
         <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>1.28</v>
+      </c>
+      <c r="Z35">
+        <v>3.25</v>
+      </c>
+      <c r="AA35">
+        <v>2</v>
+      </c>
+      <c r="AB35">
+        <v>1.73</v>
+      </c>
+      <c r="AC35">
+        <v>3.45</v>
+      </c>
+      <c r="AD35">
+        <v>1.25</v>
+      </c>
+      <c r="AE35">
         <v>1.06</v>
       </c>
-      <c r="Y35">
-        <v>1.33</v>
-      </c>
-      <c r="Z35">
-        <v>3.1</v>
-      </c>
-      <c r="AA35">
-        <v>2.05</v>
-      </c>
-      <c r="AB35">
-        <v>1.7</v>
-      </c>
-      <c r="AC35">
-        <v>3.5</v>
-      </c>
-      <c r="AD35">
-        <v>1.29</v>
-      </c>
-      <c r="AE35">
-        <v>1.05</v>
-      </c>
       <c r="AF35">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG35">
         <v>1.85</v>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="O36">
-        <v>3.15</v>
+        <v>3.51</v>
       </c>
       <c r="P36">
         <v>2.39</v>
@@ -6192,7 +6192,7 @@
         <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
         <v>3</v>
@@ -6201,7 +6201,7 @@
         <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O37">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
         <v>2.67</v>
@@ -6367,7 +6367,7 @@
         <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.05</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O39">
         <v>3.6</v>
@@ -6675,7 +6675,7 @@
         <v>2.1</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="R39">
         <v>2.14</v>
@@ -6684,7 +6684,7 @@
         <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U39">
         <v>2.6</v>
@@ -6702,28 +6702,28 @@
         <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB39">
         <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
         <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6832,28 +6832,28 @@
         <v>1.25</v>
       </c>
       <c r="O40">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="P40">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q40">
         <v>1.57</v>
       </c>
       <c r="R40">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
         <v>4.8</v>
       </c>
       <c r="U40">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V40">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W40">
         <v>1.2</v>
@@ -6880,7 +6880,7 @@
         <v>1.9</v>
       </c>
       <c r="AE40">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
         <v>1.68</v>
@@ -6902,7 +6902,7 @@
         <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.17</v>
       </c>
       <c r="T41">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U41">
         <v>1.95</v>
@@ -7019,7 +7019,7 @@
         <v>1.81</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7158,10 +7158,10 @@
         <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -7173,7 +7173,7 @@
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
         <v>2.2</v>
@@ -7194,13 +7194,13 @@
         <v>4.35</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB42">
         <v>2.22</v>
       </c>
       <c r="AC42">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD42">
         <v>1.5</v>
@@ -7348,7 +7348,7 @@
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
@@ -7369,13 +7369,13 @@
         <v>1.29</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AG43">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
         <v>3.18</v>
@@ -7535,10 +7535,10 @@
         <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>1.34</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U47">
         <v>2.7</v>
@@ -8018,7 +8018,7 @@
         <v>3.5</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
         <v>1.05</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
         <v>3.05</v>
       </c>
       <c r="P52">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q52">
         <v>3.2</v>
@@ -8827,13 +8827,13 @@
         <v>2.33</v>
       </c>
       <c r="AB52">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC52">
         <v>4.36</v>
       </c>
       <c r="AD52">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE52">
         <v>1.02</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="O56">
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -9452,28 +9452,28 @@
         <v>2.46</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
         <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="AA56">
         <v>1.51</v>
@@ -9482,19 +9482,19 @@
         <v>2.55</v>
       </c>
       <c r="AC56">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD56">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE56">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF56">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AK56">
         <v>1.2</v>
@@ -9618,13 +9618,13 @@
         <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U57">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
         <v>1.06</v>
@@ -9639,7 +9639,7 @@
         <v>2.9</v>
       </c>
       <c r="AA57">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AB57">
         <v>1.83</v>
@@ -9772,16 +9772,16 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="R58">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
         <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U58">
         <v>3</v>
@@ -9793,28 +9793,28 @@
         <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y58">
         <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA58">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB58">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC58">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="AD58">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE58">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
         <v>1.92</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O60">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="Q60">
         <v>3</v>
@@ -10116,7 +10116,7 @@
         <v>1.36</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
         <v>1.06</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK60">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>2.05</v>
       </c>
       <c r="Q62">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R62">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S62">
         <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V62">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA62">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB62">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AC62">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AD62">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF62">
         <v>1.53</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O63">
         <v>3.55</v>
@@ -10590,28 +10590,28 @@
         <v>3.12</v>
       </c>
       <c r="R63">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U63">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="V63">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
         <v>4.8</v>
@@ -10623,7 +10623,7 @@
         <v>2.4</v>
       </c>
       <c r="AC63">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
         <v>1.44</v>
@@ -10635,7 +10635,7 @@
         <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK63">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="R66">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
         <v>1.39</v>
@@ -11103,7 +11103,7 @@
         <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA66">
         <v>1.92</v>
@@ -11140,7 +11140,7 @@
         <v>1.42</v>
       </c>
       <c r="AK66">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O71">
         <v>4.8</v>
       </c>
       <c r="P71">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q71">
         <v>1.8</v>
@@ -11897,16 +11897,16 @@
         <v>2.7</v>
       </c>
       <c r="S71">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="U71">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V71">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W71">
         <v>1.2</v>
@@ -11918,28 +11918,28 @@
         <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.75</v>
+        <v>6.21</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB71">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC71">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD71">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE71">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF71">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O73">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q73">
         <v>2.41</v>
@@ -12226,22 +12226,22 @@
         <v>1.21</v>
       </c>
       <c r="T73">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W73">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z73">
         <v>5.4</v>
@@ -12259,13 +12259,13 @@
         <v>1.66</v>
       </c>
       <c r="AE73">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF73">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG73">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="O76">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12718,7 +12718,7 @@
         <v>2.5</v>
       </c>
       <c r="U76">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V76">
         <v>1.3</v>
@@ -12730,10 +12730,10 @@
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z76">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA76">
         <v>2.33</v>
@@ -12742,7 +12742,7 @@
         <v>1.61</v>
       </c>
       <c r="AC76">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD76">
         <v>1.19</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O81">
         <v>3.5</v>
       </c>
       <c r="P81">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q81">
         <v>3.65</v>
@@ -13527,10 +13527,10 @@
         <v>2.18</v>
       </c>
       <c r="S81">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T81">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U81">
         <v>2.65</v>
@@ -13548,7 +13548,7 @@
         <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA81">
         <v>1.8</v>
@@ -13557,19 +13557,19 @@
         <v>2</v>
       </c>
       <c r="AC81">
-        <v>2.72</v>
+        <v>3.02</v>
       </c>
       <c r="AD81">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE81">
         <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG81">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
         <v>1.36</v>
@@ -13681,7 +13681,7 @@
         <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q82">
         <v>3.3</v>
@@ -13708,19 +13708,19 @@
         <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z82">
         <v>4.1</v>
       </c>
       <c r="AA82">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB82">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC82">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AD82">
         <v>1.4</v>
@@ -13729,10 +13729,10 @@
         <v>1.17</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="O83">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P83">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -13886,7 +13886,7 @@
         <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE83">
         <v>1.19</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="AK83">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P84">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q84">
         <v>3.62</v>
@@ -14019,7 +14019,7 @@
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U84">
         <v>2.8</v>
@@ -14031,22 +14031,22 @@
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y84">
         <v>1.31</v>
       </c>
       <c r="Z84">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA84">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC84">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD84">
         <v>1.25</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P85">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -14237,7 +14237,7 @@
         <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="O86">
         <v>3.45</v>
       </c>
       <c r="P86">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
         <v>2.81</v>
@@ -14345,7 +14345,7 @@
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U86">
         <v>2.29</v>
@@ -14493,7 +14493,7 @@
         <v>2.8</v>
       </c>
       <c r="O87">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
         <v>2.11</v>
@@ -14529,7 +14529,7 @@
         <v>7</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB87">
         <v>2.96</v>
@@ -14541,7 +14541,7 @@
         <v>1.85</v>
       </c>
       <c r="AE87">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF87">
         <v>1.32</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK87">
         <v>1.35</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O88">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q88">
         <v>2.4</v>
@@ -14680,7 +14680,7 @@
         <v>1.75</v>
       </c>
       <c r="W88">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14695,38 +14695,38 @@
         <v>1.33</v>
       </c>
       <c r="AB88">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AC88">
         <v>1.99</v>
       </c>
       <c r="AD88">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE88">
         <v>1.27</v>
       </c>
       <c r="AF88">
+        <v>1.3</v>
+      </c>
+      <c r="AG88">
+        <v>3.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.33</v>
       </c>
-      <c r="AG88">
-        <v>3</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.25</v>
-      </c>
       <c r="AK88">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="O89">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
       </c>
       <c r="R89">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="S89">
         <v>1.12</v>
       </c>
       <c r="T89">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="U89">
         <v>1.7</v>
@@ -14849,31 +14849,31 @@
         <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z89">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA89">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AB89">
         <v>4.4</v>
       </c>
       <c r="AC89">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD89">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AE89">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG89">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14988,10 +14988,10 @@
         <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
         <v>1.36</v>
@@ -15012,10 +15012,10 @@
         <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z90">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA90">
         <v>1.81</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
         <v>1.41</v>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O91">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="P91">
         <v>2.6</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O92">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
         <v>2.7</v>
@@ -15338,16 +15338,16 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
         <v>4</v>
       </c>
       <c r="AA92">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB92">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC92">
         <v>2.59</v>
@@ -15378,7 +15378,7 @@
         <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,68 +15464,68 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="O93">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P93">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="Q93">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S93">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="T93">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="U93">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="V93">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y93">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="Z93">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA93">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="AB93">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AC93">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD93">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE93">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG93">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK93">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G94">
@@ -15627,68 +15627,68 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N94">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P94">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q94">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="R94">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="S94">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="U94">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V94">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W94">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AB94">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AC94">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD94">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF94">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG94">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AK94">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15812,7 +15812,7 @@
         <v>1.22</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U95">
         <v>2.08</v>
@@ -15821,34 +15821,34 @@
         <v>1.66</v>
       </c>
       <c r="W95">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA95">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB95">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC95">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AD95">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG95">
         <v>2.8</v>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O96">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
         <v>1.8</v>
@@ -15990,7 +15990,7 @@
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
         <v>3.3</v>
@@ -16005,7 +16005,7 @@
         <v>3.35</v>
       </c>
       <c r="AD96">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE96">
         <v>1.08</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O97">
         <v>3.3</v>
       </c>
       <c r="P97">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="Q97">
         <v>2.68</v>
@@ -16135,10 +16135,10 @@
         <v>2.07</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U97">
         <v>2.79</v>
@@ -16147,7 +16147,7 @@
         <v>1.36</v>
       </c>
       <c r="W97">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
         <v>1.01</v>
@@ -16156,7 +16156,7 @@
         <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA97">
         <v>1.89</v>
@@ -16177,7 +16177,7 @@
         <v>1.71</v>
       </c>
       <c r="AG97">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O98">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P98">
         <v>2.45</v>
@@ -16295,7 +16295,7 @@
         <v>3.3</v>
       </c>
       <c r="R98">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -16307,10 +16307,10 @@
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W98">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
         <v>1.01</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O101">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P101">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q101">
         <v>2.7</v>
@@ -16805,10 +16805,10 @@
         <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z101">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="AA101">
         <v>1.95</v>
@@ -16817,19 +16817,19 @@
         <v>1.78</v>
       </c>
       <c r="AC101">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AD101">
         <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG101">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O102">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB102">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O107">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
         <v>2.8</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="O109">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P109">
         <v>1.73</v>
@@ -18103,7 +18103,7 @@
         <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X109">
         <v>1.01</v>
@@ -18112,7 +18112,7 @@
         <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA109">
         <v>1.57</v>
@@ -18121,13 +18121,13 @@
         <v>2.38</v>
       </c>
       <c r="AC109">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AD109">
         <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
         <v>1.57</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="O110">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="P110">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q110">
         <v>1.61</v>
@@ -18275,10 +18275,10 @@
         <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA110">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB110">
         <v>1.95</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK110">
         <v>3.3</v>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O114">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
         <v>4.33</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
+        <v>3.25</v>
+      </c>
+      <c r="O117">
         <v>3.1</v>
       </c>
-      <c r="O117">
-        <v>3.2</v>
-      </c>
       <c r="P117">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -19395,10 +19395,10 @@
         <v>2.05</v>
       </c>
       <c r="S117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T117">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U117">
         <v>2.81</v>
@@ -19413,16 +19413,16 @@
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z117">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA117">
         <v>1.98</v>
       </c>
       <c r="AB117">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC117">
         <v>3.45</v>
@@ -19431,13 +19431,13 @@
         <v>1.26</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF117">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG117">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,19 +19543,19 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.7</v>
+        <v>3.33</v>
       </c>
       <c r="O118">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P118">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q118">
         <v>4.48</v>
       </c>
       <c r="R118">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S118">
         <v>1.46</v>
@@ -19576,19 +19576,19 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z118">
         <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB118">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC118">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="AD118">
         <v>1.22</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O123">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P123">
         <v>2.15</v>
@@ -20388,7 +20388,7 @@
         <v>1.03</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y123">
         <v>1.36</v>
@@ -20409,7 +20409,7 @@
         <v>1.19</v>
       </c>
       <c r="AE123">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
         <v>1.85</v>
@@ -20527,13 +20527,13 @@
         <v>3.15</v>
       </c>
       <c r="P124">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="Q124">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S124">
         <v>1.44</v>
@@ -20551,7 +20551,7 @@
         <v>1.02</v>
       </c>
       <c r="X124">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
         <v>1.35</v>
@@ -20563,22 +20563,22 @@
         <v>2.3</v>
       </c>
       <c r="AB124">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AC124">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD124">
         <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG124">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>2.3</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P126">
         <v>3</v>
@@ -20874,7 +20874,7 @@
         <v>1.33</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X126">
         <v>1.07</v>
@@ -20883,19 +20883,19 @@
         <v>1.38</v>
       </c>
       <c r="Z126">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA126">
         <v>2.13</v>
       </c>
       <c r="AB126">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC126">
         <v>4.33</v>
       </c>
       <c r="AD126">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
@@ -21013,19 +21013,19 @@
         <v>1.6</v>
       </c>
       <c r="O127">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="P127">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q127">
         <v>2.19</v>
       </c>
       <c r="R127">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="S127">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T127">
         <v>2.75</v>
@@ -21034,25 +21034,25 @@
         <v>2.89</v>
       </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AA127">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB127">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC127">
         <v>3.8</v>
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O128">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P128">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q128">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R128">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S128">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T128">
         <v>2.62</v>
       </c>
       <c r="U128">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V128">
         <v>1.33</v>
       </c>
       <c r="W128">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X128">
         <v>1.05</v>
@@ -21218,19 +21218,19 @@
         <v>1.7</v>
       </c>
       <c r="AC128">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AD128">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE128">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF128">
         <v>1.91</v>
       </c>
       <c r="AG128">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21339,13 +21339,13 @@
         <v>1.76</v>
       </c>
       <c r="O129">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P129">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q129">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R129">
         <v>2.36</v>
@@ -21363,7 +21363,7 @@
         <v>1.44</v>
       </c>
       <c r="W129">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X129">
         <v>1.02</v>
@@ -21393,7 +21393,7 @@
         <v>1.8</v>
       </c>
       <c r="AG129">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,28 +21499,28 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O130">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
         <v>3.5</v>
       </c>
       <c r="Q130">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R130">
         <v>2.16</v>
       </c>
       <c r="S130">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T130">
         <v>2.47</v>
       </c>
       <c r="U130">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="V130">
         <v>1.34</v>
@@ -21535,10 +21535,10 @@
         <v>1.36</v>
       </c>
       <c r="Z130">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AA130">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB130">
         <v>1.74</v>
@@ -21556,7 +21556,7 @@
         <v>1.85</v>
       </c>
       <c r="AG130">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21825,10 +21825,10 @@
         </is>
       </c>
       <c r="N132">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="O132">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
         <v>2.2</v>
@@ -21988,28 +21988,28 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="Q133">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R133">
         <v>2.25</v>
       </c>
       <c r="S133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T133">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U133">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="V133">
         <v>1.51</v>
@@ -22024,7 +22024,7 @@
         <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA133">
         <v>1.8</v>
@@ -22045,7 +22045,7 @@
         <v>1.62</v>
       </c>
       <c r="AG133">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>3.58</v>
       </c>
       <c r="U134">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="V134">
         <v>1.64</v>
@@ -22184,13 +22184,13 @@
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA134">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB134">
         <v>2.49</v>
@@ -22205,10 +22205,10 @@
         <v>1.23</v>
       </c>
       <c r="AF134">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG134">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.6</v>
+        <v>4.28</v>
       </c>
       <c r="O137">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q137">
         <v>4.5</v>
@@ -22655,34 +22655,34 @@
         <v>2.23</v>
       </c>
       <c r="S137">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T137">
         <v>3.05</v>
       </c>
       <c r="U137">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V137">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
         <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z137">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA137">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB137">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC137">
         <v>2.66</v>
@@ -22694,10 +22694,10 @@
         <v>1.13</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23292,43 +23292,43 @@
         </is>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O141">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P141">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA141">
         <v>2.37</v>
@@ -23337,19 +23337,19 @@
         <v>1.53</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="O142">
         <v>2.8</v>
       </c>
       <c r="P142">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA142">
         <v>2.37</v>
       </c>
       <c r="AB142">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,43 +23618,43 @@
         </is>
       </c>
       <c r="N143">
+        <v>1.84</v>
+      </c>
+      <c r="O143">
+        <v>3.05</v>
+      </c>
+      <c r="P143">
+        <v>3.96</v>
+      </c>
+      <c r="Q143">
+        <v>2.55</v>
+      </c>
+      <c r="R143">
         <v>1.83</v>
       </c>
-      <c r="O143">
-        <v>2.9</v>
-      </c>
-      <c r="P143">
-        <v>4.61</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA143">
         <v>2.5</v>
@@ -23663,19 +23663,19 @@
         <v>1.5</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,31 +23781,31 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O144">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P144">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q144">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R144">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S144">
         <v>1.22</v>
       </c>
       <c r="T144">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U144">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="V144">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W144">
         <v>1.14</v>
@@ -23814,7 +23814,7 @@
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z144">
         <v>4.92</v>
@@ -23823,19 +23823,19 @@
         <v>1.54</v>
       </c>
       <c r="AB144">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AC144">
         <v>2.29</v>
       </c>
       <c r="AD144">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE144">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF144">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG144">
         <v>2.4</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK144">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,10 +23944,10 @@
         </is>
       </c>
       <c r="N145">
-        <v>4.03</v>
+        <v>4.49</v>
       </c>
       <c r="O145">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P145">
         <v>1.79</v>
@@ -24001,7 +24001,7 @@
         <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="O146">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P146">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="Q146">
         <v>2.47</v>
@@ -24122,49 +24122,49 @@
         <v>2.13</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T146">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U146">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V146">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
         <v>3.8</v>
       </c>
       <c r="AA146">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC146">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD146">
         <v>1.36</v>
       </c>
       <c r="AE146">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF146">
         <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24270,16 +24270,16 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
         <v>4.4</v>
       </c>
       <c r="Q147">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R147">
         <v>2.1</v>
@@ -24288,13 +24288,13 @@
         <v>1.4</v>
       </c>
       <c r="T147">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="U147">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="V147">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W147">
         <v>1.03</v>
@@ -24303,10 +24303,10 @@
         <v>1.06</v>
       </c>
       <c r="Y147">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z147">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA147">
         <v>1.92</v>
@@ -24315,16 +24315,16 @@
         <v>1.76</v>
       </c>
       <c r="AC147">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AD147">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE147">
         <v>1.04</v>
       </c>
       <c r="AF147">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG147">
         <v>1.73</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK147">
         <v>2</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="O150">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P150">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O151">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P151">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="O152">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P152">
         <v>2.45</v>
       </c>
       <c r="Q152">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R152">
         <v>2.1</v>
@@ -25112,7 +25112,7 @@
         <v>1.4</v>
       </c>
       <c r="W152">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X152">
         <v>1.03</v>
@@ -25142,7 +25142,7 @@
         <v>1.76</v>
       </c>
       <c r="AG152">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK152">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O155">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P155">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q155">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R155">
         <v>2.15</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T155">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U155">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="V155">
         <v>1.38</v>
       </c>
       <c r="W155">
+        <v>1.05</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.28</v>
+      </c>
+      <c r="Z155">
+        <v>3.55</v>
+      </c>
+      <c r="AA155">
+        <v>2.03</v>
+      </c>
+      <c r="AB155">
+        <v>1.8</v>
+      </c>
+      <c r="AC155">
+        <v>3.35</v>
+      </c>
+      <c r="AD155">
+        <v>1.32</v>
+      </c>
+      <c r="AE155">
         <v>1.08</v>
       </c>
-      <c r="X155">
-        <v>1.04</v>
-      </c>
-      <c r="Y155">
-        <v>1.29</v>
-      </c>
-      <c r="Z155">
-        <v>3.5</v>
-      </c>
-      <c r="AA155">
-        <v>1.9</v>
-      </c>
-      <c r="AB155">
-        <v>1.81</v>
-      </c>
-      <c r="AC155">
-        <v>3.45</v>
-      </c>
-      <c r="AD155">
-        <v>1.3</v>
-      </c>
-      <c r="AE155">
-        <v>1.09</v>
-      </c>
       <c r="AF155">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O156">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="Q156">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R156">
         <v>2.15</v>
       </c>
       <c r="S156">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
+        <v>2.73</v>
+      </c>
+      <c r="U156">
         <v>2.93</v>
-      </c>
-      <c r="U156">
-        <v>2.98</v>
       </c>
       <c r="V156">
         <v>1.38</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z156">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA156">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB156">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC156">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD156">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE156">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,10 +25900,10 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O157">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P157">
         <v>3.2</v>
@@ -25915,13 +25915,13 @@
         <v>1.95</v>
       </c>
       <c r="S157">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T157">
         <v>2.29</v>
       </c>
       <c r="U157">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V157">
         <v>1.24</v>
@@ -25945,7 +25945,7 @@
         <v>1.53</v>
       </c>
       <c r="AC157">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="AD157">
         <v>1.14</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK157">
         <v>1.7</v>
@@ -26063,25 +26063,25 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O158">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P158">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q158">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="R158">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S158">
         <v>1.55</v>
       </c>
       <c r="T158">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="U158">
         <v>3.7</v>
@@ -26111,13 +26111,13 @@
         <v>4.65</v>
       </c>
       <c r="AD158">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE158">
         <v>1</v>
       </c>
       <c r="AF158">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG158">
         <v>1.7</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK158">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26229,7 +26229,7 @@
         <v>2.45</v>
       </c>
       <c r="O159">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
         <v>2.55</v>
@@ -26299,7 +26299,7 @@
         <v>1.29</v>
       </c>
       <c r="AK159">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26413,7 +26413,7 @@
         <v>1.85</v>
       </c>
       <c r="V160">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W160">
         <v>1.22</v>
@@ -26443,10 +26443,10 @@
         <v>1.33</v>
       </c>
       <c r="AF160">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG160">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26561,52 +26561,52 @@
         <v>2.53</v>
       </c>
       <c r="Q161">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="R161">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S161">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="U161">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V161">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W161">
         <v>1.03</v>
       </c>
       <c r="X161">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z161">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AA161">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB161">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC161">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AD161">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE161">
         <v>1.03</v>
       </c>
       <c r="AF161">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG161">
         <v>1.8</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK161">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,16 +26715,16 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O162">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P162">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q162">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="R162">
         <v>2.15</v>
@@ -26736,7 +26736,7 @@
         <v>2.63</v>
       </c>
       <c r="U162">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V162">
         <v>1.5</v>
@@ -26769,10 +26769,10 @@
         <v>1.15</v>
       </c>
       <c r="AF162">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG162">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK162">
         <v>2.1</v>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O163">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P163">
         <v>5.95</v>
@@ -26896,7 +26896,7 @@
         <v>1.44</v>
       </c>
       <c r="T163">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U163">
         <v>3</v>
@@ -26917,7 +26917,7 @@
         <v>2.5</v>
       </c>
       <c r="AA163">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB163">
         <v>1.55</v>
@@ -26951,7 +26951,7 @@
         <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27210,10 +27210,10 @@
         <v>3.2</v>
       </c>
       <c r="P165">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="Q165">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="R165">
         <v>2</v>
@@ -27228,7 +27228,7 @@
         <v>3.24</v>
       </c>
       <c r="V165">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W165">
         <v>1.03</v>
@@ -27243,7 +27243,7 @@
         <v>2.7</v>
       </c>
       <c r="AA165">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AB165">
         <v>1.57</v>
@@ -27255,13 +27255,13 @@
         <v>1.22</v>
       </c>
       <c r="AE165">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF165">
         <v>1.83</v>
       </c>
       <c r="AG165">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>1.33</v>
       </c>
       <c r="AK165">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27367,7 +27367,7 @@
         </is>
       </c>
       <c r="N166">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O166">
         <v>3.3</v>
@@ -27376,7 +27376,7 @@
         <v>1.8</v>
       </c>
       <c r="Q166">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="R166">
         <v>2.2</v>
@@ -27388,10 +27388,10 @@
         <v>2.74</v>
       </c>
       <c r="U166">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V166">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W166">
         <v>1.08</v>
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O167">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P167">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="Q167">
         <v>2.26</v>
       </c>
       <c r="R167">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S167">
         <v>1.36</v>
@@ -27566,16 +27566,16 @@
         <v>1.26</v>
       </c>
       <c r="Z167">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA167">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB167">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC167">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="AD167">
         <v>1.32</v>
@@ -27587,7 +27587,7 @@
         <v>1.83</v>
       </c>
       <c r="AG167">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O169">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P169">
-        <v>4.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q169">
         <v>2.35</v>
@@ -28022,16 +28022,16 @@
         <v>1.58</v>
       </c>
       <c r="O170">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P170">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q170">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R170">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S170">
         <v>1.39</v>
@@ -28040,43 +28040,43 @@
         <v>2.96</v>
       </c>
       <c r="U170">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V170">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W170">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X170">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y170">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z170">
         <v>3.35</v>
       </c>
       <c r="AA170">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB170">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC170">
         <v>3.4</v>
       </c>
       <c r="AD170">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE170">
         <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG170">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>1.15</v>
       </c>
       <c r="AK170">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O171">
+        <v>2.6</v>
+      </c>
+      <c r="P171">
         <v>2.7</v>
-      </c>
-      <c r="P171">
-        <v>2.59</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28348,10 +28348,10 @@
         <v>2.15</v>
       </c>
       <c r="O172">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P172">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q172">
         <v>2.78</v>
@@ -28384,7 +28384,7 @@
         <v>2.11</v>
       </c>
       <c r="AA172">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB172">
         <v>1.31</v>
@@ -28677,7 +28677,7 @@
         <v>3</v>
       </c>
       <c r="P174">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="Q174">
         <v>2.58</v>
@@ -28689,7 +28689,7 @@
         <v>1.6</v>
       </c>
       <c r="T174">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U174">
         <v>3.9</v>
@@ -28719,7 +28719,7 @@
         <v>5.65</v>
       </c>
       <c r="AD174">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE174">
         <v>1.03</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="O175">
         <v>2.75</v>
       </c>
       <c r="P175">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q175">
         <v>2.76</v>
@@ -28867,13 +28867,13 @@
         <v>1.17</v>
       </c>
       <c r="Y175">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z175">
         <v>1.99</v>
       </c>
       <c r="AA175">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AB175">
         <v>1.29</v>
@@ -28885,7 +28885,7 @@
         <v>1.04</v>
       </c>
       <c r="AE175">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF175">
         <v>2.45</v>
@@ -28997,19 +28997,19 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O176">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P176">
-        <v>6.5</v>
+        <v>7.42</v>
       </c>
       <c r="Q176">
         <v>1.76</v>
       </c>
       <c r="R176">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="S176">
         <v>1.18</v>
@@ -29033,7 +29033,7 @@
         <v>1.07</v>
       </c>
       <c r="Z176">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA176">
         <v>1.34</v>
@@ -29045,10 +29045,10 @@
         <v>1.87</v>
       </c>
       <c r="AD176">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE176">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF176">
         <v>1.57</v>
@@ -29208,7 +29208,7 @@
         <v>4.3</v>
       </c>
       <c r="AD177">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE177">
         <v>1.05</v>
@@ -29217,7 +29217,7 @@
         <v>2.17</v>
       </c>
       <c r="AG177">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK177">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29649,43 +29649,43 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O180">
+        <v>2.9</v>
+      </c>
+      <c r="P180">
+        <v>3.7</v>
+      </c>
+      <c r="Q180">
         <v>2.75</v>
       </c>
-      <c r="P180">
-        <v>3.75</v>
-      </c>
-      <c r="Q180">
-        <v>2.81</v>
-      </c>
       <c r="R180">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S180">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T180">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U180">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V180">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W180">
         <v>1.04</v>
       </c>
       <c r="X180">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y180">
         <v>1.53</v>
       </c>
       <c r="Z180">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AA180">
         <v>2.67</v>
@@ -29694,19 +29694,19 @@
         <v>1.43</v>
       </c>
       <c r="AC180">
-        <v>5.75</v>
+        <v>4.35</v>
       </c>
       <c r="AD180">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE180">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF180">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG180">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>1.18</v>
       </c>
       <c r="AK180">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,37 +29812,37 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O181">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P181">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q181">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R181">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S181">
+        <v>1.39</v>
+      </c>
+      <c r="T181">
+        <v>2.63</v>
+      </c>
+      <c r="U181">
+        <v>2.7</v>
+      </c>
+      <c r="V181">
         <v>1.4</v>
-      </c>
-      <c r="T181">
-        <v>2.75</v>
-      </c>
-      <c r="U181">
-        <v>2.87</v>
-      </c>
-      <c r="V181">
-        <v>1.37</v>
       </c>
       <c r="W181">
         <v>1.05</v>
       </c>
       <c r="X181">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y181">
         <v>1.31</v>
@@ -29851,7 +29851,7 @@
         <v>3.25</v>
       </c>
       <c r="AA181">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB181">
         <v>1.75</v>
@@ -29866,10 +29866,10 @@
         <v>1.06</v>
       </c>
       <c r="AF181">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG181">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>1.4</v>
       </c>
       <c r="AK181">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O182">
         <v>4.2</v>
@@ -29984,7 +29984,7 @@
         <v>5.5</v>
       </c>
       <c r="Q182">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R182">
         <v>2.22</v>
@@ -30048,7 +30048,7 @@
         <v>1.17</v>
       </c>
       <c r="AK182">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30171,25 +30171,25 @@
         <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z183">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA183">
         <v>1.91</v>
       </c>
       <c r="AB183">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC183">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD183">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE183">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF183">
         <v>1.8</v>
@@ -30307,7 +30307,7 @@
         <v>3</v>
       </c>
       <c r="P184">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q184">
         <v>3.02</v>
@@ -30331,7 +30331,7 @@
         <v>1.04</v>
       </c>
       <c r="X184">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y184">
         <v>1.44</v>
@@ -30346,10 +30346,10 @@
         <v>1.47</v>
       </c>
       <c r="AC184">
-        <v>4.85</v>
+        <v>5.4</v>
       </c>
       <c r="AD184">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE184">
         <v>1</v>
@@ -30358,7 +30358,7 @@
         <v>2.05</v>
       </c>
       <c r="AG184">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30992,13 +30992,13 @@
         <v>4.33</v>
       </c>
       <c r="AA188">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB188">
         <v>1.98</v>
       </c>
       <c r="AC188">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AD188">
         <v>1.44</v>
@@ -31116,19 +31116,19 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O189">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P189">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="Q189">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="R189">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S189">
         <v>1.22</v>
@@ -31146,13 +31146,13 @@
         <v>1.16</v>
       </c>
       <c r="X189">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
         <v>1.1</v>
       </c>
       <c r="Z189">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA189">
         <v>1.44</v>
@@ -31173,7 +31173,7 @@
         <v>1.5</v>
       </c>
       <c r="AG189">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="O190">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Q190">
         <v>2.9</v>
@@ -31777,10 +31777,10 @@
         <v>2.3</v>
       </c>
       <c r="Q193">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="R193">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S193">
         <v>1.37</v>
@@ -31819,7 +31819,7 @@
         <v>1.3</v>
       </c>
       <c r="AE193">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF193">
         <v>1.66</v>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AK193">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL193">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -671,7 +671,7 @@
         <v>1.28</v>
       </c>
       <c r="Z2">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA2">
         <v>2.05</v>
@@ -683,10 +683,10 @@
         <v>3.42</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
         <v>1.8</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="O3">
         <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>4.35</v>
+        <v>4.77</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AB5">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
         <v>1.45</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.55</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
         <v>5.21</v>
@@ -2485,7 +2485,7 @@
         <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O14">
         <v>3.2</v>
@@ -2600,7 +2600,7 @@
         <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2609,7 +2609,7 @@
         <v>1.36</v>
       </c>
       <c r="T14">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
         <v>2.81</v>
@@ -2648,7 +2648,7 @@
         <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
         <v>3.75</v>
@@ -2805,7 +2805,7 @@
         <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
@@ -2923,10 +2923,10 @@
         <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="R16">
         <v>2.14</v>
@@ -2941,10 +2941,10 @@
         <v>3</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2953,10 +2953,10 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
         <v>1.62</v>
@@ -2968,7 +2968,7 @@
         <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
         <v>1.95</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
         <v>3.6</v>
@@ -3095,22 +3095,22 @@
         <v>2.48</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
         <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
         <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q18">
         <v>2.3</v>
@@ -3409,7 +3409,7 @@
         <v>1.28</v>
       </c>
       <c r="O19">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P19">
         <v>7.1</v>
@@ -3418,13 +3418,13 @@
         <v>1.73</v>
       </c>
       <c r="R19">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S19">
         <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
         <v>2.2</v>
@@ -3439,13 +3439,13 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
         <v>4.6</v>
       </c>
       <c r="AA19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB19">
         <v>2.5</v>
@@ -3479,7 +3479,7 @@
         <v>1.11</v>
       </c>
       <c r="AK19">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3593,19 +3593,19 @@
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
         <v>1.8</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="Q21">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="R21">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
         <v>1.44</v>
@@ -3753,59 +3753,59 @@
         <v>2.46</v>
       </c>
       <c r="U21">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V21">
         <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z21">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AA21">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC21">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AD21">
+        <v>1.18</v>
+      </c>
+      <c r="AE21">
+        <v>1.05</v>
+      </c>
+      <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
+        <v>1.71</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.69</v>
+      </c>
+      <c r="AK21">
         <v>1.22</v>
-      </c>
-      <c r="AE21">
-        <v>1.03</v>
-      </c>
-      <c r="AF21">
-        <v>1.9</v>
-      </c>
-      <c r="AG21">
-        <v>1.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.75</v>
-      </c>
-      <c r="AK21">
-        <v>1.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4713,13 +4713,13 @@
         <v>1.63</v>
       </c>
       <c r="O27">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="P27">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R27">
         <v>2.19</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="O28">
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T28">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="U28">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="V28">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA28">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB28">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="AD28">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
         <v>1.79</v>
       </c>
       <c r="AG28">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5365,19 +5365,19 @@
         <v>2.98</v>
       </c>
       <c r="O31">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q31">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="R31">
         <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
         <v>2.81</v>
@@ -5389,7 +5389,7 @@
         <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5404,7 +5404,7 @@
         <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
         <v>3.1</v>
@@ -5413,7 +5413,7 @@
         <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
         <v>1.65</v>
@@ -5537,10 +5537,10 @@
         <v>1.85</v>
       </c>
       <c r="R32">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T32">
         <v>3.8</v>
@@ -5549,10 +5549,10 @@
         <v>2.2</v>
       </c>
       <c r="V32">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
         <v>1.6</v>
       </c>
       <c r="AE32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF32">
         <v>1.62</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="O36">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="P36">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
         <v>1.33</v>
@@ -6198,43 +6198,43 @@
         <v>3</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V36">
         <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
         <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>2.64</v>
       </c>
       <c r="O38">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
         <v>3.04</v>
@@ -6557,10 +6557,10 @@
         <v>1.36</v>
       </c>
       <c r="AF38">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG38">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O42">
         <v>3.4</v>
@@ -7167,37 +7167,37 @@
         <v>3</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S42">
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
         <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA42">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
         <v>2.3</v>
@@ -7209,10 +7209,10 @@
         <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA47">
         <v>2.06</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AK47">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P49">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O51">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P51">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q51">
         <v>1.79</v>
@@ -8661,10 +8661,10 @@
         <v>5</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB51">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="AC51">
         <v>2.25</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O52">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="P52">
         <v>3</v>
@@ -8827,7 +8827,7 @@
         <v>2.33</v>
       </c>
       <c r="AB52">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC52">
         <v>4.36</v>
@@ -9600,43 +9600,43 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
       <c r="O57">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q57">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R57">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="S57">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U57">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V57">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W57">
         <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="AA57">
         <v>1.86</v>
@@ -9645,19 +9645,19 @@
         <v>1.83</v>
       </c>
       <c r="AC57">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD57">
         <v>1.3</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AG57">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>2.15</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T58">
         <v>2.65</v>
@@ -9793,10 +9793,10 @@
         <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z58">
         <v>3</v>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10768,19 +10768,19 @@
         <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
         <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB64">
         <v>2.18</v>
@@ -10795,7 +10795,7 @@
         <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
         <v>2.3</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -10943,16 +10943,16 @@
         <v>4.2</v>
       </c>
       <c r="AA65">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC65">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AD65">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE65">
         <v>1.14</v>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U78">
         <v>2.41</v>
       </c>
       <c r="V78">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
         <v>1.08</v>
@@ -13071,7 +13071,7 @@
         <v>2.75</v>
       </c>
       <c r="AD78">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE78">
         <v>1.17</v>
@@ -13080,7 +13080,7 @@
         <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O79">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="P79">
         <v>5.55</v>
@@ -13198,7 +13198,7 @@
         <v>1.84</v>
       </c>
       <c r="R79">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="S79">
         <v>1.22</v>
@@ -13207,10 +13207,10 @@
         <v>3.8</v>
       </c>
       <c r="U79">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="V79">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W79">
         <v>1.14</v>
@@ -13222,16 +13222,16 @@
         <v>1.08</v>
       </c>
       <c r="Z79">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA79">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB79">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC79">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD79">
         <v>1.72</v>
@@ -13240,10 +13240,10 @@
         <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>5.2</v>
       </c>
       <c r="AA80">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AB80">
         <v>2.55</v>
@@ -13397,7 +13397,7 @@
         <v>2.25</v>
       </c>
       <c r="AD80">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE80">
         <v>1.21</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14979,37 +14979,37 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O90">
         <v>3.01</v>
       </c>
       <c r="P90">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S90">
         <v>1.36</v>
       </c>
       <c r="T90">
+        <v>2.8</v>
+      </c>
+      <c r="U90">
         <v>2.88</v>
       </c>
-      <c r="U90">
-        <v>2.5</v>
-      </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
         <v>1.06</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.25</v>
@@ -15018,25 +15018,25 @@
         <v>3.5</v>
       </c>
       <c r="AA90">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="AB90">
         <v>1.88</v>
       </c>
       <c r="AC90">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD90">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE90">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG90">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16452,16 +16452,16 @@
         <v>3.8</v>
       </c>
       <c r="P99">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q99">
         <v>2.07</v>
       </c>
       <c r="R99">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S99">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T99">
         <v>2.92</v>
@@ -16470,10 +16470,10 @@
         <v>2.5</v>
       </c>
       <c r="V99">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16488,7 +16488,7 @@
         <v>1.81</v>
       </c>
       <c r="AB99">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC99">
         <v>2.88</v>
@@ -16497,13 +16497,13 @@
         <v>1.34</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF99">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG99">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK99">
         <v>2.21</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="O100">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P100">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q100">
         <v>2</v>
       </c>
       <c r="R100">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
         <v>1.33</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P102">
         <v>2.8</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA102">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB102">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17427,16 +17427,16 @@
         <v>1.33</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P105">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q105">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R105">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S105">
         <v>1.22</v>
@@ -17466,10 +17466,10 @@
         <v>1.44</v>
       </c>
       <c r="AB105">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AC105">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD105">
         <v>1.65</v>
@@ -17478,7 +17478,7 @@
         <v>1.24</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
         <v>2.2</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK105">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,28 +17587,28 @@
         </is>
       </c>
       <c r="N106">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O106">
-        <v>5.25</v>
+        <v>5.95</v>
       </c>
       <c r="P106">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Q106">
-        <v>6.79</v>
+        <v>7.46</v>
       </c>
       <c r="R106">
         <v>2.91</v>
       </c>
       <c r="S106">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U106">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V106">
         <v>1.78</v>
@@ -17620,7 +17620,7 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z106">
         <v>5.75</v>
@@ -17629,22 +17629,22 @@
         <v>1.36</v>
       </c>
       <c r="AB106">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC106">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AD106">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AE106">
         <v>1.33</v>
       </c>
       <c r="AF106">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK106">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18776,7 +18776,7 @@
         <v>3.9</v>
       </c>
       <c r="AD113">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
         <v>1.06</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O114">
         <v>3.4</v>
@@ -18930,7 +18930,7 @@
         <v>2.95</v>
       </c>
       <c r="AA114">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB114">
         <v>1.8</v>
@@ -18939,7 +18939,7 @@
         <v>3.4</v>
       </c>
       <c r="AD114">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
@@ -18948,7 +18948,7 @@
         <v>1.9</v>
       </c>
       <c r="AG114">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O115">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q115">
         <v>2.4</v>
       </c>
       <c r="R115">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T115">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U115">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V115">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
         <v>1</v>
       </c>
       <c r="Y115">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA115">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC115">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AD115">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE115">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19549,7 +19549,7 @@
         <v>3.25</v>
       </c>
       <c r="P118">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q118">
         <v>4.48</v>
@@ -19582,10 +19582,10 @@
         <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB118">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC118">
         <v>3.86</v>
@@ -21665,7 +21665,7 @@
         <v>1.87</v>
       </c>
       <c r="O131">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P131">
         <v>3.75</v>
@@ -21677,10 +21677,10 @@
         <v>2.36</v>
       </c>
       <c r="S131">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T131">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U131">
         <v>2.45</v>
@@ -22486,7 +22486,7 @@
         <v>3.8</v>
       </c>
       <c r="Q136">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R136">
         <v>1.75</v>
@@ -22534,7 +22534,7 @@
         <v>2.5</v>
       </c>
       <c r="AG136">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O138">
         <v>3.55</v>
@@ -22848,10 +22848,10 @@
         <v>2.63</v>
       </c>
       <c r="AC138">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="AD138">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE138">
         <v>1.25</v>
@@ -22966,31 +22966,31 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O139">
         <v>4.65</v>
       </c>
       <c r="P139">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="Q139">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="R139">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="S139">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T139">
         <v>6</v>
       </c>
       <c r="U139">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V139">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="W139">
         <v>1.4</v>
@@ -23020,7 +23020,7 @@
         <v>1.8</v>
       </c>
       <c r="AF139">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AG139">
         <v>3.7</v>
@@ -23039,7 +23039,7 @@
         <v>1.14</v>
       </c>
       <c r="AK139">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23132,28 +23132,28 @@
         <v>4.25</v>
       </c>
       <c r="O140">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P140">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q140">
         <v>4.8</v>
       </c>
       <c r="R140">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S140">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T140">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="U140">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V140">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W140">
         <v>1.2</v>
@@ -23162,31 +23162,31 @@
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z140">
-        <v>5.55</v>
+        <v>5.38</v>
       </c>
       <c r="AA140">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB140">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AC140">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD140">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE140">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF140">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG140">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>1.17</v>
       </c>
       <c r="AK140">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="O141">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P141">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q141">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="R141">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="S141">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="T141">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="U141">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V141">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X141">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y141">
         <v>1.47</v>
       </c>
       <c r="Z141">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AA141">
         <v>2.37</v>
       </c>
       <c r="AB141">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AC141">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="AD141">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE141">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF141">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG141">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK141">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.07</v>
+        <v>1.84</v>
       </c>
       <c r="O142">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P142">
-        <v>2.16</v>
+        <v>3.96</v>
       </c>
       <c r="Q142">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="R142">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S142">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="T142">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="U142">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W142">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X142">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y142">
         <v>1.47</v>
       </c>
       <c r="Z142">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AA142">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB142">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC142">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AD142">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE142">
         <v>1.01</v>
       </c>
       <c r="AF142">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AG142">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK142">
-        <v>1.23</v>
+        <v>1.79</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,37 +23618,37 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="O143">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="P143">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q143">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R143">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S143">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="T143">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="U143">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V143">
         <v>1.22</v>
       </c>
       <c r="W143">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X143">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y143">
         <v>1.47</v>
@@ -23657,25 +23657,25 @@
         <v>2.35</v>
       </c>
       <c r="AA143">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB143">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC143">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD143">
         <v>1.12</v>
       </c>
       <c r="AE143">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF143">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AG143">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK143">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24460,19 +24460,19 @@
         <v>1.45</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X148">
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z148">
         <v>3.92</v>
       </c>
       <c r="AA148">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB148">
         <v>2.04</v>
@@ -24484,7 +24484,7 @@
         <v>1.33</v>
       </c>
       <c r="AE148">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF148">
         <v>1.62</v>
@@ -24599,28 +24599,28 @@
         <v>1.33</v>
       </c>
       <c r="O149">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P149">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Q149">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R149">
         <v>2.88</v>
       </c>
       <c r="S149">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T149">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U149">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V149">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W149">
         <v>1.17</v>
@@ -24632,7 +24632,7 @@
         <v>1.1</v>
       </c>
       <c r="Z149">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA149">
         <v>1.47</v>
@@ -24641,7 +24641,7 @@
         <v>2.55</v>
       </c>
       <c r="AC149">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AD149">
         <v>1.62</v>
@@ -24666,7 +24666,7 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK149">
         <v>2.92</v>
@@ -25257,10 +25257,10 @@
         <v>2.25</v>
       </c>
       <c r="Q153">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="R153">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S153">
         <v>1.4</v>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AK153">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,61 +25574,61 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="O155">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P155">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="Q155">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R155">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T155">
+        <v>2.73</v>
+      </c>
+      <c r="U155">
         <v>2.93</v>
       </c>
-      <c r="U155">
-        <v>2.98</v>
-      </c>
       <c r="V155">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y155">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z155">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="AA155">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB155">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC155">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD155">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG155">
         <v>1.85</v>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O156">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P156">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q156">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R156">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T156">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U156">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="V156">
         <v>1.38</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z156">
+        <v>3.2</v>
+      </c>
+      <c r="AA156">
+        <v>2.03</v>
+      </c>
+      <c r="AB156">
+        <v>1.75</v>
+      </c>
+      <c r="AC156">
         <v>3.5</v>
       </c>
-      <c r="AA156">
-        <v>1.9</v>
-      </c>
-      <c r="AB156">
-        <v>1.81</v>
-      </c>
-      <c r="AC156">
-        <v>3.45</v>
-      </c>
       <c r="AD156">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE156">
         <v>1.09</v>
       </c>
       <c r="AF156">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26229,22 +26229,22 @@
         <v>2.45</v>
       </c>
       <c r="O159">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P159">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q159">
         <v>3.1</v>
       </c>
       <c r="R159">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S159">
         <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U159">
         <v>2.5</v>
@@ -26253,34 +26253,34 @@
         <v>1.43</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X159">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
         <v>1.25</v>
       </c>
       <c r="Z159">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA159">
         <v>1.78</v>
       </c>
       <c r="AB159">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC159">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD159">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE159">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF159">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG159">
         <v>2.12</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O163">
         <v>3.5</v>
       </c>
       <c r="P163">
-        <v>5.95</v>
+        <v>5.45</v>
       </c>
       <c r="Q163">
         <v>2.2</v>
@@ -26893,7 +26893,7 @@
         <v>2.05</v>
       </c>
       <c r="S163">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T163">
         <v>2.6</v>
@@ -26917,13 +26917,13 @@
         <v>2.5</v>
       </c>
       <c r="AA163">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AB163">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC163">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD163">
         <v>1.17</v>
@@ -27207,10 +27207,10 @@
         <v>1.92</v>
       </c>
       <c r="O165">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P165">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q165">
         <v>2.54</v>
@@ -27234,10 +27234,10 @@
         <v>1.03</v>
       </c>
       <c r="X165">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y165">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z165">
         <v>2.7</v>
@@ -27252,13 +27252,13 @@
         <v>4.16</v>
       </c>
       <c r="AD165">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE165">
         <v>1.02</v>
       </c>
       <c r="AF165">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG165">
         <v>1.73</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O171">
         <v>2.6</v>
       </c>
       <c r="P171">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>3.6</v>
       </c>
       <c r="Q172">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R172">
         <v>1.74</v>
@@ -28366,7 +28366,7 @@
         <v>2.23</v>
       </c>
       <c r="U172">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V172">
         <v>1.2</v>
@@ -28393,7 +28393,7 @@
         <v>5.1</v>
       </c>
       <c r="AD172">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AE172">
         <v>1.02</v>
@@ -28517,55 +28517,55 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U173">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V173">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X173">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z173">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA173">
         <v>1.57</v>
       </c>
       <c r="AB173">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK173">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O174">
         <v>3</v>
       </c>
       <c r="P174">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="Q174">
         <v>2.58</v>
@@ -28686,7 +28686,7 @@
         <v>1.91</v>
       </c>
       <c r="S174">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T174">
         <v>2.2</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O175">
         <v>2.75</v>
@@ -28843,16 +28843,16 @@
         <v>3.7</v>
       </c>
       <c r="Q175">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R175">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="S175">
         <v>1.75</v>
       </c>
       <c r="T175">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="U175">
         <v>4.4</v>
@@ -28885,7 +28885,7 @@
         <v>1.04</v>
       </c>
       <c r="AE175">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF175">
         <v>2.45</v>
@@ -29202,7 +29202,7 @@
         <v>2.37</v>
       </c>
       <c r="AB177">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC177">
         <v>4.3</v>
@@ -29214,7 +29214,7 @@
         <v>1.05</v>
       </c>
       <c r="AF177">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG177">
         <v>1.7</v>
@@ -29233,7 +29233,7 @@
         <v>1.13</v>
       </c>
       <c r="AK177">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="Q178">
         <v>4.5</v>
@@ -29341,7 +29341,7 @@
         <v>1.4</v>
       </c>
       <c r="T178">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U178">
         <v>2.75</v>
@@ -29362,10 +29362,10 @@
         <v>3.3</v>
       </c>
       <c r="AA178">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AB178">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC178">
         <v>3.4</v>
@@ -29377,10 +29377,10 @@
         <v>1.1</v>
       </c>
       <c r="AF178">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG178">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK178">
         <v>1.21</v>
@@ -29507,10 +29507,10 @@
         <v>2.9</v>
       </c>
       <c r="U179">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V179">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W179">
         <v>1.05</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK179">
         <v>1.58</v>
@@ -29984,7 +29984,7 @@
         <v>5.5</v>
       </c>
       <c r="Q182">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R182">
         <v>2.22</v>
@@ -30153,10 +30153,10 @@
         <v>2.1</v>
       </c>
       <c r="S183">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T183">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U183">
         <v>2.7</v>
@@ -30165,34 +30165,34 @@
         <v>1.36</v>
       </c>
       <c r="W183">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X183">
         <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z183">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA183">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB183">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC183">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AD183">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE183">
         <v>1.05</v>
       </c>
       <c r="AF183">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG183">
         <v>1.9</v>
@@ -30313,7 +30313,7 @@
         <v>3.02</v>
       </c>
       <c r="R184">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="S184">
         <v>1.5</v>
@@ -30325,7 +30325,7 @@
         <v>3.52</v>
       </c>
       <c r="V184">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W184">
         <v>1.04</v>
@@ -30337,10 +30337,10 @@
         <v>1.44</v>
       </c>
       <c r="Z184">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AA184">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB184">
         <v>1.47</v>
@@ -30473,7 +30473,7 @@
         <v>5.05</v>
       </c>
       <c r="Q185">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R185">
         <v>2.75</v>
@@ -30488,10 +30488,10 @@
         <v>1.93</v>
       </c>
       <c r="V185">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="W185">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X185">
         <v>1.01</v>
@@ -30500,7 +30500,7 @@
         <v>1.11</v>
       </c>
       <c r="Z185">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA185">
         <v>1.3</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK185">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30627,19 +30627,19 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O186">
         <v>3.6</v>
       </c>
       <c r="P186">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q186">
         <v>2.5</v>
       </c>
       <c r="R186">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S186">
         <v>1.3</v>
@@ -30666,10 +30666,10 @@
         <v>4.5</v>
       </c>
       <c r="AA186">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB186">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC186">
         <v>2.63</v>
@@ -30678,7 +30678,7 @@
         <v>1.48</v>
       </c>
       <c r="AE186">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF186">
         <v>1.55</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK186">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30805,13 +30805,13 @@
         <v>1.95</v>
       </c>
       <c r="S187">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T187">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U187">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V187">
         <v>1.3</v>
@@ -30832,10 +30832,10 @@
         <v>2.44</v>
       </c>
       <c r="AB187">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC187">
-        <v>4.35</v>
+        <v>4.62</v>
       </c>
       <c r="AD187">
         <v>1.14</v>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK187">
         <v>1.63</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="O190">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P190">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="Q190">
         <v>2.9</v>
@@ -31309,31 +31309,31 @@
         <v>1.11</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y190">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z190">
         <v>3.7</v>
       </c>
       <c r="AA190">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB190">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC190">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD190">
         <v>1.38</v>
       </c>
       <c r="AE190">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF190">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG190">
         <v>2.2</v>
@@ -31451,7 +31451,7 @@
         <v>2.85</v>
       </c>
       <c r="Q191">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R191">
         <v>1.94</v>
@@ -31469,16 +31469,16 @@
         <v>1.35</v>
       </c>
       <c r="W191">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X191">
         <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z191">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="AA191">
         <v>2.16</v>
@@ -31487,16 +31487,16 @@
         <v>1.7</v>
       </c>
       <c r="AC191">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AD191">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE191">
         <v>1.06</v>
       </c>
       <c r="AF191">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG191">
         <v>1.85</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK191">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31614,16 +31614,16 @@
         <v>2.25</v>
       </c>
       <c r="Q192">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R192">
         <v>2.3</v>
       </c>
       <c r="S192">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U192">
         <v>2.3</v>
@@ -31638,16 +31638,16 @@
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z192">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="AA192">
         <v>1.66</v>
       </c>
       <c r="AB192">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC192">
         <v>2.63</v>
@@ -31659,7 +31659,7 @@
         <v>1.15</v>
       </c>
       <c r="AF192">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG192">
         <v>2.4</v>
@@ -31931,19 +31931,19 @@
         </is>
       </c>
       <c r="N194">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="O194">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P194">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q194">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R194">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S194">
         <v>1.29</v>
@@ -31964,16 +31964,16 @@
         <v>1.03</v>
       </c>
       <c r="Y194">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z194">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA194">
         <v>1.57</v>
       </c>
       <c r="AB194">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC194">
         <v>2.48</v>
@@ -31982,7 +31982,7 @@
         <v>1.55</v>
       </c>
       <c r="AE194">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF194">
         <v>1.53</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -804,7 +804,7 @@
         <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>4.77</v>
+        <v>4.15</v>
       </c>
       <c r="Q4">
+        <v>2.05</v>
+      </c>
+      <c r="R4">
+        <v>2.3</v>
+      </c>
+      <c r="S4">
+        <v>1.3</v>
+      </c>
+      <c r="T4">
+        <v>3.2</v>
+      </c>
+      <c r="U4">
+        <v>2.53</v>
+      </c>
+      <c r="V4">
+        <v>1.49</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1.22</v>
+      </c>
+      <c r="Z4">
+        <v>3.8</v>
+      </c>
+      <c r="AA4">
+        <v>1.69</v>
+      </c>
+      <c r="AB4">
+        <v>2.05</v>
+      </c>
+      <c r="AC4">
+        <v>2.75</v>
+      </c>
+      <c r="AD4">
+        <v>1.4</v>
+      </c>
+      <c r="AE4">
+        <v>1.12</v>
+      </c>
+      <c r="AF4">
+        <v>1.73</v>
+      </c>
+      <c r="AG4">
         <v>2</v>
       </c>
-      <c r="R4">
-        <v>2.45</v>
-      </c>
-      <c r="S4">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.25</v>
       </c>
-      <c r="T4">
-        <v>3.28</v>
-      </c>
-      <c r="U4">
-        <v>2.14</v>
-      </c>
-      <c r="V4">
-        <v>1.57</v>
-      </c>
-      <c r="W4">
-        <v>1.09</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.14</v>
-      </c>
-      <c r="Z4">
-        <v>4.33</v>
-      </c>
-      <c r="AA4">
-        <v>1.57</v>
-      </c>
-      <c r="AB4">
-        <v>2.3</v>
-      </c>
-      <c r="AC4">
-        <v>2.41</v>
-      </c>
-      <c r="AD4">
-        <v>1.45</v>
-      </c>
-      <c r="AE4">
-        <v>1.18</v>
-      </c>
-      <c r="AF4">
-        <v>1.65</v>
-      </c>
-      <c r="AG4">
-        <v>2.17</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.12</v>
-      </c>
       <c r="AK4">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
         <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AC5">
         <v>2.43</v>
       </c>
       <c r="AD5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
         <v>2.57</v>
@@ -1658,7 +1658,7 @@
         <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD8">
         <v>1.25</v>
@@ -1797,13 +1797,13 @@
         <v>2.45</v>
       </c>
       <c r="U9">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.1</v>
@@ -1818,7 +1818,7 @@
         <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
         <v>4.76</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>4.8</v>
+        <v>3.49</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC17">
-        <v>2.35</v>
+        <v>3.04</v>
       </c>
       <c r="AD17">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.28</v>
+      </c>
+      <c r="O18">
+        <v>4.8</v>
+      </c>
+      <c r="P18">
+        <v>7.1</v>
+      </c>
+      <c r="Q18">
         <v>1.73</v>
       </c>
-      <c r="O18">
-        <v>3.75</v>
-      </c>
-      <c r="P18">
-        <v>4</v>
-      </c>
-      <c r="Q18">
-        <v>2.3</v>
-      </c>
       <c r="R18">
+        <v>2.6</v>
+      </c>
+      <c r="S18">
+        <v>1.22</v>
+      </c>
+      <c r="T18">
+        <v>3.28</v>
+      </c>
+      <c r="U18">
         <v>2.2</v>
       </c>
-      <c r="S18">
-        <v>1.35</v>
-      </c>
-      <c r="T18">
-        <v>2.82</v>
-      </c>
-      <c r="U18">
-        <v>2.7</v>
-      </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>3.49</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.94</v>
+        <v>3.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="O19">
+        <v>3.9</v>
+      </c>
+      <c r="P19">
+        <v>3.6</v>
+      </c>
+      <c r="Q19">
+        <v>2.33</v>
+      </c>
+      <c r="R19">
+        <v>2.48</v>
+      </c>
+      <c r="S19">
+        <v>1.26</v>
+      </c>
+      <c r="T19">
+        <v>3.5</v>
+      </c>
+      <c r="U19">
+        <v>2.25</v>
+      </c>
+      <c r="V19">
+        <v>1.53</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>1.2</v>
+      </c>
+      <c r="Z19">
         <v>4.8</v>
       </c>
-      <c r="P19">
-        <v>7.1</v>
-      </c>
-      <c r="Q19">
-        <v>1.73</v>
-      </c>
-      <c r="R19">
-        <v>2.6</v>
-      </c>
-      <c r="S19">
-        <v>1.22</v>
-      </c>
-      <c r="T19">
-        <v>3.28</v>
-      </c>
-      <c r="U19">
-        <v>2.2</v>
-      </c>
-      <c r="V19">
-        <v>1.66</v>
-      </c>
-      <c r="W19">
-        <v>1.17</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.15</v>
-      </c>
-      <c r="Z19">
-        <v>4.6</v>
-      </c>
       <c r="AA19">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC19">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>3.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>5.95</v>
+        <v>2.9</v>
       </c>
       <c r="O83">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="Q83">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="R83">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="S83">
+        <v>1.36</v>
+      </c>
+      <c r="T83">
+        <v>2.88</v>
+      </c>
+      <c r="U83">
+        <v>2.8</v>
+      </c>
+      <c r="V83">
+        <v>1.36</v>
+      </c>
+      <c r="W83">
+        <v>1.08</v>
+      </c>
+      <c r="X83">
+        <v>1.06</v>
+      </c>
+      <c r="Y83">
+        <v>1.31</v>
+      </c>
+      <c r="Z83">
+        <v>3.25</v>
+      </c>
+      <c r="AA83">
+        <v>2</v>
+      </c>
+      <c r="AB83">
+        <v>1.75</v>
+      </c>
+      <c r="AC83">
+        <v>3.4</v>
+      </c>
+      <c r="AD83">
         <v>1.25</v>
       </c>
-      <c r="T83">
-        <v>3.8</v>
-      </c>
-      <c r="U83">
-        <v>2.25</v>
-      </c>
-      <c r="V83">
-        <v>1.6</v>
-      </c>
-      <c r="W83">
-        <v>1.13</v>
-      </c>
-      <c r="X83">
-        <v>1.04</v>
-      </c>
-      <c r="Y83">
-        <v>1.18</v>
-      </c>
-      <c r="Z83">
-        <v>4.55</v>
-      </c>
-      <c r="AA83">
-        <v>1.6</v>
-      </c>
-      <c r="AB83">
-        <v>2.4</v>
-      </c>
-      <c r="AC83">
-        <v>2.25</v>
-      </c>
-      <c r="AD83">
-        <v>1.47</v>
-      </c>
       <c r="AE83">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG83">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AK83">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.9</v>
+        <v>5.95</v>
       </c>
       <c r="O84">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P84">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="Q84">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="R84">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V84">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W84">
+        <v>1.13</v>
+      </c>
+      <c r="X84">
+        <v>1.04</v>
+      </c>
+      <c r="Y84">
+        <v>1.18</v>
+      </c>
+      <c r="Z84">
+        <v>4.55</v>
+      </c>
+      <c r="AA84">
+        <v>1.6</v>
+      </c>
+      <c r="AB84">
+        <v>2.4</v>
+      </c>
+      <c r="AC84">
+        <v>2.25</v>
+      </c>
+      <c r="AD84">
+        <v>1.47</v>
+      </c>
+      <c r="AE84">
+        <v>1.19</v>
+      </c>
+      <c r="AF84">
+        <v>1.66</v>
+      </c>
+      <c r="AG84">
+        <v>2.05</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.16</v>
+      </c>
+      <c r="AK84">
         <v>1.08</v>
-      </c>
-      <c r="X84">
-        <v>1.06</v>
-      </c>
-      <c r="Y84">
-        <v>1.31</v>
-      </c>
-      <c r="Z84">
-        <v>3.25</v>
-      </c>
-      <c r="AA84">
-        <v>2</v>
-      </c>
-      <c r="AB84">
-        <v>1.75</v>
-      </c>
-      <c r="AC84">
-        <v>3.4</v>
-      </c>
-      <c r="AD84">
-        <v>1.25</v>
-      </c>
-      <c r="AE84">
-        <v>1.05</v>
-      </c>
-      <c r="AF84">
-        <v>1.75</v>
-      </c>
-      <c r="AG84">
-        <v>1.9</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.5</v>
-      </c>
-      <c r="AK84">
-        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -20527,16 +20527,16 @@
         <v>3.15</v>
       </c>
       <c r="P124">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="Q124">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R124">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T124">
         <v>2.07</v>
@@ -20566,7 +20566,7 @@
         <v>1.63</v>
       </c>
       <c r="AC124">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD124">
         <v>1.22</v>
@@ -20575,7 +20575,7 @@
         <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
         <v>1.8</v>
@@ -22640,19 +22640,19 @@
         </is>
       </c>
       <c r="N137">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="O137">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P137">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q137">
         <v>4.5</v>
       </c>
       <c r="R137">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S137">
         <v>1.32</v>
@@ -22661,16 +22661,16 @@
         <v>3.05</v>
       </c>
       <c r="U137">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V137">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W137">
         <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
         <v>1.22</v>
@@ -22691,26 +22691,26 @@
         <v>1.37</v>
       </c>
       <c r="AE137">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF137">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG137">
+        <v>2.05</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>2</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.25</v>
       </c>
       <c r="AK137">
         <v>1.14</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,61 +25574,61 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O155">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="P155">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q155">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R155">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S155">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T155">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U155">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W155">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y155">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA155">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AB155">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC155">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD155">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE155">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF155">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
         <v>1.85</v>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,61 +25737,61 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="O156">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P156">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="Q156">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R156">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S156">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T156">
+        <v>2.73</v>
+      </c>
+      <c r="U156">
         <v>2.93</v>
       </c>
-      <c r="U156">
-        <v>2.98</v>
-      </c>
       <c r="V156">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
+        <v>1.04</v>
+      </c>
+      <c r="Y156">
+        <v>1.29</v>
+      </c>
+      <c r="Z156">
+        <v>3.18</v>
+      </c>
+      <c r="AA156">
+        <v>1.91</v>
+      </c>
+      <c r="AB156">
+        <v>1.84</v>
+      </c>
+      <c r="AC156">
+        <v>3.45</v>
+      </c>
+      <c r="AD156">
+        <v>1.3</v>
+      </c>
+      <c r="AE156">
         <v>1.06</v>
       </c>
-      <c r="Y156">
-        <v>1.28</v>
-      </c>
-      <c r="Z156">
-        <v>3.2</v>
-      </c>
-      <c r="AA156">
-        <v>2.03</v>
-      </c>
-      <c r="AB156">
-        <v>1.75</v>
-      </c>
-      <c r="AC156">
-        <v>3.5</v>
-      </c>
-      <c r="AD156">
-        <v>1.25</v>
-      </c>
-      <c r="AE156">
-        <v>1.09</v>
-      </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG156">
         <v>1.85</v>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26715,25 +26715,25 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O162">
         <v>3.8</v>
       </c>
       <c r="P162">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q162">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="R162">
         <v>2.15</v>
       </c>
       <c r="S162">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U162">
         <v>2.33</v>
@@ -26742,7 +26742,7 @@
         <v>1.5</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X162">
         <v>1.04</v>
@@ -26772,7 +26772,7 @@
         <v>1.5</v>
       </c>
       <c r="AG162">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK162">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL162">
         <v>0</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>4.15</v>
+        <v>4.77</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T4">
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.14</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
         <v>2.15</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.77</v>
+        <v>4.15</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
         <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
         <v>2.15</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
         <v>3.4</v>
@@ -1625,7 +1625,7 @@
         <v>2.57</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>1.42</v>
@@ -1640,7 +1640,7 @@
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.06</v>
@@ -1649,28 +1649,28 @@
         <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA8">
         <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
         <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P9">
         <v>2.98</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1797,19 +1797,19 @@
         <v>2.45</v>
       </c>
       <c r="U9">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z9">
         <v>2.45</v>
@@ -1821,7 +1821,7 @@
         <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>4.76</v>
+        <v>4.81</v>
       </c>
       <c r="AD9">
         <v>1.17</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
         <v>1.53</v>
@@ -2431,10 +2431,10 @@
         <v>4.2</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
         <v>5.21</v>
@@ -2446,10 +2446,10 @@
         <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U13">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V13">
         <v>1.38</v>
@@ -2467,16 +2467,16 @@
         <v>3.18</v>
       </c>
       <c r="AA13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AD13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
         <v>1.09</v>
@@ -2591,43 +2591,43 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
         <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
         <v>1.36</v>
       </c>
       <c r="T14">
+        <v>2.81</v>
+      </c>
+      <c r="U14">
         <v>2.8</v>
-      </c>
-      <c r="U14">
-        <v>2.81</v>
       </c>
       <c r="V14">
         <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
         <v>1.9</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AK14">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2769,19 +2769,19 @@
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U15">
         <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,7 +2793,7 @@
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
         <v>1.72</v>
@@ -2802,10 +2802,10 @@
         <v>3.75</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
         <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>4.16</v>
+        <v>4.32</v>
       </c>
       <c r="R16">
         <v>2.14</v>
       </c>
       <c r="S16">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
         <v>3</v>
       </c>
       <c r="V16">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2962,19 +2962,19 @@
         <v>1.62</v>
       </c>
       <c r="AC16">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
         <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
         <v>1.3</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -3101,7 +3101,7 @@
         <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
         <v>1.4</v>
@@ -3116,28 +3116,28 @@
         <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AA17">
+        <v>1.91</v>
+      </c>
+      <c r="AB17">
         <v>1.85</v>
       </c>
-      <c r="AB17">
-        <v>1.82</v>
-      </c>
       <c r="AC17">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="O18">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
-        <v>1.73</v>
+        <v>2.33</v>
       </c>
       <c r="R18">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T18">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.5</v>
+      </c>
+      <c r="AG18">
+        <v>2.28</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.25</v>
       </c>
-      <c r="AF18">
-        <v>1.8</v>
-      </c>
-      <c r="AG18">
+      <c r="AK18">
         <v>1.91</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.11</v>
-      </c>
-      <c r="AK18">
-        <v>3.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="R19">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S19">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AD19">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE19">
         <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK19">
-        <v>1.84</v>
+        <v>2.94</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
         <v>1.33</v>
@@ -3590,10 +3590,10 @@
         <v>3.1</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
         <v>1.07</v>
@@ -3611,13 +3611,13 @@
         <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC20">
         <v>2.69</v>
       </c>
       <c r="AD20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3732,77 +3732,77 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P21">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="R21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T21">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z21">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB21">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG21">
+        <v>1.73</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.71</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.69</v>
       </c>
       <c r="AK21">
         <v>1.22</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="O22">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>4.04</v>
+        <v>3.77</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O23">
         <v>3.9</v>
       </c>
       <c r="P23">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q23">
         <v>2.1</v>
@@ -4079,10 +4079,10 @@
         <v>3.72</v>
       </c>
       <c r="U23">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W23">
         <v>1.16</v>
@@ -4091,28 +4091,28 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z23">
-        <v>5.89</v>
+        <v>5.98</v>
       </c>
       <c r="AA23">
         <v>1.41</v>
       </c>
       <c r="AB23">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AC23">
         <v>2.05</v>
       </c>
       <c r="AD23">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AE23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF23">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
         <v>2.75</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O24">
         <v>3.6</v>
@@ -4257,16 +4257,16 @@
         <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC24">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD24">
         <v>1.46</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P25">
         <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R25">
         <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
         <v>2.3</v>
@@ -4429,13 +4429,13 @@
         <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD25">
         <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
         <v>1.53</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="Q26">
         <v>2.9</v>
@@ -4577,7 +4577,7 @@
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.18</v>
@@ -4592,13 +4592,13 @@
         <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AD26">
         <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
         <v>1.5</v>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,13 +4716,13 @@
         <v>3.85</v>
       </c>
       <c r="P27">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="Q27">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
         <v>1.34</v>
@@ -4731,7 +4731,7 @@
         <v>3.14</v>
       </c>
       <c r="U27">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V27">
         <v>1.46</v>
@@ -4749,10 +4749,10 @@
         <v>3.9</v>
       </c>
       <c r="AA27">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB27">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AC27">
         <v>2.81</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
         <v>2.45</v>
@@ -4885,19 +4885,19 @@
         <v>3.3</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T28">
         <v>2.41</v>
       </c>
       <c r="U28">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
         <v>1.02</v>
@@ -4912,13 +4912,13 @@
         <v>2.75</v>
       </c>
       <c r="AA28">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AD28">
         <v>1.18</v>
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6198,43 +6198,43 @@
         <v>3</v>
       </c>
       <c r="U36">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC36">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
         <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O39">
         <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q39">
         <v>3.94</v>
@@ -6687,16 +6687,16 @@
         <v>3.2</v>
       </c>
       <c r="U39">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
         <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
         <v>1.22</v>
@@ -6705,7 +6705,7 @@
         <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB39">
         <v>2.1</v>
@@ -6717,7 +6717,7 @@
         <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.6</v>
@@ -6739,7 +6739,7 @@
         <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7822,19 +7822,19 @@
         <v>2.23</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U46">
         <v>2.43</v>
       </c>
       <c r="V46">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -7843,22 +7843,22 @@
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA46">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB46">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC46">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD46">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
         <v>1.57</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P47">
         <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S47">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T47">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
         <v>2.7</v>
@@ -8015,7 +8015,7 @@
         <v>1.73</v>
       </c>
       <c r="AC47">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD47">
         <v>1.25</v>
@@ -8821,19 +8821,19 @@
         <v>1.41</v>
       </c>
       <c r="Z52">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AA52">
         <v>2.33</v>
       </c>
       <c r="AB52">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AC52">
-        <v>4.36</v>
+        <v>3.88</v>
       </c>
       <c r="AD52">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
         <v>1.02</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="O57">
         <v>3.3</v>
@@ -9609,55 +9609,55 @@
         <v>1.99</v>
       </c>
       <c r="Q57">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R57">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V57">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
+        <v>1.27</v>
+      </c>
+      <c r="Z57">
+        <v>3.14</v>
+      </c>
+      <c r="AA57">
+        <v>1.95</v>
+      </c>
+      <c r="AB57">
+        <v>1.75</v>
+      </c>
+      <c r="AC57">
+        <v>3.5</v>
+      </c>
+      <c r="AD57">
         <v>1.25</v>
-      </c>
-      <c r="Z57">
-        <v>3.28</v>
-      </c>
-      <c r="AA57">
-        <v>1.86</v>
-      </c>
-      <c r="AB57">
-        <v>1.83</v>
-      </c>
-      <c r="AC57">
-        <v>3.04</v>
-      </c>
-      <c r="AD57">
-        <v>1.3</v>
       </c>
       <c r="AE57">
         <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="O63">
         <v>3.55</v>
@@ -10590,7 +10590,7 @@
         <v>3.12</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
         <v>1.22</v>
@@ -10599,7 +10599,7 @@
         <v>3.42</v>
       </c>
       <c r="U63">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="V63">
         <v>1.62</v>
@@ -10611,31 +10611,31 @@
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z63">
         <v>4.8</v>
       </c>
       <c r="AA63">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB63">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AD63">
         <v>1.44</v>
       </c>
       <c r="AE63">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF63">
         <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="O82">
         <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q82">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R82">
         <v>2.3</v>
@@ -13693,13 +13693,13 @@
         <v>1.3</v>
       </c>
       <c r="T82">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="U82">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V82">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13717,22 +13717,22 @@
         <v>1.73</v>
       </c>
       <c r="AB82">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC82">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD82">
         <v>1.4</v>
       </c>
       <c r="AE82">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
         <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.9</v>
+        <v>5.95</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P83">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="Q83">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="R83">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W83">
+        <v>1.13</v>
+      </c>
+      <c r="X83">
+        <v>1.04</v>
+      </c>
+      <c r="Y83">
+        <v>1.18</v>
+      </c>
+      <c r="Z83">
+        <v>4.55</v>
+      </c>
+      <c r="AA83">
+        <v>1.6</v>
+      </c>
+      <c r="AB83">
+        <v>2.4</v>
+      </c>
+      <c r="AC83">
+        <v>2.25</v>
+      </c>
+      <c r="AD83">
+        <v>1.47</v>
+      </c>
+      <c r="AE83">
+        <v>1.19</v>
+      </c>
+      <c r="AF83">
+        <v>1.66</v>
+      </c>
+      <c r="AG83">
+        <v>2.05</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.16</v>
+      </c>
+      <c r="AK83">
         <v>1.08</v>
-      </c>
-      <c r="X83">
-        <v>1.06</v>
-      </c>
-      <c r="Y83">
-        <v>1.31</v>
-      </c>
-      <c r="Z83">
-        <v>3.25</v>
-      </c>
-      <c r="AA83">
-        <v>2</v>
-      </c>
-      <c r="AB83">
-        <v>1.75</v>
-      </c>
-      <c r="AC83">
-        <v>3.4</v>
-      </c>
-      <c r="AD83">
-        <v>1.25</v>
-      </c>
-      <c r="AE83">
-        <v>1.05</v>
-      </c>
-      <c r="AF83">
-        <v>1.75</v>
-      </c>
-      <c r="AG83">
-        <v>1.9</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.5</v>
-      </c>
-      <c r="AK83">
-        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>5.95</v>
+        <v>2.9</v>
       </c>
       <c r="O84">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P84">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="Q84">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="R84">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="S84">
+        <v>1.36</v>
+      </c>
+      <c r="T84">
+        <v>2.88</v>
+      </c>
+      <c r="U84">
+        <v>2.8</v>
+      </c>
+      <c r="V84">
+        <v>1.36</v>
+      </c>
+      <c r="W84">
+        <v>1.08</v>
+      </c>
+      <c r="X84">
+        <v>1.06</v>
+      </c>
+      <c r="Y84">
+        <v>1.31</v>
+      </c>
+      <c r="Z84">
+        <v>3.25</v>
+      </c>
+      <c r="AA84">
+        <v>2</v>
+      </c>
+      <c r="AB84">
+        <v>1.75</v>
+      </c>
+      <c r="AC84">
+        <v>3.4</v>
+      </c>
+      <c r="AD84">
         <v>1.25</v>
       </c>
-      <c r="T84">
-        <v>3.8</v>
-      </c>
-      <c r="U84">
-        <v>2.25</v>
-      </c>
-      <c r="V84">
-        <v>1.6</v>
-      </c>
-      <c r="W84">
-        <v>1.13</v>
-      </c>
-      <c r="X84">
-        <v>1.04</v>
-      </c>
-      <c r="Y84">
-        <v>1.18</v>
-      </c>
-      <c r="Z84">
-        <v>4.55</v>
-      </c>
-      <c r="AA84">
-        <v>1.6</v>
-      </c>
-      <c r="AB84">
-        <v>2.4</v>
-      </c>
-      <c r="AC84">
-        <v>2.25</v>
-      </c>
-      <c r="AD84">
-        <v>1.47</v>
-      </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF84">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG84">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O90">
         <v>3.01</v>
@@ -14988,55 +14988,55 @@
         <v>2.75</v>
       </c>
       <c r="Q90">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R90">
         <v>2</v>
       </c>
       <c r="S90">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="V90">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
         <v>1.06</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y90">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z90">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA90">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AB90">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC90">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD90">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE90">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O117">
         <v>3.1</v>
@@ -19395,16 +19395,16 @@
         <v>2.05</v>
       </c>
       <c r="S117">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
         <v>2.66</v>
       </c>
       <c r="U117">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="V117">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W117">
         <v>1.05</v>
@@ -19416,7 +19416,7 @@
         <v>1.33</v>
       </c>
       <c r="Z117">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA117">
         <v>1.98</v>
@@ -19431,7 +19431,7 @@
         <v>1.26</v>
       </c>
       <c r="AE117">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
         <v>1.76</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK117">
         <v>1.3</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="O118">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="P118">
         <v>2.03</v>
       </c>
       <c r="Q118">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="R118">
         <v>2</v>
@@ -19579,7 +19579,7 @@
         <v>1.36</v>
       </c>
       <c r="Z118">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AA118">
         <v>2.2</v>
@@ -19588,7 +19588,7 @@
         <v>1.78</v>
       </c>
       <c r="AC118">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="AD118">
         <v>1.22</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AK118">
         <v>1.28</v>
@@ -22154,10 +22154,10 @@
         <v>2.1</v>
       </c>
       <c r="O134">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q134">
         <v>2.62</v>
@@ -22172,7 +22172,7 @@
         <v>3.58</v>
       </c>
       <c r="U134">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V134">
         <v>1.64</v>
@@ -22190,25 +22190,25 @@
         <v>5.25</v>
       </c>
       <c r="AA134">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB134">
         <v>2.49</v>
       </c>
       <c r="AC134">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD134">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE134">
         <v>1.23</v>
       </c>
       <c r="AF134">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG134">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G145">
@@ -23940,68 +23940,68 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N145">
-        <v>4.49</v>
+        <v>2.17</v>
       </c>
       <c r="O145">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P145">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="Q145">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="R145">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S145">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T145">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="U145">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="V145">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W145">
         <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z145">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA145">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC145">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD145">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE145">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AK145">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G146">
@@ -24103,68 +24103,68 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N146">
-        <v>2.17</v>
+        <v>4.49</v>
       </c>
       <c r="O146">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P146">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="Q146">
-        <v>2.47</v>
+        <v>4.2</v>
       </c>
       <c r="R146">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T146">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="U146">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V146">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W146">
         <v>1.11</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z146">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB146">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC146">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD146">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE146">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AK146">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,61 +25574,61 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="O155">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P155">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="Q155">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R155">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T155">
+        <v>2.73</v>
+      </c>
+      <c r="U155">
         <v>2.93</v>
       </c>
-      <c r="U155">
-        <v>2.98</v>
-      </c>
       <c r="V155">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
+        <v>1.04</v>
+      </c>
+      <c r="Y155">
+        <v>1.29</v>
+      </c>
+      <c r="Z155">
+        <v>3.18</v>
+      </c>
+      <c r="AA155">
+        <v>1.91</v>
+      </c>
+      <c r="AB155">
+        <v>1.84</v>
+      </c>
+      <c r="AC155">
+        <v>3.45</v>
+      </c>
+      <c r="AD155">
+        <v>1.3</v>
+      </c>
+      <c r="AE155">
         <v>1.06</v>
       </c>
-      <c r="Y155">
-        <v>1.28</v>
-      </c>
-      <c r="Z155">
-        <v>3.2</v>
-      </c>
-      <c r="AA155">
-        <v>2.03</v>
-      </c>
-      <c r="AB155">
-        <v>1.75</v>
-      </c>
-      <c r="AC155">
-        <v>3.5</v>
-      </c>
-      <c r="AD155">
-        <v>1.25</v>
-      </c>
-      <c r="AE155">
-        <v>1.09</v>
-      </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG155">
         <v>1.85</v>
@@ -25647,7 +25647,7 @@
         <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,61 +25737,61 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O156">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="P156">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q156">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T156">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U156">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="V156">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z156">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AB156">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC156">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD156">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE156">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF156">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
         <v>1.85</v>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27050,55 +27050,55 @@
         <v>0</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27367,7 +27367,7 @@
         </is>
       </c>
       <c r="N166">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O166">
         <v>3.3</v>
@@ -27394,7 +27394,7 @@
         <v>1.43</v>
       </c>
       <c r="W166">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X166">
         <v>1</v>
@@ -27406,10 +27406,10 @@
         <v>3.5</v>
       </c>
       <c r="AA166">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB166">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC166">
         <v>3.1</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O13">
         <v>3.42</v>
@@ -2443,13 +2443,13 @@
         <v>2.15</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="V13">
         <v>1.38</v>
@@ -2458,7 +2458,7 @@
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
         <v>1.27</v>
@@ -2467,25 +2467,25 @@
         <v>3.25</v>
       </c>
       <c r="AA13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
         <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
         <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,40 +2591,40 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U14">
         <v>2.8</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
         <v>3.5</v>
@@ -2642,13 +2642,13 @@
         <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AK14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,22 +2754,22 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
         <v>2.75</v>
@@ -2778,7 +2778,7 @@
         <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -2793,19 +2793,19 @@
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>1.28</v>
+      </c>
+      <c r="O17">
+        <v>4.9</v>
+      </c>
+      <c r="P17">
+        <v>7</v>
+      </c>
+      <c r="Q17">
         <v>1.7</v>
       </c>
-      <c r="O17">
-        <v>3.65</v>
-      </c>
-      <c r="P17">
-        <v>4.2</v>
-      </c>
-      <c r="Q17">
+      <c r="R17">
+        <v>2.6</v>
+      </c>
+      <c r="S17">
+        <v>1.25</v>
+      </c>
+      <c r="T17">
+        <v>3.28</v>
+      </c>
+      <c r="U17">
+        <v>2.2</v>
+      </c>
+      <c r="V17">
+        <v>1.66</v>
+      </c>
+      <c r="W17">
+        <v>1.12</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>4.55</v>
+      </c>
+      <c r="AA17">
+        <v>1.49</v>
+      </c>
+      <c r="AB17">
         <v>2.3</v>
       </c>
-      <c r="R17">
-        <v>2.1</v>
-      </c>
-      <c r="S17">
-        <v>1.38</v>
-      </c>
-      <c r="T17">
-        <v>2.7</v>
-      </c>
-      <c r="U17">
-        <v>2.9</v>
-      </c>
-      <c r="V17">
-        <v>1.36</v>
-      </c>
-      <c r="W17">
-        <v>1.08</v>
-      </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>1.24</v>
-      </c>
-      <c r="Z17">
-        <v>3.25</v>
-      </c>
-      <c r="AA17">
-        <v>1.95</v>
-      </c>
-      <c r="AB17">
-        <v>1.76</v>
-      </c>
       <c r="AC17">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="O18">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>4.55</v>
+        <v>3.25</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD18">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O24">
         <v>3.6</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S26">
         <v>1.25</v>
@@ -4571,7 +4571,7 @@
         <v>2.33</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W26">
         <v>1.14</v>
@@ -4586,10 +4586,10 @@
         <v>4.6</v>
       </c>
       <c r="AA26">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
         <v>2.36</v>
@@ -7194,7 +7194,7 @@
         <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
         <v>2.22</v>
@@ -8299,7 +8299,7 @@
         <v>3.64</v>
       </c>
       <c r="O49">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="P49">
         <v>2.09</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O53">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="P53">
-        <v>7.15</v>
+        <v>8.25</v>
       </c>
       <c r="Q53">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R53">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S53">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="U53">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="V53">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="W53">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
         <v>1.08</v>
       </c>
       <c r="Z53">
-        <v>7.1</v>
+        <v>5.45</v>
       </c>
       <c r="AA53">
+        <v>1.39</v>
+      </c>
+      <c r="AB53">
+        <v>2.5</v>
+      </c>
+      <c r="AC53">
+        <v>2.04</v>
+      </c>
+      <c r="AD53">
+        <v>1.7</v>
+      </c>
+      <c r="AE53">
         <v>1.3</v>
       </c>
-      <c r="AB53">
-        <v>3.2</v>
-      </c>
-      <c r="AC53">
-        <v>1.83</v>
-      </c>
-      <c r="AD53">
-        <v>1.92</v>
-      </c>
-      <c r="AE53">
-        <v>1.33</v>
-      </c>
       <c r="AF53">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK53">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O54">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="P54">
-        <v>8.25</v>
+        <v>7.15</v>
       </c>
       <c r="Q54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R54">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S54">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T54">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="U54">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="V54">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>5.45</v>
+        <v>7.1</v>
       </c>
       <c r="AA54">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AB54">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC54">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD54">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF54">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG54">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>4.58</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA58">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q75">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12733,7 +12733,7 @@
         <v>1.35</v>
       </c>
       <c r="Z76">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AA76">
         <v>2.36</v>
@@ -12770,7 +12770,7 @@
         <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -15323,40 +15323,40 @@
         <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U92">
         <v>2.45</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y92">
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="AA92">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC92">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD92">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE92">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
         <v>1.6</v>
@@ -15378,7 +15378,7 @@
         <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15652,13 +15652,13 @@
         <v>3.55</v>
       </c>
       <c r="U94">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V94">
         <v>1.52</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X94">
         <v>1.03</v>
@@ -15966,7 +15966,7 @@
         <v>1.82</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="R96">
         <v>2.1</v>
@@ -15978,13 +15978,13 @@
         <v>2.8</v>
       </c>
       <c r="U96">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="V96">
         <v>1.36</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15996,7 +15996,7 @@
         <v>3.2</v>
       </c>
       <c r="AA96">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB96">
         <v>1.78</v>
@@ -16609,31 +16609,31 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="O100">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P100">
-        <v>6.65</v>
+        <v>6.3</v>
       </c>
       <c r="Q100">
         <v>2</v>
       </c>
       <c r="R100">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U100">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V100">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W100">
         <v>1.06</v>
@@ -16645,16 +16645,16 @@
         <v>1.23</v>
       </c>
       <c r="Z100">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="AA100">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC100">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD100">
         <v>1.33</v>
@@ -16775,13 +16775,13 @@
         <v>2.35</v>
       </c>
       <c r="O101">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q101">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="R101">
         <v>2.06</v>
@@ -16796,7 +16796,7 @@
         <v>2.75</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W101">
         <v>1.06</v>
@@ -16808,7 +16808,7 @@
         <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="AA101">
         <v>1.95</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="O104">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P104">
+        <v>2.3</v>
+      </c>
+      <c r="Q104">
+        <v>3.95</v>
+      </c>
+      <c r="R104">
         <v>2.04</v>
       </c>
-      <c r="Q104">
-        <v>3.9</v>
-      </c>
-      <c r="R104">
-        <v>2.05</v>
-      </c>
       <c r="S104">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T104">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U104">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V104">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W104">
         <v>1.05</v>
       </c>
       <c r="X104">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y104">
         <v>1.4</v>
       </c>
       <c r="Z104">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA104">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB104">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC104">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD104">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE104">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG104">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
+        <v>8</v>
+      </c>
+      <c r="O105">
+        <v>5.75</v>
+      </c>
+      <c r="P105">
+        <v>1.22</v>
+      </c>
+      <c r="Q105">
+        <v>7.4</v>
+      </c>
+      <c r="R105">
+        <v>2.9</v>
+      </c>
+      <c r="S105">
+        <v>1.18</v>
+      </c>
+      <c r="T105">
+        <v>4.33</v>
+      </c>
+      <c r="U105">
+        <v>1.91</v>
+      </c>
+      <c r="V105">
+        <v>1.76</v>
+      </c>
+      <c r="W105">
+        <v>1.24</v>
+      </c>
+      <c r="X105">
+        <v>1.01</v>
+      </c>
+      <c r="Y105">
+        <v>1.07</v>
+      </c>
+      <c r="Z105">
+        <v>5.95</v>
+      </c>
+      <c r="AA105">
+        <v>1.36</v>
+      </c>
+      <c r="AB105">
+        <v>3.25</v>
+      </c>
+      <c r="AC105">
+        <v>1.91</v>
+      </c>
+      <c r="AD105">
+        <v>1.8</v>
+      </c>
+      <c r="AE105">
         <v>1.33</v>
       </c>
-      <c r="O105">
-        <v>4.8</v>
-      </c>
-      <c r="P105">
-        <v>6.5</v>
-      </c>
-      <c r="Q105">
-        <v>1.73</v>
-      </c>
-      <c r="R105">
-        <v>2.7</v>
-      </c>
-      <c r="S105">
-        <v>1.2</v>
-      </c>
-      <c r="T105">
-        <v>4</v>
-      </c>
-      <c r="U105">
-        <v>2.1</v>
-      </c>
-      <c r="V105">
-        <v>1.67</v>
-      </c>
-      <c r="W105">
-        <v>1.17</v>
-      </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.09</v>
-      </c>
-      <c r="Z105">
-        <v>5.25</v>
-      </c>
-      <c r="AA105">
-        <v>1.44</v>
-      </c>
-      <c r="AB105">
-        <v>2.63</v>
-      </c>
-      <c r="AC105">
-        <v>2.1</v>
-      </c>
-      <c r="AD105">
-        <v>1.73</v>
-      </c>
-      <c r="AE105">
-        <v>1.3</v>
-      </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK105">
-        <v>2.94</v>
+        <v>1.05</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>8</v>
+        <v>1.33</v>
       </c>
       <c r="O106">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="P106">
-        <v>1.22</v>
+        <v>6.5</v>
       </c>
       <c r="Q106">
-        <v>7.4</v>
+        <v>1.73</v>
       </c>
       <c r="R106">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="S106">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T106">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U106">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V106">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W106">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z106">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA106">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB106">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AC106">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD106">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF106">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK106">
-        <v>1.05</v>
+        <v>2.94</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,37 +17750,37 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O107">
         <v>3.4</v>
       </c>
       <c r="P107">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="R107">
         <v>2.04</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="V107">
         <v>1.36</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y107">
         <v>1.27</v>
@@ -17789,25 +17789,25 @@
         <v>3.14</v>
       </c>
       <c r="AA107">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AB107">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC107">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AD107">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE107">
         <v>1.05</v>
       </c>
       <c r="AF107">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG107">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK107">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17925,52 +17925,52 @@
         <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S108">
         <v>1.35</v>
       </c>
       <c r="T108">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="U108">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V108">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z108">
         <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB108">
         <v>1.87</v>
       </c>
       <c r="AC108">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD108">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
         <v>1.65</v>
       </c>
       <c r="AG108">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>8.550000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="O111">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="P111">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="Q111">
-        <v>6.55</v>
+        <v>4.33</v>
       </c>
       <c r="R111">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="S111">
+        <v>1.3</v>
+      </c>
+      <c r="T111">
+        <v>3.1</v>
+      </c>
+      <c r="U111">
+        <v>2.5</v>
+      </c>
+      <c r="V111">
+        <v>1.44</v>
+      </c>
+      <c r="W111">
+        <v>1.1</v>
+      </c>
+      <c r="X111">
+        <v>1</v>
+      </c>
+      <c r="Y111">
+        <v>1.19</v>
+      </c>
+      <c r="Z111">
+        <v>3.78</v>
+      </c>
+      <c r="AA111">
+        <v>1.75</v>
+      </c>
+      <c r="AB111">
+        <v>2</v>
+      </c>
+      <c r="AC111">
+        <v>2.82</v>
+      </c>
+      <c r="AD111">
+        <v>1.39</v>
+      </c>
+      <c r="AE111">
+        <v>1.11</v>
+      </c>
+      <c r="AF111">
+        <v>1.67</v>
+      </c>
+      <c r="AG111">
+        <v>2</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.94</v>
+      </c>
+      <c r="AK111">
         <v>1.22</v>
-      </c>
-      <c r="T111">
-        <v>3.48</v>
-      </c>
-      <c r="U111">
-        <v>1.97</v>
-      </c>
-      <c r="V111">
-        <v>1.62</v>
-      </c>
-      <c r="W111">
-        <v>1.14</v>
-      </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
-        <v>1.13</v>
-      </c>
-      <c r="Z111">
-        <v>6</v>
-      </c>
-      <c r="AA111">
-        <v>1.44</v>
-      </c>
-      <c r="AB111">
-        <v>2.63</v>
-      </c>
-      <c r="AC111">
-        <v>2.2</v>
-      </c>
-      <c r="AD111">
-        <v>1.62</v>
-      </c>
-      <c r="AE111">
-        <v>1.25</v>
-      </c>
-      <c r="AF111">
-        <v>1.74</v>
-      </c>
-      <c r="AG111">
-        <v>1.96</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>3.05</v>
-      </c>
-      <c r="AK111">
-        <v>1.04</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O112">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="P112">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="Q112">
-        <v>4.33</v>
+        <v>6.55</v>
       </c>
       <c r="R112">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="S112">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="U112">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="V112">
+        <v>1.62</v>
+      </c>
+      <c r="W112">
+        <v>1.14</v>
+      </c>
+      <c r="X112">
+        <v>1.01</v>
+      </c>
+      <c r="Y112">
+        <v>1.13</v>
+      </c>
+      <c r="Z112">
+        <v>6</v>
+      </c>
+      <c r="AA112">
         <v>1.44</v>
       </c>
-      <c r="W112">
-        <v>1.1</v>
-      </c>
-      <c r="X112">
-        <v>1</v>
-      </c>
-      <c r="Y112">
-        <v>1.19</v>
-      </c>
-      <c r="Z112">
-        <v>3.78</v>
-      </c>
-      <c r="AA112">
-        <v>1.75</v>
-      </c>
       <c r="AB112">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AC112">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="AD112">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AE112">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG112">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="AK112">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O116">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P116">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q116">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="R116">
+        <v>1.82</v>
+      </c>
+      <c r="S116">
+        <v>1.53</v>
+      </c>
+      <c r="T116">
+        <v>2.31</v>
+      </c>
+      <c r="U116">
+        <v>3.42</v>
+      </c>
+      <c r="V116">
+        <v>1.23</v>
+      </c>
+      <c r="W116">
+        <v>1.03</v>
+      </c>
+      <c r="X116">
+        <v>1.08</v>
+      </c>
+      <c r="Y116">
+        <v>1.41</v>
+      </c>
+      <c r="Z116">
+        <v>2.52</v>
+      </c>
+      <c r="AA116">
+        <v>2.38</v>
+      </c>
+      <c r="AB116">
+        <v>1.5</v>
+      </c>
+      <c r="AC116">
+        <v>3.95</v>
+      </c>
+      <c r="AD116">
+        <v>1.22</v>
+      </c>
+      <c r="AE116">
+        <v>1.05</v>
+      </c>
+      <c r="AF116">
         <v>1.95</v>
       </c>
-      <c r="S116">
-        <v>1.42</v>
-      </c>
-      <c r="T116">
-        <v>2.53</v>
-      </c>
-      <c r="U116">
-        <v>3.08</v>
-      </c>
-      <c r="V116">
-        <v>1.29</v>
-      </c>
-      <c r="W116">
-        <v>1.05</v>
-      </c>
-      <c r="X116">
-        <v>1.04</v>
-      </c>
-      <c r="Y116">
-        <v>1.32</v>
-      </c>
-      <c r="Z116">
-        <v>2.88</v>
-      </c>
-      <c r="AA116">
-        <v>2.12</v>
-      </c>
-      <c r="AB116">
-        <v>1.63</v>
-      </c>
-      <c r="AC116">
-        <v>3.86</v>
-      </c>
-      <c r="AD116">
-        <v>1.18</v>
-      </c>
-      <c r="AE116">
-        <v>1.07</v>
-      </c>
-      <c r="AF116">
-        <v>1.85</v>
-      </c>
       <c r="AG116">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK116">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19395,25 +19395,25 @@
         <v>2.05</v>
       </c>
       <c r="S117">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U117">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="V117">
         <v>1.37</v>
       </c>
       <c r="W117">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z117">
         <v>3.05</v>
@@ -19422,10 +19422,10 @@
         <v>2</v>
       </c>
       <c r="AB117">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC117">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD117">
         <v>1.26</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AK117">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>3.19</v>
       </c>
       <c r="Q122">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R122">
         <v>2.19</v>
@@ -20213,13 +20213,13 @@
         <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W122">
         <v>1.1</v>
@@ -20231,13 +20231,13 @@
         <v>1.19</v>
       </c>
       <c r="Z122">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA122">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB122">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC122">
         <v>2.66</v>
@@ -20530,16 +20530,16 @@
         <v>2.8</v>
       </c>
       <c r="Q124">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R124">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S124">
         <v>1.39</v>
       </c>
       <c r="T124">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U124">
         <v>2.63</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK124">
         <v>1.6</v>
@@ -20877,28 +20877,28 @@
         <v>1.01</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y126">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z126">
         <v>2.88</v>
       </c>
       <c r="AA126">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB126">
         <v>1.7</v>
       </c>
       <c r="AC126">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD126">
         <v>1.19</v>
       </c>
       <c r="AE126">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF126">
         <v>1.85</v>
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O127">
         <v>3.5</v>
       </c>
       <c r="P127">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q127">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="R127">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S127">
         <v>1.4</v>
@@ -21055,7 +21055,7 @@
         <v>1.82</v>
       </c>
       <c r="AC127">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD127">
         <v>1.25</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK127">
         <v>2.22</v>
@@ -23944,7 +23944,7 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O145">
         <v>3.75</v>
@@ -23980,19 +23980,19 @@
         <v>1.13</v>
       </c>
       <c r="Z145">
-        <v>5.12</v>
+        <v>5.18</v>
       </c>
       <c r="AA145">
         <v>1.53</v>
       </c>
       <c r="AB145">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AC145">
         <v>2.25</v>
       </c>
       <c r="AD145">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE145">
         <v>1.2</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G146">
@@ -24103,68 +24103,68 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N146">
-        <v>2.17</v>
+        <v>4.49</v>
       </c>
       <c r="O146">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P146">
-        <v>3.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q146">
-        <v>2.47</v>
+        <v>4.2</v>
       </c>
       <c r="R146">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T146">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U146">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W146">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z146">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB146">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AC146">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AD146">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G147">
@@ -24266,68 +24266,68 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N147">
-        <v>4.49</v>
+        <v>2.16</v>
       </c>
       <c r="O147">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P147">
-        <v>1.79</v>
+        <v>3.03</v>
       </c>
       <c r="Q147">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="R147">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S147">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T147">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="U147">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="V147">
+        <v>1.44</v>
+      </c>
+      <c r="W147">
+        <v>1.08</v>
+      </c>
+      <c r="X147">
+        <v>1.04</v>
+      </c>
+      <c r="Y147">
+        <v>1.22</v>
+      </c>
+      <c r="Z147">
+        <v>4.14</v>
+      </c>
+      <c r="AA147">
+        <v>1.8</v>
+      </c>
+      <c r="AB147">
+        <v>2.09</v>
+      </c>
+      <c r="AC147">
+        <v>2.92</v>
+      </c>
+      <c r="AD147">
+        <v>1.42</v>
+      </c>
+      <c r="AE147">
+        <v>1.11</v>
+      </c>
+      <c r="AF147">
         <v>1.6</v>
       </c>
-      <c r="W147">
-        <v>1.11</v>
-      </c>
-      <c r="X147">
-        <v>1.03</v>
-      </c>
-      <c r="Y147">
-        <v>1.17</v>
-      </c>
-      <c r="Z147">
-        <v>4.6</v>
-      </c>
-      <c r="AA147">
-        <v>1.57</v>
-      </c>
-      <c r="AB147">
-        <v>2.3</v>
-      </c>
-      <c r="AC147">
-        <v>2.55</v>
-      </c>
-      <c r="AD147">
-        <v>1.53</v>
-      </c>
-      <c r="AE147">
-        <v>1.2</v>
-      </c>
-      <c r="AF147">
-        <v>1.57</v>
-      </c>
       <c r="AG147">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK147">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24608,46 +24608,46 @@
         <v>2.7</v>
       </c>
       <c r="R149">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S149">
         <v>1.36</v>
       </c>
       <c r="T149">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U149">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V149">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W149">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z149">
         <v>3.7</v>
       </c>
       <c r="AA149">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB149">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC149">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD149">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE149">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF149">
         <v>1.62</v>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O150">
         <v>5.25</v>
@@ -24768,19 +24768,19 @@
         <v>7</v>
       </c>
       <c r="Q150">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R150">
         <v>2.8</v>
       </c>
       <c r="S150">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T150">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="U150">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V150">
         <v>1.62</v>
@@ -24792,31 +24792,31 @@
         <v>1.02</v>
       </c>
       <c r="Y150">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z150">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA150">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB150">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AC150">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD150">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE150">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF150">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG150">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24934,22 +24934,22 @@
         <v>3.74</v>
       </c>
       <c r="R151">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S151">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T151">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U151">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V151">
         <v>1.42</v>
       </c>
       <c r="W151">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
         <v>1.03</v>
@@ -24958,7 +24958,7 @@
         <v>1.25</v>
       </c>
       <c r="Z151">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA151">
         <v>1.8</v>
@@ -24967,7 +24967,7 @@
         <v>1.9</v>
       </c>
       <c r="AC151">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD151">
         <v>1.3</v>
@@ -25091,55 +25091,55 @@
         <v>3.15</v>
       </c>
       <c r="P152">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q152">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R152">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S152">
         <v>1.38</v>
       </c>
       <c r="T152">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U152">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="V152">
         <v>1.32</v>
       </c>
       <c r="W152">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X152">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y152">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z152">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AA152">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB152">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC152">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="AD152">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE152">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF152">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG152">
         <v>1.93</v>
@@ -25158,7 +25158,7 @@
         <v>1.44</v>
       </c>
       <c r="AK152">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25248,7 +25248,7 @@
         </is>
       </c>
       <c r="N153">
-        <v>3.06</v>
+        <v>2.41</v>
       </c>
       <c r="O153">
         <v>3.2</v>
@@ -25321,7 +25321,7 @@
         <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25462,7 +25462,7 @@
         <v>1.25</v>
       </c>
       <c r="AE154">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF154">
         <v>1.77</v>
@@ -25749,7 +25749,7 @@
         <v>2.38</v>
       </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S156">
         <v>1.37</v>
@@ -25779,13 +25779,13 @@
         <v>1.97</v>
       </c>
       <c r="AB156">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC156">
         <v>3.45</v>
       </c>
       <c r="AD156">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE156">
         <v>1.06</v>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25936,10 +25936,10 @@
         <v>1.28</v>
       </c>
       <c r="Z157">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA157">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB157">
         <v>1.76</v>
@@ -25973,7 +25973,7 @@
         <v>1.25</v>
       </c>
       <c r="AK157">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26108,7 +26108,7 @@
         <v>1.53</v>
       </c>
       <c r="AC158">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD158">
         <v>1.14</v>
@@ -26120,7 +26120,7 @@
         <v>1.95</v>
       </c>
       <c r="AG158">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK158">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,31 +26226,31 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O159">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P159">
         <v>3.45</v>
       </c>
       <c r="Q159">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R159">
         <v>1.93</v>
       </c>
       <c r="S159">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T159">
         <v>2.5</v>
       </c>
       <c r="U159">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="V159">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W159">
         <v>1.04</v>
@@ -26262,25 +26262,25 @@
         <v>1.41</v>
       </c>
       <c r="Z159">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AA159">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AB159">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC159">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD159">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE159">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF159">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG159">
         <v>1.67</v>
@@ -26299,7 +26299,7 @@
         <v>1.24</v>
       </c>
       <c r="AK159">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26561,16 +26561,16 @@
         <v>10</v>
       </c>
       <c r="Q161">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R161">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T161">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U161">
         <v>1.8</v>
@@ -26579,7 +26579,7 @@
         <v>1.76</v>
       </c>
       <c r="W161">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X161">
         <v>1.01</v>
@@ -26588,10 +26588,10 @@
         <v>1.07</v>
       </c>
       <c r="Z161">
-        <v>7.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA161">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB161">
         <v>2.83</v>
@@ -26609,7 +26609,7 @@
         <v>1.85</v>
       </c>
       <c r="AG161">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK161">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26739,7 +26739,7 @@
         <v>3.2</v>
       </c>
       <c r="V162">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W162">
         <v>1.03</v>
@@ -26757,13 +26757,13 @@
         <v>2.2</v>
       </c>
       <c r="AB162">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC162">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD162">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE162">
         <v>1.03</v>
@@ -26905,7 +26905,7 @@
         <v>1.5</v>
       </c>
       <c r="W163">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X163">
         <v>1.02</v>
@@ -26929,7 +26929,7 @@
         <v>1.33</v>
       </c>
       <c r="AE163">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF163">
         <v>1.5</v>
@@ -27204,25 +27204,25 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="O165">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P165">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="Q165">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R165">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="S165">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T165">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U165">
         <v>2.95</v>
@@ -27231,37 +27231,37 @@
         <v>1.33</v>
       </c>
       <c r="W165">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X165">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y165">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z165">
         <v>2.85</v>
       </c>
       <c r="AA165">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AB165">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC165">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="AD165">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE165">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF165">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG165">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK165">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27400,7 +27400,7 @@
         <v>1.08</v>
       </c>
       <c r="Y166">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z166">
         <v>2.7</v>
@@ -27418,7 +27418,7 @@
         <v>1.18</v>
       </c>
       <c r="AE166">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF166">
         <v>1.91</v>
@@ -27533,10 +27533,10 @@
         <v>3.93</v>
       </c>
       <c r="O167">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P167">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q167">
         <v>4.2</v>
@@ -27551,7 +27551,7 @@
         <v>2.9</v>
       </c>
       <c r="U167">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V167">
         <v>1.4</v>
@@ -27584,7 +27584,7 @@
         <v>1.07</v>
       </c>
       <c r="AF167">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG167">
         <v>1.95</v>
@@ -27720,7 +27720,7 @@
         <v>1.4</v>
       </c>
       <c r="W168">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X168">
         <v>1.05</v>
@@ -27732,13 +27732,13 @@
         <v>3.55</v>
       </c>
       <c r="AA168">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB168">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC168">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="AD168">
         <v>1.32</v>
@@ -27766,7 +27766,7 @@
         <v>1.25</v>
       </c>
       <c r="AK168">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -29172,7 +29172,7 @@
         <v>1.67</v>
       </c>
       <c r="R177">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="S177">
         <v>1.18</v>
@@ -29196,7 +29196,7 @@
         <v>1.07</v>
       </c>
       <c r="Z177">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA177">
         <v>1.33</v>
@@ -29214,10 +29214,10 @@
         <v>1.36</v>
       </c>
       <c r="AF177">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG177">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.11</v>
       </c>
       <c r="AK177">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29341,7 +29341,7 @@
         <v>1.51</v>
       </c>
       <c r="T178">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="U178">
         <v>3.25</v>
@@ -29368,10 +29368,10 @@
         <v>1.57</v>
       </c>
       <c r="AC178">
-        <v>4.54</v>
+        <v>4.39</v>
       </c>
       <c r="AD178">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE178">
         <v>1.01</v>
@@ -29380,7 +29380,7 @@
         <v>2.21</v>
       </c>
       <c r="AG178">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29486,10 +29486,10 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P179">
         <v>1.86</v>
@@ -29824,7 +29824,7 @@
         <v>2.7</v>
       </c>
       <c r="R181">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S181">
         <v>1.53</v>
@@ -29833,10 +29833,10 @@
         <v>2.45</v>
       </c>
       <c r="U181">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V181">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W181">
         <v>1.03</v>
@@ -29860,7 +29860,7 @@
         <v>4.35</v>
       </c>
       <c r="AD181">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE181">
         <v>1.01</v>
@@ -29990,10 +29990,10 @@
         <v>2.15</v>
       </c>
       <c r="S182">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T182">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="U182">
         <v>2.73</v>
@@ -30464,19 +30464,19 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O185">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P185">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q185">
         <v>3</v>
       </c>
       <c r="R185">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S185">
         <v>1.56</v>
@@ -30485,10 +30485,10 @@
         <v>2.4</v>
       </c>
       <c r="U185">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V185">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W185">
         <v>1.04</v>
@@ -30503,7 +30503,7 @@
         <v>2.45</v>
       </c>
       <c r="AA185">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AB185">
         <v>1.48</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O186">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="P186">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="Q186">
         <v>1.85</v>
@@ -30669,16 +30669,16 @@
         <v>1.3</v>
       </c>
       <c r="AB186">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AC186">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD186">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AE186">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AF186">
         <v>1.4</v>
@@ -30796,7 +30796,7 @@
         <v>3.6</v>
       </c>
       <c r="P187">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -30965,7 +30965,7 @@
         <v>2.77</v>
       </c>
       <c r="R188">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S188">
         <v>1.44</v>
@@ -30989,28 +30989,28 @@
         <v>1.45</v>
       </c>
       <c r="Z188">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AA188">
         <v>2.25</v>
       </c>
       <c r="AB188">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC188">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD188">
         <v>1.14</v>
       </c>
       <c r="AE188">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF188">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG188">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK188">
         <v>1.62</v>
@@ -31282,13 +31282,13 @@
         <v>1.7</v>
       </c>
       <c r="O190">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P190">
         <v>3.97</v>
       </c>
       <c r="Q190">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R190">
         <v>2.29</v>
@@ -31300,10 +31300,10 @@
         <v>3.8</v>
       </c>
       <c r="U190">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V190">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W190">
         <v>1.17</v>
@@ -31318,13 +31318,13 @@
         <v>5.1</v>
       </c>
       <c r="AA190">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB190">
         <v>2.55</v>
       </c>
       <c r="AC190">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD190">
         <v>1.6</v>
@@ -31336,7 +31336,7 @@
         <v>1.5</v>
       </c>
       <c r="AG190">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK190">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,10 +31451,10 @@
         <v>2.45</v>
       </c>
       <c r="Q191">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R191">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S191">
         <v>1.3</v>
@@ -31466,7 +31466,7 @@
         <v>2.63</v>
       </c>
       <c r="V191">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W191">
         <v>1.08</v>
@@ -31478,25 +31478,25 @@
         <v>1.2</v>
       </c>
       <c r="Z191">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA191">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB191">
         <v>2</v>
       </c>
       <c r="AC191">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD191">
         <v>1.33</v>
       </c>
       <c r="AE191">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF191">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG191">
         <v>2.2</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK191">
         <v>1.44</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O192">
         <v>3.15</v>
@@ -31638,7 +31638,7 @@
         <v>1.06</v>
       </c>
       <c r="Y192">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z192">
         <v>3.05</v>
@@ -31786,7 +31786,7 @@
         <v>1.25</v>
       </c>
       <c r="T193">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U193">
         <v>2.3</v>
@@ -31810,7 +31810,7 @@
         <v>1.66</v>
       </c>
       <c r="AB193">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC193">
         <v>2.63</v>
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK193">
         <v>1.36</v>
@@ -32115,10 +32115,10 @@
         <v>3.5</v>
       </c>
       <c r="U195">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V195">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W195">
         <v>1.11</v>
@@ -32139,7 +32139,7 @@
         <v>2.55</v>
       </c>
       <c r="AC195">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AD195">
         <v>1.56</v>
@@ -32151,7 +32151,7 @@
         <v>1.55</v>
       </c>
       <c r="AG195">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -644,7 +644,7 @@
         <v>4.1</v>
       </c>
       <c r="Q2">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R2">
         <v>2.09</v>
@@ -662,7 +662,7 @@
         <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
         <v>3.8</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AD4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
         <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA5">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AC5">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="O17">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>7</v>
+        <v>3.59</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="R17">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S17">
+        <v>1.26</v>
+      </c>
+      <c r="T17">
+        <v>3.32</v>
+      </c>
+      <c r="U17">
+        <v>2.25</v>
+      </c>
+      <c r="V17">
+        <v>1.53</v>
+      </c>
+      <c r="W17">
+        <v>1.1</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.14</v>
+      </c>
+      <c r="Z17">
+        <v>4.33</v>
+      </c>
+      <c r="AA17">
+        <v>1.57</v>
+      </c>
+      <c r="AB17">
+        <v>2.25</v>
+      </c>
+      <c r="AC17">
+        <v>2.35</v>
+      </c>
+      <c r="AD17">
+        <v>1.47</v>
+      </c>
+      <c r="AE17">
+        <v>1.2</v>
+      </c>
+      <c r="AF17">
+        <v>1.53</v>
+      </c>
+      <c r="AG17">
+        <v>2.3</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.25</v>
       </c>
-      <c r="T17">
-        <v>3.28</v>
-      </c>
-      <c r="U17">
-        <v>2.2</v>
-      </c>
-      <c r="V17">
-        <v>1.66</v>
-      </c>
-      <c r="W17">
-        <v>1.12</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.13</v>
-      </c>
-      <c r="Z17">
-        <v>4.55</v>
-      </c>
-      <c r="AA17">
-        <v>1.49</v>
-      </c>
-      <c r="AB17">
-        <v>2.3</v>
-      </c>
-      <c r="AC17">
-        <v>2.38</v>
-      </c>
-      <c r="AD17">
-        <v>1.56</v>
-      </c>
-      <c r="AE17">
-        <v>1.25</v>
-      </c>
-      <c r="AF17">
-        <v>1.8</v>
-      </c>
-      <c r="AG17">
-        <v>1.87</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.11</v>
-      </c>
       <c r="AK17">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="P19">
-        <v>3.59</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK19">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="O49">
         <v>3.18</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O53">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="P53">
-        <v>8.25</v>
+        <v>7.15</v>
       </c>
       <c r="Q53">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R53">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S53">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T53">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="U53">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="V53">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W53">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.08</v>
       </c>
       <c r="Z53">
-        <v>5.45</v>
+        <v>7.1</v>
       </c>
       <c r="AA53">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AB53">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC53">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD53">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AE53">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG53">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK53">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O54">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="P54">
-        <v>7.15</v>
+        <v>8.25</v>
       </c>
       <c r="Q54">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R54">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S54">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="U54">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="V54">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>7.1</v>
+        <v>5.45</v>
       </c>
       <c r="AA54">
+        <v>1.39</v>
+      </c>
+      <c r="AB54">
+        <v>2.5</v>
+      </c>
+      <c r="AC54">
+        <v>2.04</v>
+      </c>
+      <c r="AD54">
+        <v>1.7</v>
+      </c>
+      <c r="AE54">
         <v>1.3</v>
       </c>
-      <c r="AB54">
-        <v>3.2</v>
-      </c>
-      <c r="AC54">
-        <v>1.83</v>
-      </c>
-      <c r="AD54">
-        <v>1.92</v>
-      </c>
-      <c r="AE54">
-        <v>1.33</v>
-      </c>
       <c r="AF54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG54">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -16947,19 +16947,19 @@
         <v>2.5</v>
       </c>
       <c r="R102">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S102">
         <v>1.25</v>
       </c>
       <c r="T102">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U102">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V102">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W102">
         <v>1.12</v>
@@ -16968,28 +16968,28 @@
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z102">
         <v>4.4</v>
       </c>
       <c r="AA102">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB102">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC102">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AD102">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE102">
         <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG102">
         <v>2.4</v>
@@ -17008,7 +17008,7 @@
         <v>1.36</v>
       </c>
       <c r="AK102">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18891,25 +18891,25 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O114">
         <v>3.4</v>
       </c>
       <c r="P114">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q114">
         <v>2.3</v>
       </c>
       <c r="R114">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S114">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U114">
         <v>2.8</v>
@@ -18924,31 +18924,31 @@
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
         <v>2.95</v>
       </c>
       <c r="AA114">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC114">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD114">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG114">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK114">
         <v>1.95</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O137">
         <v>2.62</v>
@@ -22697,7 +22697,7 @@
         <v>2.7</v>
       </c>
       <c r="AG137">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.82</v>
+        <v>3.25</v>
       </c>
       <c r="O143">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P143">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q143">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="R143">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S143">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T143">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="U143">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V143">
         <v>1.22</v>
       </c>
       <c r="W143">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y143">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z143">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AA143">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="AB143">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC143">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD143">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE143">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF143">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG143">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK143">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="O144">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P144">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="Q144">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="R144">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S144">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T144">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="U144">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V144">
         <v>1.22</v>
       </c>
       <c r="W144">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X144">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y144">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z144">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AA144">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AB144">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC144">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD144">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE144">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF144">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG144">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK144">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25758,7 +25758,7 @@
         <v>2.85</v>
       </c>
       <c r="U156">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="V156">
         <v>1.38</v>
@@ -25767,28 +25767,28 @@
         <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
         <v>1.28</v>
       </c>
       <c r="Z156">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA156">
         <v>1.97</v>
       </c>
       <c r="AB156">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC156">
         <v>3.45</v>
       </c>
       <c r="AD156">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE156">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF156">
         <v>1.85</v>
@@ -25921,7 +25921,7 @@
         <v>2.9</v>
       </c>
       <c r="U157">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V157">
         <v>1.39</v>
@@ -26105,7 +26105,7 @@
         <v>2.28</v>
       </c>
       <c r="AB158">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC158">
         <v>4.4</v>
@@ -26117,7 +26117,7 @@
         <v>1.01</v>
       </c>
       <c r="AF158">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG158">
         <v>1.67</v>
@@ -26244,7 +26244,7 @@
         <v>1.55</v>
       </c>
       <c r="T159">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U159">
         <v>3.42</v>
@@ -26265,10 +26265,10 @@
         <v>2.41</v>
       </c>
       <c r="AA159">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB159">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC159">
         <v>5.25</v>
@@ -26280,7 +26280,7 @@
         <v>1.01</v>
       </c>
       <c r="AF159">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG159">
         <v>1.67</v>
@@ -26389,16 +26389,16 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O160">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P160">
         <v>2.6</v>
       </c>
       <c r="Q160">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R160">
         <v>2.09</v>
@@ -26407,19 +26407,19 @@
         <v>1.3</v>
       </c>
       <c r="T160">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U160">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V160">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y160">
         <v>1.25</v>
@@ -26428,19 +26428,19 @@
         <v>3.7</v>
       </c>
       <c r="AA160">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB160">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC160">
         <v>3</v>
       </c>
       <c r="AD160">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE160">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF160">
         <v>1.62</v>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK160">
         <v>1.47</v>
@@ -26552,19 +26552,19 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O161">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="P161">
-        <v>10</v>
+        <v>8.15</v>
       </c>
       <c r="Q161">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R161">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S161">
         <v>1.17</v>
@@ -26573,13 +26573,13 @@
         <v>4.5</v>
       </c>
       <c r="U161">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="V161">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W161">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X161">
         <v>1.01</v>
@@ -26588,28 +26588,28 @@
         <v>1.07</v>
       </c>
       <c r="Z161">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA161">
         <v>1.32</v>
       </c>
       <c r="AB161">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AC161">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AD161">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE161">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF161">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG161">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -27041,10 +27041,10 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O164">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P164">
         <v>5.5</v>
@@ -27062,7 +27062,7 @@
         <v>2.33</v>
       </c>
       <c r="U164">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V164">
         <v>1.26</v>
@@ -27089,16 +27089,16 @@
         <v>5</v>
       </c>
       <c r="AD164">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE164">
         <v>1.02</v>
       </c>
       <c r="AF164">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AG164">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27367,25 +27367,25 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O166">
         <v>3.2</v>
       </c>
       <c r="P166">
-        <v>3.89</v>
+        <v>3.45</v>
       </c>
       <c r="Q166">
         <v>2.54</v>
       </c>
       <c r="R166">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S166">
         <v>1.46</v>
       </c>
       <c r="T166">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U166">
         <v>3.24</v>
@@ -27412,7 +27412,7 @@
         <v>1.57</v>
       </c>
       <c r="AC166">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AD166">
         <v>1.18</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="O170">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P170">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q170">
+        <v>2.16</v>
+      </c>
+      <c r="R170">
         <v>2.32</v>
       </c>
-      <c r="R170">
-        <v>2.07</v>
-      </c>
       <c r="S170">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T170">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="U170">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V170">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W170">
         <v>1.08</v>
       </c>
       <c r="X170">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y170">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z170">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA170">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB170">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC170">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AD170">
         <v>1.29</v>
       </c>
       <c r="AE170">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG170">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK170">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="O171">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P171">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q171">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R171">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="S171">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T171">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="U171">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V171">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W171">
         <v>1.08</v>
       </c>
       <c r="X171">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z171">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA171">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB171">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC171">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AD171">
         <v>1.29</v>
       </c>
       <c r="AE171">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF171">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG171">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK171">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28523,10 +28523,10 @@
         <v>1.74</v>
       </c>
       <c r="S173">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T173">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="U173">
         <v>4</v>
@@ -28541,7 +28541,7 @@
         <v>1.15</v>
       </c>
       <c r="Y173">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z173">
         <v>2.1</v>
@@ -28680,25 +28680,25 @@
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R174">
         <v>2.3</v>
       </c>
       <c r="S174">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T174">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U174">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="V174">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W174">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X174">
         <v>1.03</v>
@@ -28710,19 +28710,19 @@
         <v>5.2</v>
       </c>
       <c r="AA174">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB174">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC174">
         <v>2.4</v>
       </c>
       <c r="AD174">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE174">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF174">
         <v>1.52</v>
@@ -28843,7 +28843,7 @@
         <v>4.63</v>
       </c>
       <c r="Q175">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="R175">
         <v>1.91</v>
@@ -28858,7 +28858,7 @@
         <v>3.9</v>
       </c>
       <c r="V175">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W175">
         <v>1.03</v>
@@ -28876,7 +28876,7 @@
         <v>2.78</v>
       </c>
       <c r="AB175">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC175">
         <v>5.65</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O176">
         <v>2.75</v>
       </c>
       <c r="P176">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q176">
         <v>2.76</v>
@@ -29015,7 +29015,7 @@
         <v>1.71</v>
       </c>
       <c r="T176">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U176">
         <v>4.5</v>
@@ -29160,43 +29160,43 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="O177">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P177">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q177">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="R177">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S177">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T177">
         <v>4.5</v>
       </c>
       <c r="U177">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V177">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W177">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z177">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AA177">
         <v>1.33</v>
@@ -29208,7 +29208,7 @@
         <v>1.85</v>
       </c>
       <c r="AD177">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE177">
         <v>1.36</v>
@@ -29217,7 +29217,7 @@
         <v>1.55</v>
       </c>
       <c r="AG177">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK177">
         <v>2.5</v>
@@ -29323,22 +29323,22 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="O178">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
         <v>5.24</v>
       </c>
       <c r="Q178">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R178">
         <v>2</v>
       </c>
       <c r="S178">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T178">
         <v>2.02</v>
@@ -29347,7 +29347,7 @@
         <v>3.25</v>
       </c>
       <c r="V178">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W178">
         <v>1.05</v>
@@ -29359,10 +29359,10 @@
         <v>1.44</v>
       </c>
       <c r="Z178">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AA178">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AB178">
         <v>1.57</v>
@@ -29492,7 +29492,7 @@
         <v>3.5</v>
       </c>
       <c r="P179">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q179">
         <v>4.5</v>
@@ -29504,7 +29504,7 @@
         <v>1.41</v>
       </c>
       <c r="T179">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U179">
         <v>2.75</v>
@@ -29525,10 +29525,10 @@
         <v>3.24</v>
       </c>
       <c r="AA179">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB179">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC179">
         <v>3.5</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK179">
         <v>1.26</v>
@@ -29652,10 +29652,10 @@
         <v>2.3</v>
       </c>
       <c r="O180">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="P180">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q180">
         <v>2.9</v>
@@ -29667,7 +29667,7 @@
         <v>1.41</v>
       </c>
       <c r="T180">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U180">
         <v>2.81</v>
@@ -29697,10 +29697,10 @@
         <v>3.18</v>
       </c>
       <c r="AD180">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE180">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF180">
         <v>1.73</v>
@@ -29842,7 +29842,7 @@
         <v>1.03</v>
       </c>
       <c r="X181">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y181">
         <v>1.44</v>
@@ -29851,7 +29851,7 @@
         <v>2.54</v>
       </c>
       <c r="AA181">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AB181">
         <v>1.52</v>
@@ -29860,13 +29860,13 @@
         <v>4.35</v>
       </c>
       <c r="AD181">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE181">
         <v>1.01</v>
       </c>
       <c r="AF181">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG181">
         <v>1.67</v>
@@ -29975,10 +29975,10 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O182">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P182">
         <v>2.54</v>
@@ -29990,13 +29990,13 @@
         <v>2.15</v>
       </c>
       <c r="S182">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T182">
         <v>2.9</v>
       </c>
       <c r="U182">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V182">
         <v>1.36</v>
@@ -30005,7 +30005,7 @@
         <v>1.07</v>
       </c>
       <c r="X182">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y182">
         <v>1.31</v>
@@ -30014,13 +30014,13 @@
         <v>3.23</v>
       </c>
       <c r="AA182">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB182">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC182">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD182">
         <v>1.28</v>
@@ -30029,7 +30029,7 @@
         <v>1.06</v>
       </c>
       <c r="AF182">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG182">
         <v>2</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK182">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30138,19 +30138,19 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O183">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P183">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q183">
         <v>1.87</v>
       </c>
       <c r="R183">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S183">
         <v>1.29</v>
@@ -30159,37 +30159,37 @@
         <v>3.3</v>
       </c>
       <c r="U183">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V183">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W183">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X183">
         <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z183">
         <v>4.4</v>
       </c>
       <c r="AA183">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB183">
         <v>2.2</v>
       </c>
       <c r="AC183">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AD183">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE183">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
         <v>1.75</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK183">
         <v>2.35</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O186">
         <v>4.75</v>
       </c>
       <c r="P186">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q186">
         <v>1.85</v>
@@ -30645,13 +30645,13 @@
         <v>1.18</v>
       </c>
       <c r="T186">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U186">
+        <v>1.84</v>
+      </c>
+      <c r="V186">
         <v>1.91</v>
-      </c>
-      <c r="V186">
-        <v>1.8</v>
       </c>
       <c r="W186">
         <v>1.25</v>
@@ -30672,7 +30672,7 @@
         <v>3.12</v>
       </c>
       <c r="AC186">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AD186">
         <v>1.97</v>
@@ -30790,16 +30790,16 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O187">
         <v>3.6</v>
       </c>
       <c r="P187">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="Q187">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R187">
         <v>2.25</v>
@@ -30814,7 +30814,7 @@
         <v>2.4</v>
       </c>
       <c r="V187">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W187">
         <v>1.09</v>
@@ -30826,16 +30826,16 @@
         <v>1.21</v>
       </c>
       <c r="Z187">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="AA187">
         <v>1.66</v>
       </c>
       <c r="AB187">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC187">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD187">
         <v>1.48</v>
@@ -30953,16 +30953,16 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O188">
         <v>3.1</v>
       </c>
       <c r="P188">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q188">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="R188">
         <v>1.9</v>
@@ -31140,7 +31140,7 @@
         <v>2.3</v>
       </c>
       <c r="V189">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W189">
         <v>1.12</v>
@@ -31164,7 +31164,7 @@
         <v>2.54</v>
       </c>
       <c r="AD189">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE189">
         <v>1.14</v>
@@ -31279,7 +31279,7 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O190">
         <v>3.8</v>
@@ -31288,10 +31288,10 @@
         <v>3.97</v>
       </c>
       <c r="Q190">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R190">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S190">
         <v>1.22</v>
@@ -31306,7 +31306,7 @@
         <v>1.6</v>
       </c>
       <c r="W190">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X190">
         <v>1.01</v>
@@ -31321,13 +31321,13 @@
         <v>1.44</v>
       </c>
       <c r="AB190">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AC190">
         <v>2.19</v>
       </c>
       <c r="AD190">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE190">
         <v>1.19</v>
@@ -31638,7 +31638,7 @@
         <v>1.06</v>
       </c>
       <c r="Y192">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z192">
         <v>3.05</v>
@@ -31940,7 +31940,7 @@
         <v>2.3</v>
       </c>
       <c r="Q194">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="R194">
         <v>2.18</v>
@@ -31955,7 +31955,7 @@
         <v>2.75</v>
       </c>
       <c r="V194">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W194">
         <v>1.07</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AK194">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,7 +32094,7 @@
         </is>
       </c>
       <c r="N195">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O195">
         <v>3.6</v>
@@ -32151,7 +32151,7 @@
         <v>1.55</v>
       </c>
       <c r="AG195">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB3">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="O4">
         <v>3.8</v>
       </c>
       <c r="P4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -988,13 +988,13 @@
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
         <v>3.8</v>
@@ -1003,7 +1003,7 @@
         <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>2.8</v>
@@ -1015,7 +1015,7 @@
         <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG4">
         <v>1.96</v>
@@ -1034,7 +1034,7 @@
         <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P5">
         <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
         <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="U5">
         <v>2.14</v>
@@ -1151,37 +1151,37 @@
         <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AB5">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE5">
         <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
         <v>2.85</v>
@@ -1299,7 +1299,7 @@
         <v>2.45</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
         <v>1.3</v>
@@ -1323,22 +1323,22 @@
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
         <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
@@ -1453,10 +1453,10 @@
         <v>2.2</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -1471,10 +1471,10 @@
         <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>1.12</v>
@@ -1492,7 +1492,7 @@
         <v>1.58</v>
       </c>
       <c r="AB7">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC7">
         <v>2.6</v>
@@ -1501,7 +1501,7 @@
         <v>1.44</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.53</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
         <v>1.62</v>
@@ -1616,31 +1616,31 @@
         <v>1.95</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
         <v>3.85</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T8">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V8">
         <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.06</v>
@@ -1649,28 +1649,28 @@
         <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>3.34</v>
+        <v>3.66</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG8">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
         <v>1.75</v>
@@ -1791,13 +1791,13 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="U9">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="V9">
         <v>1.25</v>
@@ -1806,25 +1806,25 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC9">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.31</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,31 +1942,31 @@
         <v>3.35</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q10">
-        <v>4.01</v>
+        <v>4.1</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1.05</v>
@@ -1981,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
         <v>3.5</v>
@@ -1993,7 +1993,7 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>9.15</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>5.55</v>
+        <v>5.95</v>
       </c>
       <c r="P11">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>2.8</v>
       </c>
       <c r="O12">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -2283,7 +2283,7 @@
         <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U12">
         <v>2.34</v>
@@ -2301,7 +2301,7 @@
         <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2310,7 +2310,7 @@
         <v>2.28</v>
       </c>
       <c r="AC12">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="AD12">
         <v>1.44</v>
@@ -2431,10 +2431,10 @@
         <v>3.9</v>
       </c>
       <c r="O13">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
@@ -2443,16 +2443,16 @@
         <v>2.15</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
         <v>2.8</v>
       </c>
       <c r="U13">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
         <v>1.03</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -2621,7 +2621,7 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>1.29</v>
@@ -2633,7 +2633,7 @@
         <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC14">
         <v>3.35</v>
@@ -2648,7 +2648,7 @@
         <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AK14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,65 +2754,65 @@
         </is>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q15">
         <v>2.55</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
+        <v>1.01</v>
+      </c>
+      <c r="X15">
         <v>1.02</v>
       </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB15">
         <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
+        <v>1.87</v>
+      </c>
+      <c r="AG15">
         <v>1.83</v>
       </c>
-      <c r="AG15">
-        <v>1.85</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
         <v>1.7</v>
@@ -2917,43 +2917,43 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="R16">
         <v>2</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V16">
         <v>1.33</v>
       </c>
       <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
         <v>1.05</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA16">
         <v>2.2</v>
@@ -2962,7 +2962,7 @@
         <v>1.6</v>
       </c>
       <c r="AC16">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD16">
         <v>1.16</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="Q17">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T17">
-        <v>3.32</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AB17">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>2.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD17">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.27</v>
+      </c>
+      <c r="O18">
+        <v>5</v>
+      </c>
+      <c r="P18">
+        <v>7.75</v>
+      </c>
+      <c r="Q18">
         <v>1.7</v>
       </c>
-      <c r="O18">
-        <v>3.65</v>
-      </c>
-      <c r="P18">
-        <v>4.2</v>
-      </c>
-      <c r="Q18">
-        <v>2.3</v>
-      </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="AA18">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AC18">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="AD18">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AE18">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="R19">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S19">
+        <v>1.26</v>
+      </c>
+      <c r="T19">
+        <v>3.32</v>
+      </c>
+      <c r="U19">
+        <v>2.25</v>
+      </c>
+      <c r="V19">
+        <v>1.57</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>1.14</v>
+      </c>
+      <c r="Z19">
+        <v>4.33</v>
+      </c>
+      <c r="AA19">
+        <v>1.57</v>
+      </c>
+      <c r="AB19">
+        <v>2.25</v>
+      </c>
+      <c r="AC19">
+        <v>2.35</v>
+      </c>
+      <c r="AD19">
+        <v>1.47</v>
+      </c>
+      <c r="AE19">
+        <v>1.2</v>
+      </c>
+      <c r="AF19">
+        <v>1.53</v>
+      </c>
+      <c r="AG19">
+        <v>2.3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.25</v>
       </c>
-      <c r="T19">
-        <v>3.28</v>
-      </c>
-      <c r="U19">
-        <v>2.2</v>
-      </c>
-      <c r="V19">
-        <v>1.66</v>
-      </c>
-      <c r="W19">
-        <v>1.12</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.13</v>
-      </c>
-      <c r="Z19">
-        <v>4.55</v>
-      </c>
-      <c r="AA19">
-        <v>1.49</v>
-      </c>
-      <c r="AB19">
-        <v>2.3</v>
-      </c>
-      <c r="AC19">
-        <v>2.38</v>
-      </c>
-      <c r="AD19">
-        <v>1.56</v>
-      </c>
-      <c r="AE19">
-        <v>1.25</v>
-      </c>
-      <c r="AF19">
-        <v>1.8</v>
-      </c>
-      <c r="AG19">
-        <v>1.87</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.11</v>
-      </c>
       <c r="AK19">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O21">
         <v>3.1</v>
       </c>
       <c r="P21">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T21">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="U21">
         <v>3.2</v>
@@ -3762,16 +3762,16 @@
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
         <v>1.37</v>
       </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB21">
         <v>1.61</v>
@@ -3780,16 +3780,16 @@
         <v>4.5</v>
       </c>
       <c r="AD21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG21">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O22">
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q22">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V22">
         <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD22">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
         <v>1.95</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O23">
         <v>3.9</v>
@@ -4067,55 +4067,55 @@
         <v>3.9</v>
       </c>
       <c r="Q23">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="U23">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>6.06</v>
+        <v>6.17</v>
       </c>
       <c r="AA23">
         <v>1.42</v>
       </c>
       <c r="AB23">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC23">
         <v>2.05</v>
       </c>
       <c r="AD23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
         <v>1.27</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O24">
         <v>3.6</v>
@@ -4263,10 +4263,10 @@
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AC24">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AD24">
         <v>1.46</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
         <v>2.4</v>
@@ -4420,7 +4420,7 @@
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA25">
         <v>1.57</v>
@@ -4432,7 +4432,7 @@
         <v>2.45</v>
       </c>
       <c r="AD25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE25">
         <v>1.2</v>
@@ -4457,7 +4457,7 @@
         <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,16 +4550,16 @@
         <v>2.51</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q26">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R26">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S26">
         <v>1.25</v>
@@ -4571,40 +4571,40 @@
         <v>2.33</v>
       </c>
       <c r="V26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4.6</v>
+        <v>5.26</v>
       </c>
       <c r="AA26">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AD26">
+        <v>1.51</v>
+      </c>
+      <c r="AE26">
+        <v>1.2</v>
+      </c>
+      <c r="AF26">
         <v>1.5</v>
       </c>
-      <c r="AE26">
-        <v>1.18</v>
-      </c>
-      <c r="AF26">
-        <v>1.55</v>
-      </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O27">
         <v>3.9</v>
@@ -4719,7 +4719,7 @@
         <v>5.15</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R27">
         <v>2.28</v>
@@ -4731,7 +4731,7 @@
         <v>3.14</v>
       </c>
       <c r="U27">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
         <v>1.46</v>
@@ -4743,10 +4743,10 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AA27">
         <v>1.74</v>
@@ -4767,7 +4767,7 @@
         <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
         <v>3.3</v>
@@ -4894,13 +4894,13 @@
         <v>2.41</v>
       </c>
       <c r="U28">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V28">
         <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1.04</v>
@@ -4915,7 +4915,7 @@
         <v>2.2</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC28">
         <v>4.2</v>
@@ -4927,10 +4927,10 @@
         <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG28">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5042,31 +5042,31 @@
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
         <v>1.33</v>
@@ -5084,7 +5084,7 @@
         <v>3.6</v>
       </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
@@ -5109,7 +5109,7 @@
         <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O31">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q31">
-        <v>3.26</v>
+        <v>3.82</v>
       </c>
       <c r="R31">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
         <v>1.38</v>
@@ -5392,7 +5392,7 @@
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
         <v>1.25</v>
@@ -5401,10 +5401,10 @@
         <v>3.44</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB31">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC31">
         <v>3.25</v>
@@ -5413,10 +5413,10 @@
         <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
         <v>2.15</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,28 +5528,28 @@
         <v>1.48</v>
       </c>
       <c r="O32">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="Q32">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R32">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
         <v>1.12</v>
@@ -5558,22 +5558,22 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA32">
         <v>1.46</v>
       </c>
       <c r="AB32">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AC32">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD32">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE32">
         <v>1.19</v>
@@ -5582,7 +5582,7 @@
         <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK32">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -5706,13 +5706,13 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AC33">
         <v>2.45</v>
@@ -5739,13 +5739,13 @@
         <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
         <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>4.1</v>
@@ -5869,16 +5869,16 @@
         <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V34">
         <v>1.39</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5887,16 +5887,16 @@
         <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
         <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC34">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD34">
         <v>1.32</v>
@@ -6014,55 +6014,55 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O35">
         <v>5.3</v>
       </c>
       <c r="P35">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="Q35">
         <v>1.75</v>
       </c>
       <c r="R35">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="S35">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
         <v>4</v>
       </c>
       <c r="U35">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V35">
         <v>1.83</v>
       </c>
       <c r="W35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z35">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA35">
         <v>1.33</v>
       </c>
       <c r="AB35">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AC35">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AD35">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AE35">
         <v>1.38</v>
@@ -6071,7 +6071,7 @@
         <v>1.47</v>
       </c>
       <c r="AG35">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
         <v>2.75</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
         <v>3.08</v>
@@ -6201,7 +6201,7 @@
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6210,22 +6210,22 @@
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB36">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
@@ -6234,7 +6234,7 @@
         <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,16 +6343,16 @@
         <v>2</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.32</v>
@@ -6373,31 +6373,31 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC37">
         <v>3.05</v>
       </c>
       <c r="AD37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE37">
         <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG37">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O39">
         <v>3.6</v>
@@ -6687,7 +6687,7 @@
         <v>3.2</v>
       </c>
       <c r="U39">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
         <v>1.44</v>
@@ -6702,10 +6702,10 @@
         <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA39">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB39">
         <v>2.1</v>
@@ -6714,7 +6714,7 @@
         <v>2.66</v>
       </c>
       <c r="AD39">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
         <v>1.1</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="O40">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="Q40">
         <v>1.54</v>
@@ -6862,7 +6862,7 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
         <v>7</v>
@@ -6874,10 +6874,10 @@
         <v>3.25</v>
       </c>
       <c r="AC40">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AD40">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE40">
         <v>1.33</v>
@@ -6902,7 +6902,7 @@
         <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,16 +7001,16 @@
         <v>6.1</v>
       </c>
       <c r="Q41">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R41">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="S41">
         <v>1.17</v>
       </c>
       <c r="T41">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="U41">
         <v>1.99</v>
@@ -7034,19 +7034,19 @@
         <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AC41">
         <v>1.86</v>
       </c>
       <c r="AD41">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG41">
         <v>2.38</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O42">
         <v>3.55</v>
@@ -7167,7 +7167,7 @@
         <v>3</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.25</v>
@@ -7185,7 +7185,7 @@
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.16</v>
@@ -7194,13 +7194,13 @@
         <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB42">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC42">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
         <v>1.5</v>
@@ -7228,7 +7228,7 @@
         <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="O43">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P43">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Q43">
         <v>8</v>
@@ -7333,40 +7333,40 @@
         <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U43">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
         <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC43">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q44">
         <v>3.18</v>
@@ -7514,7 +7514,7 @@
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z44">
         <v>2.92</v>
@@ -7523,19 +7523,19 @@
         <v>2.08</v>
       </c>
       <c r="AB44">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC44">
         <v>3.8</v>
       </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
         <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
         <v>1.85</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7970,46 +7970,46 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.01</v>
+        <v>3.48</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R47">
         <v>2.16</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB47">
         <v>1.77</v>
@@ -8018,16 +8018,16 @@
         <v>3.45</v>
       </c>
       <c r="AD47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.53</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O50">
         <v>3.5</v>
@@ -8468,13 +8468,13 @@
         <v>1.85</v>
       </c>
       <c r="Q50">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T50">
         <v>3.12</v>
@@ -8489,7 +8489,7 @@
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.17</v>
@@ -8507,16 +8507,16 @@
         <v>2.63</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
         <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
         <v>6</v>
       </c>
       <c r="Q51">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R51">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="S51">
         <v>1.22</v>
@@ -8649,22 +8649,22 @@
         <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC51">
         <v>2.15</v>
@@ -8673,13 +8673,13 @@
         <v>1.65</v>
       </c>
       <c r="AE51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF51">
         <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8788,22 +8788,22 @@
         <v>2.32</v>
       </c>
       <c r="O52">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="P52">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q52">
-        <v>3.31</v>
+        <v>2.86</v>
       </c>
       <c r="R52">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S52">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T52">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="U52">
         <v>3.25</v>
@@ -8815,34 +8815,34 @@
         <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z52">
         <v>2.97</v>
       </c>
       <c r="AA52">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AB52">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC52">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="AD52">
         <v>1.18</v>
       </c>
       <c r="AE52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF52">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG52">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK52">
         <v>1.55</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="O53">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="P53">
-        <v>7.15</v>
+        <v>9</v>
       </c>
       <c r="Q53">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R53">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="S53">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="U53">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="W53">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
+        <v>1.09</v>
+      </c>
+      <c r="Z53">
+        <v>6</v>
+      </c>
+      <c r="AA53">
+        <v>1.39</v>
+      </c>
+      <c r="AB53">
+        <v>2.5</v>
+      </c>
+      <c r="AC53">
+        <v>2.04</v>
+      </c>
+      <c r="AD53">
+        <v>1.7</v>
+      </c>
+      <c r="AE53">
+        <v>1.25</v>
+      </c>
+      <c r="AF53">
+        <v>1.77</v>
+      </c>
+      <c r="AG53">
+        <v>1.91</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.08</v>
       </c>
-      <c r="Z53">
-        <v>7.1</v>
-      </c>
-      <c r="AA53">
-        <v>1.3</v>
-      </c>
-      <c r="AB53">
-        <v>3.2</v>
-      </c>
-      <c r="AC53">
-        <v>1.83</v>
-      </c>
-      <c r="AD53">
-        <v>1.92</v>
-      </c>
-      <c r="AE53">
-        <v>1.33</v>
-      </c>
-      <c r="AF53">
-        <v>1.64</v>
-      </c>
-      <c r="AG53">
-        <v>2.07</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.11</v>
-      </c>
       <c r="AK53">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O54">
-        <v>5.55</v>
+        <v>6.45</v>
       </c>
       <c r="P54">
-        <v>8.25</v>
+        <v>7.1</v>
       </c>
       <c r="Q54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R54">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S54">
+        <v>1.17</v>
+      </c>
+      <c r="T54">
+        <v>4.5</v>
+      </c>
+      <c r="U54">
+        <v>1.92</v>
+      </c>
+      <c r="V54">
+        <v>1.85</v>
+      </c>
+      <c r="W54">
         <v>1.2</v>
       </c>
-      <c r="T54">
-        <v>3.9</v>
-      </c>
-      <c r="U54">
-        <v>2.07</v>
-      </c>
-      <c r="V54">
-        <v>1.67</v>
-      </c>
-      <c r="W54">
-        <v>1.18</v>
-      </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>5.45</v>
+        <v>6.8</v>
       </c>
       <c r="AA54">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB54">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC54">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AD54">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF54">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,40 +9437,40 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="O56">
         <v>3.75</v>
       </c>
       <c r="P56">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q56">
-        <v>4.43</v>
+        <v>3.58</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
         <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
         <v>5.25</v>
@@ -9479,7 +9479,7 @@
         <v>1.53</v>
       </c>
       <c r="AB56">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC56">
         <v>2.35</v>
@@ -9488,7 +9488,7 @@
         <v>1.59</v>
       </c>
       <c r="AE56">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
         <v>1.46</v>
@@ -9600,65 +9600,65 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="O57">
         <v>3.3</v>
       </c>
       <c r="P57">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q57">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R57">
         <v>2.2</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T57">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z57">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA57">
+        <v>1.83</v>
+      </c>
+      <c r="AB57">
+        <v>1.85</v>
+      </c>
+      <c r="AC57">
+        <v>3.1</v>
+      </c>
+      <c r="AD57">
+        <v>1.33</v>
+      </c>
+      <c r="AE57">
+        <v>1.09</v>
+      </c>
+      <c r="AF57">
+        <v>1.72</v>
+      </c>
+      <c r="AG57">
         <v>1.95</v>
       </c>
-      <c r="AB57">
-        <v>1.75</v>
-      </c>
-      <c r="AC57">
-        <v>3.5</v>
-      </c>
-      <c r="AD57">
-        <v>1.25</v>
-      </c>
-      <c r="AE57">
-        <v>1.07</v>
-      </c>
-      <c r="AF57">
-        <v>1.75</v>
-      </c>
-      <c r="AG57">
-        <v>1.92</v>
-      </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9805,10 +9805,10 @@
         <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC58">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="AD58">
         <v>1.24</v>
@@ -10092,10 +10092,10 @@
         <v>2.5</v>
       </c>
       <c r="O60">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P60">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="Q60">
         <v>2.84</v>
@@ -10104,10 +10104,10 @@
         <v>2.01</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T60">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U60">
         <v>2.8</v>
@@ -10125,19 +10125,19 @@
         <v>1.29</v>
       </c>
       <c r="Z60">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AA60">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB60">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC60">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD60">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE60">
         <v>1.1</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="P61">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="R61">
         <v>2</v>
@@ -10306,10 +10306,10 @@
         <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>3.55</v>
@@ -10424,13 +10424,13 @@
         <v>1.95</v>
       </c>
       <c r="Q62">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S62">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
         <v>3.25</v>
@@ -10451,10 +10451,10 @@
         <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA62">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB62">
         <v>2.17</v>
@@ -10463,16 +10463,16 @@
         <v>2.46</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF62">
         <v>1.5</v>
       </c>
       <c r="AG62">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S63">
         <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U63">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V63">
         <v>1.62</v>
@@ -10611,13 +10611,13 @@
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
         <v>4.75</v>
       </c>
       <c r="AA63">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB63">
         <v>2.4</v>
@@ -10632,7 +10632,7 @@
         <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
         <v>2.45</v>
@@ -10741,58 +10741,58 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="O64">
+        <v>3.5</v>
+      </c>
+      <c r="P64">
+        <v>3.05</v>
+      </c>
+      <c r="Q64">
+        <v>2.65</v>
+      </c>
+      <c r="R64">
+        <v>2.22</v>
+      </c>
+      <c r="S64">
+        <v>1.3</v>
+      </c>
+      <c r="T64">
         <v>3.6</v>
       </c>
-      <c r="P64">
-        <v>3</v>
-      </c>
-      <c r="Q64">
-        <v>2.71</v>
-      </c>
-      <c r="R64">
-        <v>2.21</v>
-      </c>
-      <c r="S64">
-        <v>1.29</v>
-      </c>
-      <c r="T64">
-        <v>3.22</v>
-      </c>
       <c r="U64">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V64">
         <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB64">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC64">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD64">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF64">
         <v>1.53</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.65</v>
+        <v>3.98</v>
       </c>
       <c r="O65">
         <v>3.7</v>
       </c>
       <c r="P65">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -10922,7 +10922,7 @@
         <v>1.28</v>
       </c>
       <c r="T65">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
         <v>2.3</v>
@@ -10940,28 +10940,28 @@
         <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB65">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC65">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD65">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R66">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
         <v>1.39</v>
@@ -11097,13 +11097,13 @@
         <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
         <v>1.92</v>
@@ -11118,7 +11118,7 @@
         <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
         <v>1.65</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>7.35</v>
+        <v>6</v>
       </c>
       <c r="O69">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11882,22 +11882,22 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O71">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P71">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q71">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R71">
         <v>2.7</v>
       </c>
       <c r="S71">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
         <v>3.88</v>
@@ -11918,7 +11918,7 @@
         <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA71">
         <v>1.4</v>
@@ -11927,16 +11927,16 @@
         <v>2.72</v>
       </c>
       <c r="AC71">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD71">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE71">
         <v>1.3</v>
       </c>
       <c r="AF71">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG71">
         <v>2.35</v>
@@ -12054,10 +12054,10 @@
         <v>1.8</v>
       </c>
       <c r="Q72">
-        <v>4.6</v>
+        <v>5.26</v>
       </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S72">
         <v>1.35</v>
@@ -12066,7 +12066,7 @@
         <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V72">
         <v>1.4</v>
@@ -12075,31 +12075,31 @@
         <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z72">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA72">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB72">
         <v>1.78</v>
       </c>
       <c r="AC72">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD72">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE72">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG72">
         <v>1.95</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AK72">
         <v>1.2</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O73">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P73">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q73">
         <v>2.43</v>
@@ -12226,13 +12226,13 @@
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U73">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V73">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W73">
         <v>1.17</v>
@@ -12241,22 +12241,22 @@
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z73">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA73">
         <v>1.41</v>
       </c>
       <c r="AB73">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AC73">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD73">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE73">
         <v>1.24</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O76">
         <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="Q76">
         <v>2.48</v>
@@ -12727,22 +12727,22 @@
         <v>1.02</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z76">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA76">
         <v>2.36</v>
       </c>
       <c r="AB76">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC76">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD76">
         <v>1.2</v>
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O81">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
         <v>2.15</v>
@@ -13530,40 +13530,40 @@
         <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="U81">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V81">
         <v>1.46</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA81">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB81">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC81">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD81">
         <v>1.4</v>
       </c>
       <c r="AE81">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
         <v>1.62</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AK81">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="O82">
         <v>3.5</v>
       </c>
       <c r="P82">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q82">
         <v>3.3</v>
@@ -13696,10 +13696,10 @@
         <v>3.1</v>
       </c>
       <c r="U82">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V82">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13726,10 +13726,10 @@
         <v>1.4</v>
       </c>
       <c r="AE82">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG82">
         <v>2.38</v>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q83">
         <v>3.62</v>
@@ -13856,7 +13856,7 @@
         <v>1.35</v>
       </c>
       <c r="T83">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U83">
         <v>2.88</v>
@@ -13865,7 +13865,7 @@
         <v>1.36</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.06</v>
@@ -13877,7 +13877,7 @@
         <v>3.18</v>
       </c>
       <c r="AA83">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB83">
         <v>1.8</v>
@@ -13892,10 +13892,10 @@
         <v>1.09</v>
       </c>
       <c r="AF83">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG83">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>6.4</v>
+        <v>6.26</v>
       </c>
       <c r="O84">
         <v>4.5</v>
       </c>
       <c r="P84">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -14019,7 +14019,7 @@
         <v>1.26</v>
       </c>
       <c r="T84">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U84">
         <v>2.25</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O85">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P85">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -14200,7 +14200,7 @@
         <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA85">
         <v>1.47</v>
@@ -14218,10 +14218,10 @@
         <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O86">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q86">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="R86">
         <v>2.3</v>
@@ -14345,19 +14345,19 @@
         <v>1.27</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U86">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V86">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W86">
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.15</v>
@@ -14366,19 +14366,19 @@
         <v>4.8</v>
       </c>
       <c r="AA86">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB86">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AC86">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AD86">
         <v>1.55</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
         <v>1.46</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK86">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14496,7 +14496,7 @@
         <v>3.85</v>
       </c>
       <c r="P87">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Q87">
         <v>3.36</v>
@@ -14505,10 +14505,10 @@
         <v>2.67</v>
       </c>
       <c r="S87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U87">
         <v>1.95</v>
@@ -14535,7 +14535,7 @@
         <v>2.8</v>
       </c>
       <c r="AC87">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AD87">
         <v>1.84</v>
@@ -14544,10 +14544,10 @@
         <v>1.33</v>
       </c>
       <c r="AF87">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AG87">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14656,25 +14656,25 @@
         <v>1.95</v>
       </c>
       <c r="O88">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="Q88">
         <v>2.4</v>
       </c>
       <c r="R88">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="S88">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T88">
         <v>4.2</v>
       </c>
       <c r="U88">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V88">
         <v>1.75</v>
@@ -14695,22 +14695,22 @@
         <v>1.33</v>
       </c>
       <c r="AB88">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AC88">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AD88">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE88">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF88">
         <v>1.3</v>
       </c>
       <c r="AG88">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.33</v>
       </c>
       <c r="AK88">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14819,19 +14819,19 @@
         <v>1.88</v>
       </c>
       <c r="O89">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q89">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R89">
         <v>2.9</v>
       </c>
       <c r="S89">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T89">
         <v>4.9</v>
@@ -14840,10 +14840,10 @@
         <v>1.62</v>
       </c>
       <c r="V89">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="W89">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -14855,10 +14855,10 @@
         <v>8.5</v>
       </c>
       <c r="AA89">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB89">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AC89">
         <v>1.5</v>
@@ -14867,13 +14867,13 @@
         <v>2.55</v>
       </c>
       <c r="AE89">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF89">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG89">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK89">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,37 +14979,37 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O90">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="P90">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="Q90">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R90">
         <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T90">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U90">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V90">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
+        <v>1.07</v>
+      </c>
+      <c r="X90">
         <v>1.06</v>
-      </c>
-      <c r="X90">
-        <v>1.08</v>
       </c>
       <c r="Y90">
         <v>1.29</v>
@@ -15021,22 +15021,22 @@
         <v>1.91</v>
       </c>
       <c r="AB90">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC90">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD90">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
         <v>1.4</v>
@@ -15145,16 +15145,16 @@
         <v>2.6</v>
       </c>
       <c r="O91">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P91">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q91">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S91">
         <v>1.5</v>
@@ -15169,7 +15169,7 @@
         <v>1.26</v>
       </c>
       <c r="W91">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
         <v>1.07</v>
@@ -15181,10 +15181,10 @@
         <v>2.46</v>
       </c>
       <c r="AA91">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AB91">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AC91">
         <v>4.5</v>
@@ -15199,7 +15199,7 @@
         <v>2.02</v>
       </c>
       <c r="AG91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15305,34 +15305,34 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="Q92">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R92">
         <v>2.07</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X92">
         <v>1</v>
@@ -15468,31 +15468,31 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P93">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q93">
         <v>3.45</v>
       </c>
       <c r="R93">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S93">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T93">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U93">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V93">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W93">
         <v>1.07</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK93">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15646,34 +15646,34 @@
         <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T94">
         <v>3.55</v>
       </c>
       <c r="U94">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V94">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W94">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X94">
         <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
         <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB94">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC94">
         <v>2.63</v>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
         <v>1.62</v>
@@ -15806,13 +15806,13 @@
         <v>2.5</v>
       </c>
       <c r="R95">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S95">
         <v>1.22</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U95">
         <v>2.08</v>
@@ -15830,19 +15830,19 @@
         <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AA95">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC95">
         <v>2.1</v>
       </c>
       <c r="AD95">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE95">
         <v>1.29</v>
@@ -15963,13 +15963,13 @@
         <v>3.3</v>
       </c>
       <c r="P96">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="Q96">
         <v>4.64</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
         <v>1.36</v>
@@ -15978,7 +15978,7 @@
         <v>2.8</v>
       </c>
       <c r="U96">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
         <v>1.36</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,65 +16120,65 @@
         </is>
       </c>
       <c r="N97">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q97">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R97">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S97">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="U97">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="V97">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z97">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AA97">
+        <v>2.07</v>
+      </c>
+      <c r="AB97">
+        <v>1.73</v>
+      </c>
+      <c r="AC97">
+        <v>2.9</v>
+      </c>
+      <c r="AD97">
+        <v>1.21</v>
+      </c>
+      <c r="AE97">
+        <v>1.04</v>
+      </c>
+      <c r="AF97">
+        <v>1.78</v>
+      </c>
+      <c r="AG97">
         <v>1.89</v>
       </c>
-      <c r="AB97">
-        <v>1.85</v>
-      </c>
-      <c r="AC97">
-        <v>3.2</v>
-      </c>
-      <c r="AD97">
-        <v>1.26</v>
-      </c>
-      <c r="AE97">
-        <v>1.05</v>
-      </c>
-      <c r="AF97">
-        <v>1.71</v>
-      </c>
-      <c r="AG97">
-        <v>1.98</v>
-      </c>
       <c r="AH97" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK97">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O98">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P98">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q98">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="R98">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T98">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U98">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="V98">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.3</v>
       </c>
       <c r="Z98">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AA98">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB98">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC98">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD98">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE98">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG98">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK98">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>2.1</v>
       </c>
       <c r="R99">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S99">
         <v>1.34</v>
@@ -16485,19 +16485,19 @@
         <v>3.5</v>
       </c>
       <c r="AA99">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB99">
         <v>1.96</v>
       </c>
       <c r="AC99">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD99">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
         <v>1.8</v>
@@ -16519,7 +16519,7 @@
         <v>1.19</v>
       </c>
       <c r="AK99">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="O100">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="P100">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="Q100">
         <v>2</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
         <v>1.33</v>
@@ -16642,25 +16642,25 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z100">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA100">
         <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC100">
         <v>3.25</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE100">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF100">
         <v>2</v>
@@ -16772,55 +16772,55 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O101">
         <v>3.2</v>
       </c>
       <c r="P101">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q101">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="R101">
         <v>2.06</v>
       </c>
       <c r="S101">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T101">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U101">
         <v>2.75</v>
       </c>
       <c r="V101">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
         <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AA101">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB101">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC101">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD101">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE101">
         <v>1.06</v>
@@ -16845,7 +16845,7 @@
         <v>1.27</v>
       </c>
       <c r="AK101">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,10 +16935,10 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P102">
         <v>2.8</v>
@@ -16968,22 +16968,22 @@
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z102">
         <v>4.4</v>
       </c>
       <c r="AA102">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB102">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC102">
         <v>2.53</v>
       </c>
       <c r="AD102">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
         <v>1.17</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17261,16 +17261,16 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O104">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P104">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q104">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="R104">
         <v>2.04</v>
@@ -17297,19 +17297,19 @@
         <v>1.4</v>
       </c>
       <c r="Z104">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AA104">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB104">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC104">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD104">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE104">
         <v>1.06</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK104">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="O105">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="P105">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Q105">
         <v>7.4</v>
@@ -17442,7 +17442,7 @@
         <v>1.18</v>
       </c>
       <c r="T105">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U105">
         <v>1.91</v>
@@ -17466,7 +17466,7 @@
         <v>1.36</v>
       </c>
       <c r="AB105">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AC105">
         <v>1.91</v>
@@ -17478,7 +17478,7 @@
         <v>1.33</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
         <v>2.15</v>
@@ -17596,22 +17596,22 @@
         <v>6.5</v>
       </c>
       <c r="Q106">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R106">
         <v>2.7</v>
       </c>
       <c r="S106">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U106">
         <v>2.1</v>
       </c>
       <c r="V106">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W106">
         <v>1.17</v>
@@ -17620,10 +17620,10 @@
         <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA106">
         <v>1.44</v>
@@ -17635,16 +17635,16 @@
         <v>2.1</v>
       </c>
       <c r="AD106">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE106">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF106">
         <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17753,25 +17753,25 @@
         <v>1.73</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q107">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R107">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="S107">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="U107">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V107">
         <v>1.36</v>
@@ -17789,41 +17789,41 @@
         <v>3.14</v>
       </c>
       <c r="AA107">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AB107">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC107">
         <v>3.34</v>
       </c>
       <c r="AD107">
+        <v>1.29</v>
+      </c>
+      <c r="AE107">
+        <v>1.04</v>
+      </c>
+      <c r="AF107">
+        <v>1.83</v>
+      </c>
+      <c r="AG107">
+        <v>1.87</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.25</v>
       </c>
-      <c r="AE107">
-        <v>1.05</v>
-      </c>
-      <c r="AF107">
-        <v>1.85</v>
-      </c>
-      <c r="AG107">
-        <v>1.83</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.23</v>
-      </c>
       <c r="AK107">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
         <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S108">
         <v>1.35</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,31 +18079,31 @@
         <v>3.7</v>
       </c>
       <c r="O109">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q109">
-        <v>4.54</v>
+        <v>4.7</v>
       </c>
       <c r="R109">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="S109">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U109">
         <v>2.44</v>
       </c>
       <c r="V109">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
         <v>1.03</v>
@@ -18124,7 +18124,7 @@
         <v>2.39</v>
       </c>
       <c r="AD109">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
         <v>1.2</v>
@@ -18149,7 +18149,7 @@
         <v>2.16</v>
       </c>
       <c r="AK109">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,34 +18239,34 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O110">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="P110">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q110">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R110">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U110">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="V110">
         <v>1.43</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>1.02</v>
@@ -18275,10 +18275,10 @@
         <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA110">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB110">
         <v>1.9</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK110">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="O111">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P111">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q111">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="R111">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T111">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V111">
+        <v>1.5</v>
+      </c>
+      <c r="W111">
+        <v>1.11</v>
+      </c>
+      <c r="X111">
+        <v>1.04</v>
+      </c>
+      <c r="Y111">
+        <v>1.17</v>
+      </c>
+      <c r="Z111">
+        <v>3.98</v>
+      </c>
+      <c r="AA111">
+        <v>1.67</v>
+      </c>
+      <c r="AB111">
+        <v>2.2</v>
+      </c>
+      <c r="AC111">
+        <v>2.64</v>
+      </c>
+      <c r="AD111">
         <v>1.44</v>
       </c>
-      <c r="W111">
+      <c r="AE111">
+        <v>1.12</v>
+      </c>
+      <c r="AF111">
+        <v>1.68</v>
+      </c>
+      <c r="AG111">
+        <v>2.01</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.18</v>
+      </c>
+      <c r="AK111">
         <v>1.1</v>
-      </c>
-      <c r="X111">
-        <v>1</v>
-      </c>
-      <c r="Y111">
-        <v>1.19</v>
-      </c>
-      <c r="Z111">
-        <v>3.78</v>
-      </c>
-      <c r="AA111">
-        <v>1.75</v>
-      </c>
-      <c r="AB111">
-        <v>2</v>
-      </c>
-      <c r="AC111">
-        <v>2.82</v>
-      </c>
-      <c r="AD111">
-        <v>1.39</v>
-      </c>
-      <c r="AE111">
-        <v>1.11</v>
-      </c>
-      <c r="AF111">
-        <v>1.67</v>
-      </c>
-      <c r="AG111">
-        <v>2</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.94</v>
-      </c>
-      <c r="AK111">
-        <v>1.22</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>8.550000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O112">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="P112">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Q112">
-        <v>6.55</v>
+        <v>8</v>
       </c>
       <c r="R112">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="S112">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T112">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="U112">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="V112">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W112">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA112">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB112">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC112">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD112">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF112">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AG112">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AK112">
         <v>1.04</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P113">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q113">
         <v>2.73</v>
@@ -18782,7 +18782,7 @@
         <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG113">
         <v>1.85</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19054,22 +19054,22 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P115">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q115">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R115">
         <v>2.2</v>
       </c>
       <c r="S115">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
         <v>3.1</v>
@@ -19081,16 +19081,16 @@
         <v>1.48</v>
       </c>
       <c r="W115">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
         <v>1</v>
       </c>
       <c r="Y115">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z115">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA115">
         <v>1.8</v>
@@ -19099,16 +19099,16 @@
         <v>1.95</v>
       </c>
       <c r="AC115">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE115">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF115">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AG115">
         <v>2.05</v>
@@ -19226,10 +19226,10 @@
         <v>2.7</v>
       </c>
       <c r="Q116">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="R116">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S116">
         <v>1.53</v>
@@ -19244,7 +19244,7 @@
         <v>1.23</v>
       </c>
       <c r="W116">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.08</v>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O117">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P117">
         <v>2.5</v>
@@ -19398,10 +19398,10 @@
         <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="U117">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="V117">
         <v>1.37</v>
@@ -19413,7 +19413,7 @@
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z117">
         <v>3.05</v>
@@ -19422,13 +19422,13 @@
         <v>2</v>
       </c>
       <c r="AB117">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC117">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD117">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
         <v>1.05</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AK117">
         <v>1.4</v>
@@ -19549,22 +19549,22 @@
         <v>3.3</v>
       </c>
       <c r="P118">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q118">
         <v>3.83</v>
       </c>
       <c r="R118">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S118">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U118">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="V118">
         <v>1.35</v>
@@ -19576,31 +19576,31 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z118">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AA118">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AB118">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC118">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AD118">
         <v>1.22</v>
       </c>
       <c r="AE118">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF118">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG118">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19869,31 +19869,31 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O120">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P120">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q120">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R120">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T120">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="U120">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V120">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W120">
         <v>1.1</v>
@@ -19905,28 +19905,28 @@
         <v>1.22</v>
       </c>
       <c r="Z120">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="AA120">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB120">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC120">
         <v>2.83</v>
       </c>
       <c r="AD120">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG120">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20050,46 +20050,46 @@
         <v>1.52</v>
       </c>
       <c r="T121">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U121">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V121">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W121">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
         <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z121">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AA121">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AB121">
         <v>1.53</v>
       </c>
       <c r="AC121">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD121">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE121">
         <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AG121">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK121">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O123">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P123">
         <v>2.15</v>
@@ -20373,10 +20373,10 @@
         <v>2.05</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T123">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="U123">
         <v>3.1</v>
@@ -20385,7 +20385,7 @@
         <v>1.31</v>
       </c>
       <c r="W123">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X123">
         <v>1.03</v>
@@ -20394,19 +20394,19 @@
         <v>1.34</v>
       </c>
       <c r="Z123">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AA123">
         <v>2.15</v>
       </c>
       <c r="AB123">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC123">
-        <v>3.74</v>
+        <v>4.04</v>
       </c>
       <c r="AD123">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE123">
         <v>1.06</v>
@@ -20521,25 +20521,25 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O124">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P124">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Q124">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R124">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S124">
         <v>1.39</v>
       </c>
       <c r="T124">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U124">
         <v>2.63</v>
@@ -20554,13 +20554,13 @@
         <v>1.06</v>
       </c>
       <c r="Y124">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z124">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA124">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AB124">
         <v>1.62</v>
@@ -20575,10 +20575,10 @@
         <v>1.03</v>
       </c>
       <c r="AF124">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
         <v>1.6</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="O125">
-        <v>4.55</v>
+        <v>5.1</v>
       </c>
       <c r="P125">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O126">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P126">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="Q126">
         <v>3.12</v>
@@ -20865,7 +20865,7 @@
         <v>1.42</v>
       </c>
       <c r="T126">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U126">
         <v>3.1</v>
@@ -20889,22 +20889,22 @@
         <v>2.25</v>
       </c>
       <c r="AB126">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC126">
         <v>4.4</v>
       </c>
       <c r="AD126">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
         <v>1.07</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG126">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21013,10 +21013,10 @@
         <v>1.61</v>
       </c>
       <c r="O127">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P127">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="Q127">
         <v>2.21</v>
@@ -21040,7 +21040,7 @@
         <v>1.07</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y127">
         <v>1.33</v>
@@ -21052,13 +21052,13 @@
         <v>2.03</v>
       </c>
       <c r="AB127">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC127">
         <v>3.8</v>
       </c>
       <c r="AD127">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE127">
         <v>1.08</v>
@@ -21339,25 +21339,25 @@
         <v>2.1</v>
       </c>
       <c r="O129">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P129">
         <v>3.26</v>
       </c>
       <c r="Q129">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="R129">
         <v>2</v>
       </c>
       <c r="S129">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T129">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U129">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V129">
         <v>1.33</v>
@@ -21369,7 +21369,7 @@
         <v>1.06</v>
       </c>
       <c r="Y129">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z129">
         <v>3.26</v>
@@ -21393,7 +21393,7 @@
         <v>1.91</v>
       </c>
       <c r="AG129">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O130">
         <v>3.5</v>
       </c>
       <c r="P130">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
       </c>
       <c r="R130">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S130">
         <v>1.33</v>
@@ -21553,7 +21553,7 @@
         <v>1.13</v>
       </c>
       <c r="AF130">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG130">
         <v>1.95</v>
@@ -21572,7 +21572,7 @@
         <v>1.24</v>
       </c>
       <c r="AK130">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O131">
+        <v>3.25</v>
+      </c>
+      <c r="P131">
         <v>3.3</v>
-      </c>
-      <c r="P131">
-        <v>3.64</v>
       </c>
       <c r="Q131">
         <v>2.56</v>
@@ -21698,19 +21698,19 @@
         <v>1.37</v>
       </c>
       <c r="Z131">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="AA131">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB131">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC131">
         <v>3.9</v>
       </c>
       <c r="AD131">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE131">
         <v>1.07</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="P133">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22169,7 +22169,7 @@
         <v>1.3</v>
       </c>
       <c r="T134">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U134">
         <v>2.36</v>
@@ -22178,7 +22178,7 @@
         <v>1.51</v>
       </c>
       <c r="W134">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
         <v>1.03</v>
@@ -22317,40 +22317,40 @@
         <v>2.1</v>
       </c>
       <c r="O135">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="Q135">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R135">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S135">
         <v>1.18</v>
       </c>
       <c r="T135">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="U135">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V135">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W135">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X135">
         <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z135">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA135">
         <v>1.42</v>
@@ -22359,10 +22359,10 @@
         <v>2.49</v>
       </c>
       <c r="AC135">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AD135">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AE135">
         <v>1.28</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O136">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P136">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Q136">
         <v>5.5</v>
@@ -22504,22 +22504,22 @@
         <v>1.5</v>
       </c>
       <c r="W136">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
         <v>1.18</v>
       </c>
       <c r="Z136">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA136">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB136">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC136">
         <v>2.5</v>
@@ -22528,13 +22528,13 @@
         <v>1.44</v>
       </c>
       <c r="AE136">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF136">
         <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O138">
         <v>3.8</v>
@@ -22818,13 +22818,13 @@
         <v>2.23</v>
       </c>
       <c r="S138">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T138">
         <v>3.05</v>
       </c>
       <c r="U138">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V138">
         <v>1.44</v>
@@ -22857,7 +22857,7 @@
         <v>1.12</v>
       </c>
       <c r="AF138">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG138">
         <v>2.05</v>
@@ -22966,61 +22966,61 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O139">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="P139">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="Q139">
         <v>1.82</v>
       </c>
       <c r="R139">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="S139">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T139">
         <v>6</v>
       </c>
       <c r="U139">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V139">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="W139">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X139">
         <v>1</v>
       </c>
       <c r="Y139">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA139">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AB139">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="AC139">
         <v>1.36</v>
       </c>
       <c r="AD139">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="AE139">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF139">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AG139">
         <v>3.7</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O140">
         <v>3.7</v>
       </c>
       <c r="P140">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q140">
         <v>2.62</v>
@@ -23147,7 +23147,7 @@
         <v>1.2</v>
       </c>
       <c r="T140">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U140">
         <v>2.12</v>
@@ -23168,7 +23168,7 @@
         <v>5.45</v>
       </c>
       <c r="AA140">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB140">
         <v>2.59</v>
@@ -23186,7 +23186,7 @@
         <v>1.4</v>
       </c>
       <c r="AG140">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="O141">
         <v>4.5</v>
       </c>
       <c r="P141">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q141">
         <v>4.4</v>
@@ -23307,10 +23307,10 @@
         <v>2.62</v>
       </c>
       <c r="S141">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T141">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U141">
         <v>2.05</v>
@@ -23328,7 +23328,7 @@
         <v>1.08</v>
       </c>
       <c r="Z141">
-        <v>5.55</v>
+        <v>6.3</v>
       </c>
       <c r="AA141">
         <v>1.4</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="O142">
         <v>2.8</v>
       </c>
       <c r="P142">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q142">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="R142">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S142">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="T142">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="U142">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="V142">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W142">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X142">
         <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Z142">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AA142">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AB142">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC142">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AD142">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE142">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF142">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG142">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK142">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>3.25</v>
+        <v>1.84</v>
       </c>
       <c r="O143">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P143">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="Q143">
-        <v>4.3</v>
+        <v>2.53</v>
       </c>
       <c r="R143">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S143">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T143">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="U143">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V143">
         <v>1.22</v>
       </c>
       <c r="W143">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X143">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y143">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z143">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AA143">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AB143">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC143">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AD143">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE143">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF143">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG143">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK143">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
+        <v>3.07</v>
+      </c>
+      <c r="O144">
+        <v>2.95</v>
+      </c>
+      <c r="P144">
+        <v>2.16</v>
+      </c>
+      <c r="Q144">
+        <v>4.55</v>
+      </c>
+      <c r="R144">
         <v>1.82</v>
       </c>
-      <c r="O144">
-        <v>2.9</v>
-      </c>
-      <c r="P144">
-        <v>3.96</v>
-      </c>
-      <c r="Q144">
-        <v>2.5</v>
-      </c>
-      <c r="R144">
-        <v>1.83</v>
-      </c>
       <c r="S144">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T144">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U144">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V144">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W144">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X144">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y144">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z144">
+        <v>2.52</v>
+      </c>
+      <c r="AA144">
         <v>2.46</v>
       </c>
-      <c r="AA144">
-        <v>2.49</v>
-      </c>
       <c r="AB144">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AC144">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AD144">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE144">
         <v>1.01</v>
       </c>
       <c r="AF144">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AG144">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.36</v>
       </c>
       <c r="AK144">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,16 +23944,16 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O145">
         <v>3.75</v>
       </c>
       <c r="P145">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q145">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R145">
         <v>2.4</v>
@@ -23980,19 +23980,19 @@
         <v>1.13</v>
       </c>
       <c r="Z145">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="AA145">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB145">
         <v>2.23</v>
       </c>
       <c r="AC145">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD145">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE145">
         <v>1.2</v>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N146">
-        <v>4.49</v>
+        <v>4.03</v>
       </c>
       <c r="O146">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P146">
         <v>1.79</v>
@@ -24155,7 +24155,7 @@
         <v>2.55</v>
       </c>
       <c r="AD146">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE146">
         <v>1.18</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O147">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q147">
         <v>2.47</v>
@@ -24285,16 +24285,16 @@
         <v>2.13</v>
       </c>
       <c r="S147">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T147">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U147">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V147">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W147">
         <v>1.08</v>
@@ -24303,31 +24303,31 @@
         <v>1.04</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z147">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB147">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC147">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD147">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE147">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF147">
         <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>1.28</v>
       </c>
       <c r="AK147">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,19 +24433,19 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O148">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P148">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q148">
         <v>2.18</v>
       </c>
       <c r="R148">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S148">
         <v>1.44</v>
@@ -24481,7 +24481,7 @@
         <v>3.74</v>
       </c>
       <c r="AD148">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE148">
         <v>1.03</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O149">
         <v>3.4</v>
@@ -24608,22 +24608,22 @@
         <v>2.7</v>
       </c>
       <c r="R149">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S149">
         <v>1.36</v>
       </c>
       <c r="T149">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U149">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V149">
         <v>1.45</v>
       </c>
       <c r="W149">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X149">
         <v>1.01</v>
@@ -24632,7 +24632,7 @@
         <v>1.22</v>
       </c>
       <c r="Z149">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA149">
         <v>1.76</v>
@@ -24644,7 +24644,7 @@
         <v>2.85</v>
       </c>
       <c r="AD149">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE149">
         <v>1.15</v>
@@ -24762,10 +24762,10 @@
         <v>1.35</v>
       </c>
       <c r="O150">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="P150">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q150">
         <v>1.73</v>
@@ -24801,13 +24801,13 @@
         <v>1.5</v>
       </c>
       <c r="AB150">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AC150">
         <v>2.34</v>
       </c>
       <c r="AD150">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE150">
         <v>1.22</v>
@@ -24816,7 +24816,7 @@
         <v>1.77</v>
       </c>
       <c r="AG150">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24931,16 +24931,16 @@
         <v>2.05</v>
       </c>
       <c r="Q151">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R151">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S151">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T151">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="U151">
         <v>2.62</v>
@@ -24949,37 +24949,37 @@
         <v>1.42</v>
       </c>
       <c r="W151">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y151">
         <v>1.25</v>
       </c>
       <c r="Z151">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA151">
         <v>1.8</v>
       </c>
       <c r="AB151">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC151">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD151">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE151">
         <v>1.08</v>
       </c>
       <c r="AF151">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG151">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK151">
         <v>1.3</v>
@@ -25085,19 +25085,19 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O152">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P152">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q152">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R152">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S152">
         <v>1.38</v>
@@ -25106,31 +25106,31 @@
         <v>2.75</v>
       </c>
       <c r="U152">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="V152">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W152">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X152">
         <v>1.06</v>
       </c>
       <c r="Y152">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z152">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="AA152">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB152">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC152">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AD152">
         <v>1.24</v>
@@ -25139,7 +25139,7 @@
         <v>1.08</v>
       </c>
       <c r="AF152">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG152">
         <v>1.93</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O153">
         <v>3.2</v>
       </c>
       <c r="P153">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q153">
         <v>3.1</v>
@@ -25263,19 +25263,19 @@
         <v>2.15</v>
       </c>
       <c r="S153">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T153">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U153">
         <v>2.8</v>
       </c>
       <c r="V153">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W153">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X153">
         <v>1.03</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="O154">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P154">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -25429,7 +25429,7 @@
         <v>1.44</v>
       </c>
       <c r="T154">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U154">
         <v>3</v>
@@ -25441,34 +25441,34 @@
         <v>1.08</v>
       </c>
       <c r="X154">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
         <v>1.33</v>
       </c>
       <c r="Z154">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AA154">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB154">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC154">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD154">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE154">
         <v>1.04</v>
       </c>
       <c r="AF154">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG154">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25574,16 +25574,16 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O155">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P155">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q155">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R155">
         <v>2</v>
@@ -25595,7 +25595,7 @@
         <v>2.4</v>
       </c>
       <c r="U155">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="V155">
         <v>1.18</v>
@@ -25604,34 +25604,34 @@
         <v>1.02</v>
       </c>
       <c r="X155">
+        <v>1.1</v>
+      </c>
+      <c r="Y155">
+        <v>1.44</v>
+      </c>
+      <c r="Z155">
+        <v>2.5</v>
+      </c>
+      <c r="AA155">
+        <v>2.62</v>
+      </c>
+      <c r="AB155">
+        <v>1.44</v>
+      </c>
+      <c r="AC155">
+        <v>4.7</v>
+      </c>
+      <c r="AD155">
+        <v>1.15</v>
+      </c>
+      <c r="AE155">
         <v>1.05</v>
       </c>
-      <c r="Y155">
-        <v>1.47</v>
-      </c>
-      <c r="Z155">
-        <v>2.49</v>
-      </c>
-      <c r="AA155">
-        <v>2.45</v>
-      </c>
-      <c r="AB155">
-        <v>1.5</v>
-      </c>
-      <c r="AC155">
-        <v>3.5</v>
-      </c>
-      <c r="AD155">
-        <v>1.09</v>
-      </c>
-      <c r="AE155">
-        <v>1.01</v>
-      </c>
       <c r="AF155">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG155">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK155">
         <v>1.14</v>
@@ -26063,25 +26063,25 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O158">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P158">
         <v>3.87</v>
       </c>
       <c r="Q158">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="R158">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S158">
         <v>1.49</v>
       </c>
       <c r="T158">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U158">
         <v>3.15</v>
@@ -26093,16 +26093,16 @@
         <v>1.05</v>
       </c>
       <c r="X158">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y158">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z158">
         <v>2.65</v>
       </c>
       <c r="AA158">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AB158">
         <v>1.54</v>
@@ -26235,40 +26235,40 @@
         <v>3.45</v>
       </c>
       <c r="Q159">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R159">
         <v>1.93</v>
       </c>
       <c r="S159">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T159">
         <v>2.38</v>
       </c>
       <c r="U159">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V159">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W159">
         <v>1.04</v>
       </c>
       <c r="X159">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y159">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z159">
         <v>2.41</v>
       </c>
       <c r="AA159">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB159">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC159">
         <v>5.25</v>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK159">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O161">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="P161">
-        <v>8.15</v>
+        <v>7.95</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -26570,13 +26570,13 @@
         <v>1.17</v>
       </c>
       <c r="T161">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U161">
         <v>1.95</v>
       </c>
       <c r="V161">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W161">
         <v>1.2</v>
@@ -26588,7 +26588,7 @@
         <v>1.07</v>
       </c>
       <c r="Z161">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA161">
         <v>1.32</v>
@@ -26609,7 +26609,7 @@
         <v>1.75</v>
       </c>
       <c r="AG161">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,80 +26715,80 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="O162">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="P162">
-        <v>2.53</v>
+        <v>4.48</v>
       </c>
       <c r="Q162">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="R162">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S162">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="U162">
-        <v>3.2</v>
+        <v>2.33</v>
       </c>
       <c r="V162">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="W162">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y162">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z162">
-        <v>2.97</v>
+        <v>4.15</v>
       </c>
       <c r="AA162">
+        <v>1.61</v>
+      </c>
+      <c r="AB162">
+        <v>2.1</v>
+      </c>
+      <c r="AC162">
         <v>2.2</v>
       </c>
-      <c r="AB162">
-        <v>1.68</v>
-      </c>
-      <c r="AC162">
-        <v>3.74</v>
-      </c>
       <c r="AD162">
+        <v>1.33</v>
+      </c>
+      <c r="AE162">
+        <v>1.15</v>
+      </c>
+      <c r="AF162">
+        <v>1.5</v>
+      </c>
+      <c r="AG162">
+        <v>2.12</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
         <v>1.18</v>
       </c>
-      <c r="AE162">
-        <v>1.03</v>
-      </c>
-      <c r="AF162">
-        <v>1.85</v>
-      </c>
-      <c r="AG162">
-        <v>1.8</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>1.25</v>
-      </c>
       <c r="AK162">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.63</v>
+        <v>2.53</v>
       </c>
       <c r="O163">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="P163">
-        <v>4.15</v>
+        <v>2.53</v>
       </c>
       <c r="Q163">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="R163">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S163">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T163">
+        <v>2.13</v>
+      </c>
+      <c r="U163">
         <v>3.2</v>
       </c>
-      <c r="U163">
-        <v>2.33</v>
-      </c>
       <c r="V163">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="W163">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X163">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y163">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z163">
-        <v>4.33</v>
+        <v>2.92</v>
       </c>
       <c r="AA163">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB163">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC163">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD163">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF163">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG163">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27204,25 +27204,25 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O165">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P165">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q165">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R165">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S165">
         <v>1.44</v>
       </c>
       <c r="T165">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U165">
         <v>2.95</v>
@@ -27234,28 +27234,28 @@
         <v>1.04</v>
       </c>
       <c r="X165">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y165">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z165">
         <v>2.85</v>
       </c>
       <c r="AA165">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AB165">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC165">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD165">
         <v>1.16</v>
       </c>
       <c r="AE165">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF165">
         <v>1.95</v>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK165">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27412,7 +27412,7 @@
         <v>1.57</v>
       </c>
       <c r="AC166">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="AD166">
         <v>1.18</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>3.93</v>
+        <v>4.25</v>
       </c>
       <c r="O167">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q167">
         <v>4.2</v>
@@ -27551,7 +27551,7 @@
         <v>2.9</v>
       </c>
       <c r="U167">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V167">
         <v>1.4</v>
@@ -27560,16 +27560,16 @@
         <v>1.08</v>
       </c>
       <c r="X167">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA167">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB167">
         <v>1.88</v>
@@ -27578,13 +27578,13 @@
         <v>3.1</v>
       </c>
       <c r="AD167">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE167">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF167">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
         <v>1.95</v>
@@ -27603,7 +27603,7 @@
         <v>1.22</v>
       </c>
       <c r="AK167">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27699,7 +27699,7 @@
         <v>3.6</v>
       </c>
       <c r="P168">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q168">
         <v>2.15</v>
@@ -27729,22 +27729,22 @@
         <v>1.26</v>
       </c>
       <c r="Z168">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA168">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB168">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC168">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD168">
         <v>1.32</v>
       </c>
       <c r="AE168">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF168">
         <v>1.83</v>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="O170">
         <v>3.75</v>
@@ -28034,22 +28034,22 @@
         <v>2.32</v>
       </c>
       <c r="S170">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T170">
         <v>2.98</v>
       </c>
       <c r="U170">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V170">
         <v>1.38</v>
       </c>
       <c r="W170">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X170">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y170">
         <v>1.26</v>
@@ -28061,19 +28061,19 @@
         <v>2</v>
       </c>
       <c r="AB170">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC170">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD170">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE170">
         <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG170">
         <v>1.85</v>
@@ -28182,16 +28182,16 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O171">
         <v>3.5</v>
       </c>
       <c r="P171">
-        <v>4.5</v>
+        <v>4.81</v>
       </c>
       <c r="Q171">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="R171">
         <v>2.07</v>
@@ -28203,13 +28203,13 @@
         <v>2.62</v>
       </c>
       <c r="U171">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V171">
         <v>1.35</v>
       </c>
       <c r="W171">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X171">
         <v>1.02</v>
@@ -28218,10 +28218,10 @@
         <v>1.33</v>
       </c>
       <c r="Z171">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA171">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB171">
         <v>1.73</v>
@@ -28239,7 +28239,7 @@
         <v>1.92</v>
       </c>
       <c r="AG171">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28680,16 +28680,16 @@
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R174">
         <v>2.3</v>
       </c>
       <c r="S174">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T174">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U174">
         <v>2.29</v>
@@ -29163,40 +29163,40 @@
         <v>1.46</v>
       </c>
       <c r="O177">
+        <v>4.33</v>
+      </c>
+      <c r="P177">
         <v>4.5</v>
-      </c>
-      <c r="P177">
-        <v>4.8</v>
       </c>
       <c r="Q177">
         <v>1.91</v>
       </c>
       <c r="R177">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S177">
         <v>1.2</v>
       </c>
       <c r="T177">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U177">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V177">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W177">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z177">
-        <v>5.55</v>
+        <v>5.8</v>
       </c>
       <c r="AA177">
         <v>1.33</v>
@@ -29211,13 +29211,13 @@
         <v>1.85</v>
       </c>
       <c r="AE177">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF177">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AG177">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK177">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29323,10 +29323,10 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O178">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P178">
         <v>5.24</v>
@@ -29815,7 +29815,7 @@
         <v>1.91</v>
       </c>
       <c r="O181">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P181">
         <v>3.7</v>
@@ -29824,31 +29824,31 @@
         <v>2.7</v>
       </c>
       <c r="R181">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S181">
         <v>1.53</v>
       </c>
       <c r="T181">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U181">
         <v>3.2</v>
       </c>
       <c r="V181">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W181">
         <v>1.03</v>
       </c>
       <c r="X181">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y181">
         <v>1.44</v>
       </c>
       <c r="Z181">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA181">
         <v>2.42</v>
@@ -29857,19 +29857,19 @@
         <v>1.52</v>
       </c>
       <c r="AC181">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD181">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE181">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF181">
         <v>2.05</v>
       </c>
       <c r="AG181">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O182">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P182">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="Q182">
         <v>2.9</v>
@@ -29996,7 +29996,7 @@
         <v>2.9</v>
       </c>
       <c r="U182">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V182">
         <v>1.36</v>
@@ -30014,7 +30014,7 @@
         <v>3.23</v>
       </c>
       <c r="AA182">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB182">
         <v>1.85</v>
@@ -30023,13 +30023,13 @@
         <v>3.2</v>
       </c>
       <c r="AD182">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE182">
         <v>1.06</v>
       </c>
       <c r="AF182">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG182">
         <v>2</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
+        <v>1.39</v>
+      </c>
+      <c r="AK182">
         <v>1.4</v>
-      </c>
-      <c r="AK182">
-        <v>1.41</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30310,40 +30310,40 @@
         <v>2.8</v>
       </c>
       <c r="Q184">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R184">
         <v>2.1</v>
       </c>
       <c r="S184">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T184">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U184">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="V184">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W184">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X184">
         <v>1.04</v>
       </c>
       <c r="Y184">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z184">
         <v>3.35</v>
       </c>
       <c r="AA184">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB184">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC184">
         <v>3.45</v>
@@ -30355,10 +30355,10 @@
         <v>1.05</v>
       </c>
       <c r="AF184">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG184">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>1.56</v>
       </c>
       <c r="T185">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U185">
         <v>3.5</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O186">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P186">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="Q186">
         <v>1.85</v>
@@ -30648,10 +30648,10 @@
         <v>4.4</v>
       </c>
       <c r="U186">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V186">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="W186">
         <v>1.25</v>
@@ -30669,13 +30669,13 @@
         <v>1.3</v>
       </c>
       <c r="AB186">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AC186">
         <v>1.85</v>
       </c>
       <c r="AD186">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE186">
         <v>1.38</v>
@@ -30790,7 +30790,7 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O187">
         <v>3.6</v>
@@ -30799,7 +30799,7 @@
         <v>2.85</v>
       </c>
       <c r="Q187">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R187">
         <v>2.25</v>
@@ -30814,25 +30814,25 @@
         <v>2.4</v>
       </c>
       <c r="V187">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W187">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X187">
         <v>1.04</v>
       </c>
       <c r="Y187">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z187">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="AA187">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB187">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC187">
         <v>2.55</v>
@@ -31128,49 +31128,49 @@
         <v>1.95</v>
       </c>
       <c r="R189">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S189">
         <v>1.28</v>
       </c>
       <c r="T189">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U189">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W189">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X189">
         <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z189">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA189">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB189">
         <v>1.98</v>
       </c>
       <c r="AC189">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AD189">
         <v>1.44</v>
       </c>
       <c r="AE189">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF189">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG189">
         <v>2.05</v>
@@ -31279,34 +31279,34 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="O190">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P190">
-        <v>3.97</v>
+        <v>3.57</v>
       </c>
       <c r="Q190">
         <v>2.15</v>
       </c>
       <c r="R190">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S190">
         <v>1.22</v>
       </c>
       <c r="T190">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U190">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V190">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W190">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X190">
         <v>1.01</v>
@@ -31315,16 +31315,16 @@
         <v>1.14</v>
       </c>
       <c r="Z190">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA190">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB190">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC190">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AD190">
         <v>1.5</v>
@@ -31352,7 +31352,7 @@
         <v>1.17</v>
       </c>
       <c r="AK190">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31442,10 +31442,10 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O191">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P191">
         <v>2.45</v>
@@ -31614,7 +31614,7 @@
         <v>2.87</v>
       </c>
       <c r="Q192">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R192">
         <v>1.94</v>
@@ -31635,25 +31635,25 @@
         <v>1.06</v>
       </c>
       <c r="X192">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z192">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AA192">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB192">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC192">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD192">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE192">
         <v>1.03</v>
@@ -31777,7 +31777,7 @@
         <v>2.25</v>
       </c>
       <c r="Q193">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R193">
         <v>2.3</v>
@@ -31841,7 +31841,7 @@
         <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31940,7 +31940,7 @@
         <v>2.3</v>
       </c>
       <c r="Q194">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="R194">
         <v>2.18</v>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AK194">
         <v>1.31</v>
@@ -32103,7 +32103,7 @@
         <v>1.77</v>
       </c>
       <c r="Q195">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R195">
         <v>2.38</v>
@@ -32127,16 +32127,16 @@
         <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z195">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA195">
         <v>1.57</v>
       </c>
       <c r="AB195">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AC195">
         <v>2.47</v>
@@ -32148,7 +32148,7 @@
         <v>1.18</v>
       </c>
       <c r="AF195">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG195">
         <v>2.3</v>

--- a/jogos_2026-08-16.xlsx
+++ b/jogos_2026-08-16.xlsx
@@ -9251,13 +9251,13 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "18"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -17250,14 +17250,14 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N104">
@@ -17322,12 +17322,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83", "90"]</t>
         </is>
       </c>
       <c r="AJ104">
@@ -17340,28 +17340,28 @@
         <v>0</v>
       </c>
       <c r="AM104">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN104">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO104">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP104">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ104">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS104">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT104">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
@@ -18705,26 +18705,26 @@
         </is>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N113">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "57"]</t>
         </is>
       </c>
       <c r="AJ113">
@@ -18807,28 +18807,28 @@
         <v>0</v>
       </c>
       <c r="AM113">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN113">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO113">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP113">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ113">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR113">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS113">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT113">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
@@ -18868,13 +18868,13 @@
         </is>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -18883,11 +18883,11 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N114">
@@ -18952,12 +18952,12 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ114">
@@ -18970,28 +18970,28 @@
         <v>0</v>
       </c>
       <c r="AM114">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN114">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO114">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP114">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ114">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR114">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS114">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT114">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
@@ -19031,13 +19031,13 @@
         </is>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -19046,115 +19046,115 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N115">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O115">
         <v>3.45</v>
       </c>
       <c r="P115">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q115">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="R115">
         <v>2.08</v>
       </c>
       <c r="S115">
+        <v>1.38</v>
+      </c>
+      <c r="T115">
+        <v>2.75</v>
+      </c>
+      <c r="U115">
+        <v>2.9</v>
+      </c>
+      <c r="V115">
         <v>1.36</v>
       </c>
-      <c r="T115">
-        <v>2.88</v>
-      </c>
-      <c r="U115">
-        <v>2.8</v>
-      </c>
-      <c r="V115">
-        <v>1.4</v>
-      </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
         <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB115">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC115">
         <v>3.6</v>
       </c>
       <c r="AD115">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE115">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
+        <v>1.93</v>
+      </c>
+      <c r="AG115">
+        <v>1.79</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>["22", "44"]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>["77"]</t>
+        </is>
+      </c>
+      <c r="AJ115">
+        <v>1.17</v>
+      </c>
+      <c r="AK115">
         <v>1.9</v>
       </c>
-      <c r="AG115">
-        <v>1.83</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.15</v>
-      </c>
-      <c r="AK115">
-        <v>1.95</v>
-      </c>
       <c r="AL115">
         <v>0</v>
       </c>
       <c r="AM115">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN115">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO115">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP115">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ115">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR115">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS115">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT115">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
@@ -19194,26 +19194,26 @@
         </is>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N116">
@@ -19278,12 +19278,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "89"]</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "52", "65"]</t>
         </is>
       </c>
       <c r="AJ116">
@@ -19296,28 +19296,28 @@
         <v>0</v>
       </c>
       <c r="AM116">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN116">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO116">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP116">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ116">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AR116">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS116">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AT116">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N117">
@@ -19459,28 +19459,28 @@
         <v>0</v>
       </c>
       <c r="AM117">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN117">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO117">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP117">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ117">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR117">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS117">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT117">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
@@ -19520,13 +19520,13 @@
         </is>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N118">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "31"]</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
@@ -19622,28 +19622,28 @@
         <v>0</v>
       </c>
       <c r="AM118">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN118">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO118">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP118">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR118">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS118">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT118">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
@@ -19683,26 +19683,26 @@
         </is>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119">
         <v>0</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N119">
@@ -19767,12 +19767,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "49"]</t>
         </is>
       </c>
       <c r="AJ119">
@@ -19785,28 +19785,28 @@
         <v>0</v>
       </c>
       <c r="AM119">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN119">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO119">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP119">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ119">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR119">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS119">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT119">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
@@ -20009,26 +20009,26 @@
         </is>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121">
         <v>0</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N121">
@@ -20093,12 +20093,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "42"]</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "81", "90+7", "90+10"]</t>
         </is>
       </c>
       <c r="AJ121">
@@ -20111,28 +20111,28 @@
         <v>0</v>
       </c>
       <c r="AM121">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN121">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AO121">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP121">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AQ121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR121">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AS121">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT121">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
@@ -20172,26 +20172,26 @@
         </is>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N122">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "52"]</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
@@ -20274,28 +20274,28 @@
         <v>0</v>
       </c>
       <c r="AM122">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN122">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO122">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP122">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ122">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR122">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AS122">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT122">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
@@ -20501,23 +20501,23 @@
         <v>0</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I124">
         <v>0</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K124">
         <v>0</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N124">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "36", "40", "62"]</t>
         </is>
       </c>
       <c r="AJ124">
@@ -20600,28 +20600,28 @@
         <v>0</v>
       </c>
       <c r="AM124">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN124">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO124">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP124">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ124">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AR124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS124">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT124">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
@@ -20661,26 +20661,26 @@
         </is>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125">
         <v>0</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N125">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "48", "90+6"]</t>
         </is>
       </c>
       <c r="AJ125">
@@ -20763,28 +20763,28 @@
         <v>0</v>
       </c>
       <c r="AM125">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN125">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO125">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP125">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ125">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR125">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS125">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT125">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N126">
@@ -20926,28 +20926,28 @@
         <v>0</v>
       </c>
       <c r="AM126">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN126">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO126">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP126">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ126">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS126">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT126">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
@@ -20987,10 +20987,10 @@
         </is>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -20999,14 +20999,14 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N127">
@@ -21071,12 +21071,12 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "66", "90+1", "90+4"]</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ127">
@@ -21089,28 +21089,28 @@
         <v>0</v>
       </c>
       <c r="AM127">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN127">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO127">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP127">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR127">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS127">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT127">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
@@ -21150,26 +21150,26 @@
         </is>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N128">
@@ -21234,12 +21234,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "37", "90"]</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "45+5"]</t>
         </is>
       </c>
       <c r="AJ128">
@@ -21252,28 +21252,28 @@
         <v>0</v>
       </c>
       <c r="AM128">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN128">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO128">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP128">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ128">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR128">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS128">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT128">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
@@ -21313,10 +21313,10 @@
         </is>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -21325,14 +21325,14 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N129">
@@ -21397,12 +21397,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ129">
@@ -21415,28 +21415,28 @@
         <v>0</v>
       </c>
       <c r="AM129">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN129">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO129">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP129">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ129">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AR129">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS129">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT129">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
@@ -21476,42 +21476,42 @@
         </is>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N130">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="O130">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="P130">
         <v>9.5</v>
       </c>
       <c r="Q130">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R130">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="S130">
         <v>1.22</v>
@@ -21523,13 +21523,13 @@
         <v>2.05</v>
       </c>
       <c r="V130">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W130">
         <v>1.17</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
         <v>1.12</v>
@@ -21547,20 +21547,20 @@
         <v>2.05</v>
       </c>
       <c r="AD130">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE130">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF130">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG130">
         <v>1.73</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "13", "17", "26", "90"]</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
@@ -21572,34 +21572,34 @@
         <v>1.03</v>
       </c>
       <c r="AK130">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AL130">
         <v>0</v>
       </c>
       <c r="AM130">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN130">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO130">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP130">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR130">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AS130">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT130">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
@@ -21639,26 +21639,26 @@
         </is>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N131">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "40", "80"]</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
@@ -21741,28 +21741,28 @@
         <v>0</v>
       </c>
       <c r="AM131">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN131">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO131">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP131">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ131">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR131">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AS131">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT131">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
@@ -21802,26 +21802,26 @@
         </is>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N132">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "12", "14", "42", "45+4", "56", "74", "86"]</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
@@ -21904,28 +21904,28 @@
         <v>0</v>
       </c>
       <c r="AM132">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN132">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO132">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP132">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ132">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AR132">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS132">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT132">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
@@ -21965,26 +21965,26 @@
         </is>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N133">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "30", "45+1", "90+1"]</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
@@ -22067,28 +22067,28 @@
         <v>0</v>
       </c>
       <c r="AM133">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN133">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO133">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP133">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ133">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR133">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS133">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT133">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
@@ -22128,13 +22128,13 @@
         </is>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -22147,7 +22147,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N134">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
@@ -22230,28 +22230,28 @@
         <v>0</v>
       </c>
       <c r="AM134">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN134">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO134">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP134">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ134">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS134">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT134">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>0</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -22306,11 +22306,11 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N135">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ135">
@@ -22393,28 +22393,28 @@
         <v>0</v>
       </c>
       <c r="AM135">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN135">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO135">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP135">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ135">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AR135">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS135">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT135">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
@@ -22457,23 +22457,23 @@
         <v>0</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I136">
         <v>0</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136">
         <v>0</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N136">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "67", "78"]</t>
         </is>
       </c>
       <c r="AJ136">
@@ -22556,28 +22556,28 @@
         <v>0</v>
       </c>
       <c r="AM136">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN136">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO136">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP136">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ136">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR136">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS136">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT136">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
@@ -22617,26 +22617,26 @@
         </is>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I137">
         <v>0</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N137">
@@ -22701,12 +22701,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "53", "61"]</t>
         </is>
       </c>
       <c r="AJ137">
@@ -22719,28 +22719,28 @@
         <v>0</v>
       </c>
       <c r="AM137">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN137">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO137">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP137">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ137">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR137">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS137">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT137">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
@@ -22780,26 +22780,26 @@
         </is>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N138">
@@ -22864,12 +22864,12 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "75"]</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AJ138">
@@ -22882,28 +22882,28 @@
         <v>0</v>
       </c>
       <c r="AM138">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN138">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO138">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP138">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ138">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR138">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS138">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT138">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
@@ -22943,36 +22943,36 @@
         </is>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N139">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O139">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P139">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -22981,10 +22981,10 @@
         <v>1.75</v>
       </c>
       <c r="S139">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T139">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="U139">
         <v>4.2</v>
@@ -22996,13 +22996,13 @@
         <v>1.02</v>
       </c>
       <c r="X139">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Y139">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z139">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AA139">
         <v>3.6</v>
@@ -23011,62 +23011,62 @@
         <v>1.25</v>
       </c>
       <c r="AC139">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="AD139">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE139">
         <v>1.01</v>
       </c>
       <c r="AF139">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG139">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "29", "81"]</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ139">
         <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL139">
         <v>0</v>
       </c>
       <c r="AM139">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN139">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO139">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP139">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR139">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS139">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT139">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
@@ -23106,26 +23106,26 @@
         </is>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>0</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N140">
@@ -23190,12 +23190,12 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ140">
@@ -23208,28 +23208,28 @@
         <v>0</v>
       </c>
       <c r="AM140">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN140">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO140">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP140">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ140">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR140">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS140">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT140">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
@@ -23269,26 +23269,26 @@
         </is>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N141">
@@ -23353,12 +23353,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "54", "55"]</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "38", "43"]</t>
         </is>
       </c>
       <c r="AJ141">
@@ -23371,28 +23371,28 @@
         <v>0</v>
       </c>
       <c r="AM141">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN141">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO141">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP141">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ141">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AR141">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AS141">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT141">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
@@ -23432,26 +23432,26 @@
         </is>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142">
         <v>0</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N142">
@@ -23516,12 +23516,12 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "48", "72"]</t>
         </is>
       </c>
       <c r="AJ142">
@@ -23534,28 +23534,28 @@
         <v>0</v>
       </c>
       <c r="AM142">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN142">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO142">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP142">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ142">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR142">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS142">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT142">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
@@ -23595,26 +23595,26 @@
         </is>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N143">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "59"]</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "45", "54", "89"]</t>
         </is>
       </c>
       <c r="AJ143">
@@ -23697,28 +23697,28 @@
         <v>0</v>
       </c>
       <c r="AM143">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN143">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO143">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP143">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ143">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR143">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AS143">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT143">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N144">
@@ -23860,28 +23860,28 @@
         <v>0</v>
       </c>
       <c r="AM144">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN144">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO144">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP144">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ144">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR144">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS144">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT144">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -23933,14 +23933,14 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N145">
@@ -24005,7 +24005,7 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "76", "90+4"]</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
@@ -24023,28 +24023,28 @@
         <v>0</v>
       </c>
       <c r="AM145">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN145">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO145">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP145">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ145">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR145">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS145">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT145">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
@@ -24084,26 +24084,26 @@
         </is>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K146">
         <v>0</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N146">
@@ -24168,12 +24168,12 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "39"]</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "35", "68"]</t>
         </is>
       </c>
       <c r="AJ146">
@@ -24186,28 +24186,28 @@
         <v>0</v>
       </c>
       <c r="AM146">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN146">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO146">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP146">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ146">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR146">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS146">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT146">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N147">
@@ -24349,28 +24349,28 @@
         <v>0</v>
       </c>
       <c r="AM147">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN147">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO147">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP147">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ147">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AR147">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS147">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT147">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
@@ -24410,26 +24410,26 @@
         </is>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N148">
@@ -24494,12 +24494,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "53"]</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AJ148">
@@ -24512,28 +24512,28 @@
         <v>0</v>
       </c>
       <c r="AM148">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN148">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO148">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP148">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ148">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR148">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS148">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT148">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
@@ -24736,13 +24736,13 @@
         </is>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -24751,11 +24751,11 @@
         <v>0</v>
       </c>
       <c r="L150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N150">
@@ -24820,12 +24820,12 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "77"]</t>
         </is>
       </c>
       <c r="AJ150">
@@ -24838,28 +24838,28 @@
         <v>0</v>
       </c>
       <c r="AM150">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN150">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO150">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP150">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ150">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS150">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT150">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
@@ -24890,22 +24890,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -24918,111 +24918,111 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N151">
+        <v>1.34</v>
+      </c>
+      <c r="O151">
+        <v>4.8</v>
+      </c>
+      <c r="P151">
+        <v>7.5</v>
+      </c>
+      <c r="Q151">
+        <v>1.75</v>
+      </c>
+      <c r="R151">
+        <v>2.75</v>
+      </c>
+      <c r="S151">
+        <v>1.25</v>
+      </c>
+      <c r="T151">
+        <v>3.6</v>
+      </c>
+      <c r="U151">
         <v>2.25</v>
       </c>
-      <c r="O151">
-        <v>3.45</v>
-      </c>
-      <c r="P151">
-        <v>2.95</v>
-      </c>
-      <c r="Q151">
-        <v>2.7</v>
-      </c>
-      <c r="R151">
-        <v>2.07</v>
-      </c>
-      <c r="S151">
-        <v>1.36</v>
-      </c>
-      <c r="T151">
-        <v>3.1</v>
-      </c>
-      <c r="U151">
-        <v>2.74</v>
-      </c>
       <c r="V151">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W151">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z151">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="AA151">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AB151">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AC151">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="AD151">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE151">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF151">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG151">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
+          <t>["25"]</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ151">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>1.62</v>
+        <v>2.94</v>
       </c>
       <c r="AL151">
         <v>0</v>
       </c>
       <c r="AM151">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN151">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO151">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP151">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ151">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR151">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AS151">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT151">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
@@ -25053,16 +25053,16 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -25074,118 +25074,118 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N152">
-        <v>1.34</v>
+        <v>2.25</v>
       </c>
       <c r="O152">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P152">
-        <v>7.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q152">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="R152">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T152">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U152">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
+        <v>1.25</v>
+      </c>
+      <c r="Z152">
+        <v>3.6</v>
+      </c>
+      <c r="AA152">
+        <v>1.83</v>
+      </c>
+      <c r="AB152">
+        <v>2</v>
+      </c>
+      <c r="AC152">
+        <v>2.89</v>
+      </c>
+      <c r="AD152">
+        <v>1.36</v>
+      </c>
+      <c r="AE152">
         <v>1.14</v>
       </c>
-      <c r="Z152">
-        <v>4.95</v>
-      </c>
-      <c r="AA152">
-        <v>1.5</v>
-      </c>
-      <c r="AB152">
-        <v>2.55</v>
-      </c>
-      <c r="AC152">
-        <v>2.3</v>
-      </c>
-      <c r="AD152">
-        <v>1.6</v>
-      </c>
-      <c r="AE152">
-        <v>1.2</v>
-      </c>
       <c r="AF152">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG152">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
+          <t>["53", "62", "70"]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ152">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK152">
-        <v>2.94</v>
+        <v>1.62</v>
       </c>
       <c r="AL152">
         <v>0</v>
       </c>
       <c r="AM152">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN152">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO152">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP152">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ152">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR152">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS152">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT152">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
@@ -25225,26 +25225,26 @@
         </is>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N153">
@@ -25309,7 +25309,7 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "51"]</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
@@ -25327,28 +25327,28 @@
         <v>0</v>
       </c>
       <c r="AM153">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN153">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO153">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP153">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ153">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS153">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT153">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N154">
@@ -25490,28 +25490,28 @@
         <v>0</v>
       </c>
       <c r="AM154">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN154">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO154">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP154">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ154">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR154">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS154">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT154">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
@@ -25551,26 +25551,26 @@
         </is>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155">
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N155">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "71", "88"]</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
@@ -25653,28 +25653,28 @@
         <v>0</v>
       </c>
       <c r="AM155">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN155">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO155">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP155">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ155">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR155">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS155">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT155">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
@@ -25877,26 +25877,26 @@
         </is>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K157">
         <v>0</v>
       </c>
       <c r="L157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N157">
@@ -25961,12 +25961,12 @@
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "35", "47", "56", "84"]</t>
         </is>
       </c>
       <c r="AJ157">
@@ -25979,28 +25979,28 @@
         <v>0</v>
       </c>
       <c r="AM157">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN157">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO157">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP157">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ157">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR157">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS157">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT157">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
@@ -26203,26 +26203,26 @@
         </is>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L159">
         <v>0</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N159">
@@ -26287,7 +26287,7 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "62", "66"]</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
@@ -26305,28 +26305,28 @@
         <v>0</v>
       </c>
       <c r="AM159">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN159">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO159">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP159">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ159">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR159">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS159">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT159">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
@@ -26366,26 +26366,26 @@
         </is>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160">
         <v>0</v>
       </c>
       <c r="L160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N160">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "63"]</t>
         </is>
       </c>
       <c r="AJ160">
@@ -26468,28 +26468,28 @@
         <v>0</v>
       </c>
       <c r="AM160">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN160">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO160">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP160">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ160">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR160">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS160">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT160">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
@@ -26529,13 +26529,13 @@
         </is>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N161">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
@@ -26631,28 +26631,28 @@
         <v>0</v>
       </c>
       <c r="AM161">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN161">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO161">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP161">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ161">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR161">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS161">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT161">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
@@ -26715,55 +26715,55 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O162">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P162">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q162">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R162">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S162">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T162">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="U162">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="V162">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W162">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
         <v>1.25</v>
       </c>
       <c r="Z162">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="AA162">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB162">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC162">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD162">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE162">
         <v>1.1</v>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK162">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27021,13 +27021,13 @@
         <v>0</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164">
         <v>0</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164">
         <v>0</v>
@@ -27037,7 +27037,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N164">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AJ164">
@@ -27120,28 +27120,28 @@
         <v>0</v>
       </c>
       <c r="AM164">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN164">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO164">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP164">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ164">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR164">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS164">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT164">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
@@ -27184,13 +27184,13 @@
         <v>0</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165">
         <v>0</v>
       </c>
       <c r="J165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165">
         <v>0</v>
@@ -27200,7 +27200,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N165">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ165">
@@ -27283,28 +27283,28 @@
         <v>0</v>
       </c>
       <c r="AM165">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN165">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO165">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="AP165">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ165">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AR165">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS165">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT165">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
@@ -27370,28 +27370,28 @@
         <v>1.65</v>
       </c>
       <c r="O166">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P166">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q166">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="R166">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S166">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T166">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="U166">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V166">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W166">
         <v>1.04</v>
@@ -27406,25 +27406,25 @@
         <v>2.5</v>
       </c>
       <c r="AA166">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AB166">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC166">
         <v>5</v>
       </c>
       <c r="AD166">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE166">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF166">
         <v>2.07</v>
       </c>
       <c r="AG166">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK166">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27507,13 +27507,13 @@
         </is>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -27522,11 +27522,11 @@
         <v>0</v>
       </c>
       <c r="L167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N167">
@@ -27591,12 +27591,12 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "29"]</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ167">
@@ -27609,28 +27609,28 @@
         <v>0</v>
       </c>
       <c r="AM167">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN167">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO167">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP167">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ167">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR167">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS167">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT167">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -27682,14 +27682,14 @@
         <v>0</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L168">
         <v>0</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N168">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "84"]</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
@@ -27772,28 +27772,28 @@
         <v>0</v>
       </c>
       <c r="AM168">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN168">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO168">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP168">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ168">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR168">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS168">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT168">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
@@ -28019,16 +28019,16 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O170">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P170">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q170">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R170">
         <v>2.25</v>
@@ -28067,10 +28067,10 @@
         <v>3.05</v>
       </c>
       <c r="AD170">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE170">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF170">
         <v>1.8</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK170">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28341,7 +28341,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N172">
@@ -28363,7 +28363,7 @@
         <v>1.38</v>
       </c>
       <c r="T172">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="U172">
         <v>2.66</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O173">
         <v>3.5</v>
@@ -28517,7 +28517,7 @@
         <v>4.9</v>
       </c>
       <c r="Q173">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="R173">
         <v>2.04</v>
@@ -28541,25 +28541,25 @@
         <v>1.06</v>
       </c>
       <c r="Y173">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z173">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA173">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB173">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC173">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD173">
         <v>1.22</v>
       </c>
       <c r="AE173">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF173">
         <v>2</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK173">
         <v>2.04</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O174">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P174">
-        <v>2.48</v>
+        <v>4.33</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA174">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB174">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="O175">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P175">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q175">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R175">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S175">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T175">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U175">
+        <v>0</v>
+      </c>
+      <c r="V175">
+        <v>0</v>
+      </c>
+      <c r="W175">
+        <v>0</v>
+      </c>
+      <c r="X175">
+        <v>0</v>
+      </c>
+      <c r="Y175">
+        <v>0</v>
+      </c>
+      <c r="Z175">
+        <v>0</v>
+      </c>
+      <c r="AA175">
         <v>4</v>
       </c>
-      <c r="V175">
-        <v>1.2</v>
-      </c>
-      <c r="W175">
-        <v>1.03</v>
-      </c>
-      <c r="X175">
-        <v>1.15</v>
-      </c>
-      <c r="Y175">
-        <v>1.66</v>
-      </c>
-      <c r="Z175">
-        <v>2.1</v>
-      </c>
-      <c r="AA175">
-        <v>2.65</v>
-      </c>
       <c r="AB175">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC175">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD175">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE175">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF175">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG175">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK175">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q176">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="R176">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="S176">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="T176">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="U176">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="V176">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="W176">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y176">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="Z176">
-        <v>4.2</v>
+        <v>2.23</v>
       </c>
       <c r="AA176">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AB176">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AC176">
-        <v>2.57</v>
+        <v>5.1</v>
       </c>
       <c r="AD176">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="AE176">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF176">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="AG176">
-        <v>2.39</v>
+        <v>1.51</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AK176">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O177">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P177">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q177">
-        <v>2.58</v>
+        <v>2.71</v>
       </c>
       <c r="R177">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="T177">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="U177">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="V177">
+        <v>1.54</v>
+      </c>
+      <c r="W177">
+        <v>1.12</v>
+      </c>
+      <c r="X177">
+        <v>1.03</v>
+      </c>
+      <c r="Y177">
         <v>1.2</v>
       </c>
-      <c r="W177">
-        <v>1.03</v>
-      </c>
-      <c r="X177">
-        <v>1.11</v>
-      </c>
-      <c r="Y177">
-        <v>1.65</v>
-      </c>
       <c r="Z177">
+        <v>4.2</v>
+      </c>
+      <c r="AA177">
+        <v>1.66</v>
+      </c>
+      <c r="AB177">
         <v>2.15</v>
       </c>
-      <c r="AA177">
-        <v>2.48</v>
-      </c>
-      <c r="AB177">
-        <v>1.34</v>
-      </c>
       <c r="AC177">
-        <v>4.6</v>
+        <v>2.57</v>
       </c>
       <c r="AD177">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="AE177">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF177">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG177">
-        <v>1.42</v>
+        <v>2.39</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AK177">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-16 18:00:00</t>
+          <t>2026-08-16 17:00:00</t>
         </is>
       </c>
     </row>
@@ -29323,28 +29323,28 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O178">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="P178">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q178">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R178">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S178">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="T178">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="U178">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="V178">
         <v>1.14</v>
@@ -29356,19 +29356,19 @@
         <v>1.12</v>
       </c>
       <c r="Y178">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Z178">
         <v>2.02</v>
       </c>
       <c r="AA178">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AB178">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC178">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AD178">
         <v>1.05</v>
@@ -29377,7 +29377,7 @@
         <v>1.01</v>
       </c>
       <c r="AF178">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG178">
         <v>1.44</v>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK178">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,10 +29495,10 @@
         <v>4.45</v>
       </c>
       <c r="Q179">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="R179">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S179">
         <v>1.2</v>
@@ -29522,7 +29522,7 @@
         <v>1.08</v>
       </c>
       <c r="Z179">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="AA179">
         <v>1.36</v>
@@ -29540,10 +29540,10 @@
         <v>1.32</v>
       </c>
       <c r="AF179">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG179">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK179">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,10 +29649,10 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O180">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="P180">
         <v>5.45</v>
@@ -29688,25 +29688,25 @@
         <v>2.64</v>
       </c>
       <c r="AA180">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB180">
         <v>1.58</v>
       </c>
       <c r="AC180">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="AD180">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE180">
         <v>1.05</v>
       </c>
       <c r="AF180">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG180">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK180">
         <v>1.93</v>
@@ -29833,7 +29833,7 @@
         <v>2.7</v>
       </c>
       <c r="U181">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V181">
         <v>1.41</v>
@@ -29845,16 +29845,16 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z181">
         <v>3.4</v>
       </c>
       <c r="AA181">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB181">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC181">
         <v>3.4</v>
@@ -29981,7 +29981,7 @@
         <v>3.3</v>
       </c>
       <c r="P182">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q182">
         <v>2.9</v>
@@ -29996,7 +29996,7 @@
         <v>2.62</v>
       </c>
       <c r="U182">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="V182">
         <v>1.39</v>
@@ -30026,7 +30026,7 @@
         <v>1.25</v>
       </c>
       <c r="AE182">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF182">
         <v>1.73</v>
@@ -30048,7 +30048,7 @@
         <v>1.33</v>
       </c>
       <c r="AK182">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O183">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P183">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q183">
         <v>3.6</v>
@@ -30171,16 +30171,16 @@
         <v>1.07</v>
       </c>
       <c r="Y183">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z183">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AA183">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AB183">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC183">
         <v>4.1</v>
@@ -30189,13 +30189,13 @@
         <v>1.18</v>
       </c>
       <c r="AE183">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF183">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG183">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30310,13 +30310,13 @@
         <v>4.15</v>
       </c>
       <c r="Q184">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R184">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="S184">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T184">
         <v>2.25</v>
@@ -30340,7 +30340,7 @@
         <v>2.19</v>
       </c>
       <c r="AA184">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB184">
         <v>1.38</v>
@@ -30464,49 +30464,49 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O185">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P185">
         <v>5.5</v>
       </c>
       <c r="Q185">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="R185">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S185">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T185">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U185">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V185">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W185">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X185">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
         <v>1.2</v>
       </c>
       <c r="Z185">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA185">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB185">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC185">
         <v>2.63</v>
@@ -30515,13 +30515,13 @@
         <v>1.47</v>
       </c>
       <c r="AE185">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF185">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG185">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK185">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30630,10 +30630,10 @@
         <v>2.4</v>
       </c>
       <c r="O186">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P186">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="Q186">
         <v>2.97</v>
@@ -30660,7 +30660,7 @@
         <v>1.03</v>
       </c>
       <c r="Y186">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z186">
         <v>3.3</v>
@@ -30790,22 +30790,22 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O187">
         <v>2.9</v>
       </c>
       <c r="P187">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q187">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="R187">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S187">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T187">
         <v>2.4</v>
@@ -30823,22 +30823,22 @@
         <v>1.07</v>
       </c>
       <c r="Y187">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Z187">
         <v>2.45</v>
       </c>
       <c r="AA187">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB187">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC187">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AD187">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE187">
         <v>1</v>
@@ -30847,7 +30847,7 @@
         <v>2.1</v>
       </c>
       <c r="AG187">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK187">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O188">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P188">
-        <v>4.55</v>
+        <v>5.1</v>
       </c>
       <c r="Q188">
         <v>1.85</v>
@@ -30971,13 +30971,13 @@
         <v>1.18</v>
       </c>
       <c r="T188">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U188">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V188">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W188">
         <v>1.25</v>
@@ -30986,31 +30986,31 @@
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z188">
-        <v>8</v>
+        <v>7.74</v>
       </c>
       <c r="AA188">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB188">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AC188">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD188">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE188">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF188">
         <v>1.4</v>
       </c>
       <c r="AG188">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31116,19 +31116,19 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O189">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P189">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q189">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R189">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S189">
         <v>1.3</v>
@@ -31140,7 +31140,7 @@
         <v>2.4</v>
       </c>
       <c r="V189">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W189">
         <v>1.1</v>
@@ -31152,25 +31152,25 @@
         <v>1.2</v>
       </c>
       <c r="Z189">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA189">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB189">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC189">
         <v>2.55</v>
       </c>
       <c r="AD189">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE189">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF189">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG189">
         <v>2.3</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK189">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31279,61 +31279,61 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O190">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P190">
         <v>3.2</v>
       </c>
       <c r="Q190">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="R190">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S190">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T190">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U190">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V190">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W190">
         <v>1.03</v>
       </c>
       <c r="X190">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y190">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z190">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AA190">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AB190">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC190">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
       <c r="AD190">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE190">
         <v>1.05</v>
       </c>
       <c r="AF190">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG190">
         <v>1.75</v>
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="O191">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P191">
-        <v>5.44</v>
+        <v>4.22</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
       </c>
       <c r="R191">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S191">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T191">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U191">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="V191">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="W191">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X191">
         <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z191">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA191">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AB191">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AC191">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="AD191">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE191">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF191">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG191">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK191">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31940,7 +31940,7 @@
         <v>2.55</v>
       </c>
       <c r="Q194">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R194">
         <v>1.93</v>
@@ -32094,22 +32094,22 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O195">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P195">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q195">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="R195">
         <v>2.3</v>
       </c>
       <c r="S195">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T195">
         <v>3.22</v>
@@ -32121,37 +32121,37 @@
         <v>1.53</v>
       </c>
       <c r="W195">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X195">
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z195">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA195">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB195">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC195">
         <v>2.63</v>
       </c>
       <c r="AD195">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE195">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF195">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG195">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>2.3</v>
       </c>
       <c r="Q196">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="R196">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S196">
         <v>1.33</v>
       </c>
       <c r="T196">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U196">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V196">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W196">
         <v>1.07</v>
       </c>
       <c r="X196">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y196">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z196">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA196">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB196">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC196">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD196">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE196">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AK196">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32423,61 +32423,61 @@
         <v>3.75</v>
       </c>
       <c r="O197">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="P197">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q197">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R197">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S197">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T197">
         <v>3.5</v>
       </c>
       <c r="U197">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="V197">
         <v>1.58</v>
       </c>
       <c r="W197">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X197">
         <v>1.03</v>
       </c>
       <c r="Y197">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z197">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA197">
         <v>1.57</v>
       </c>
       <c r="AB197">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC197">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AD197">
         <v>1.56</v>
       </c>
       <c r="AE197">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF197">
         <v>1.5</v>
       </c>
       <c r="AG197">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
         <v>1.25</v>
